--- a/FOA Singles/Living-Single.xlsx
+++ b/FOA Singles/Living-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -811,14 +811,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ALMA 60" TV Stand, styled in Transitional and designed for everyday comfort. Built as a living tv console, it pairs well with a wide range of interiors. With Glass, Solid Wood, Wood Veneer, and Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 60"L X 18"W X 24"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Glass, Solid Wood, Wood Veneer.
-Color: Gray
-Weight: 90.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ALMA 60" TV Stand, styled in Transitional and designed for everyday comfort. Built as a living tv console, it pairs well with a wide range of interiors. With Glass, Solid Wood, Wood Veneer, and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 60"L X 18"W X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 90.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -939,14 +939,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALMA 72" TV Stand adds a Transitional touch while keeping the room feeling warm and welcoming. As a living tv console, it is designed to complement your space. Crafted from Glass, Solid Wood, Wood Veneer, it is finished in Gray tones that pair easily with surrounding decor.
-Product Dimensions: 72"L X 18"W X 24"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Glass, Solid Wood, Wood Veneer.
-Color: Gray
-Weight: 110 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALMA 72" TV Stand adds a Transitional touch while keeping the room feeling warm and welcoming. As a living tv console, it is designed to complement your space. Crafted from Glass, Solid Wood, Wood Veneer, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 72"L X 18"W X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 110 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BLAIR 70" TV Console, styled in Contemporary and designed for everyday comfort. This living tv console is made to fit naturally into the room. With Steel, Paper Veneer, and White or Champagne or Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 70 1/8"W X 15 3/4"D X 22 3/8"H
-Materials: Steel, Paper Veneer.
-Color: White or Champagne or Gray
-Weight: 94.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BLAIR 70" TV Console, styled in Contemporary and designed for everyday comfort. This living tv console is made to fit naturally into the room. With Steel, Paper Veneer, and White or Champagne or Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 70 1/8"W X 15 3/4"D X 22 3/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Paper Veneer.&lt;br&gt;
+Color: White or Champagne or Gray&lt;br&gt;
+Weight: 94.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="G5" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BORREGO TV Stand brings a Rustic look to your home with a refined, comfortable feel. Built as a living tv console, it pairs well with a wide range of interiors. The Metal, Solid Wood, construction is complemented by Dark Oak tones for a polished look.
-Product Dimensions: 72"W X 20"D X 29 7/8"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Metal, Solid Wood.
-Color: Dark Oak
-Weight: 169.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BORREGO TV Stand brings a Rustic look to your home with a refined, comfortable feel. Built as a living tv console, it pairs well with a wide range of interiors. The Metal, Solid Wood, construction is complemented by Dark Oak tones for a polished look.&lt;br&gt;
+Product Dimensions: 72"W X 20"D X 29 7/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Solid Wood.&lt;br&gt;
+Color: Dark Oak&lt;br&gt;
+Weight: 169.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H5" s="28" t="inlineStr">
@@ -1325,14 +1325,14 @@
       </c>
       <c r="G6" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BORREGO TV Stand, styled in Rustic and designed for everyday comfort. As a living tv console, it is designed to complement your space. With Metal, Solid Wood, and Antique White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 72"W X 20"D X 29 7/8"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Metal, Solid Wood.
-Color: Antique White
-Weight: 169.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BORREGO TV Stand, styled in Rustic and designed for everyday comfort. As a living tv console, it is designed to complement your space. With Metal, Solid Wood, and Antique White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 72"W X 20"D X 29 7/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Solid Wood.&lt;br&gt;
+Color: Antique White&lt;br&gt;
+Weight: 169.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H6" s="28" t="inlineStr">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BROMOAK Console Base, styled in Traditional and designed for everyday comfort. As a living tv console, it is designed to complement your space. With Solid Wood, Wood Veneer, and Weathered Oak tones, it blends structure and softness in one clean profile.
-Product Dimensions: 66"L X 23.75"W X 38"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Weathered Oak
-Weight: 202.82 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BROMOAK Console Base, styled in Traditional and designed for everyday comfort. As a living tv console, it is designed to complement your space. With Solid Wood, Wood Veneer, and Weathered Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 66"L X 23.75"W X 38"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Weathered Oak&lt;br&gt;
+Weight: 202.82 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1583,14 +1583,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BROMOAK Left Facing Unit Base adds a Traditional touch while keeping the room feeling warm and welcoming. This living tv console is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in Weathered Oak tones that pair easily with surrounding decor.
-Product Dimensions: 27.75"L X 21.75"W X 34"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Weathered Oak
-Weight: 84.88 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BROMOAK Left Facing Unit Base adds a Traditional touch while keeping the room feeling warm and welcoming. This living tv console is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in Weathered Oak tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 27.75"L X 21.75"W X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Weathered Oak&lt;br&gt;
+Weight: 84.88 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1711,14 +1711,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with BROMOAK Left Facing Unit Top and its Traditional character. Built as a living tv console, it pairs well with a wide range of interiors. Finished in Weathered Oak tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 32"L X 23"W X 56"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Weathered Oak
-Weight: 148.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with BROMOAK Left Facing Unit Top and its Traditional character. Built as a living tv console, it pairs well with a wide range of interiors. Finished in Weathered Oak tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 32"L X 23"W X 56"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Weathered Oak&lt;br&gt;
+Weight: 148.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BROMOAK Right Facing Unit Base brings a Traditional look to your home with a refined, comfortable feel. As a living tv console, it is designed to complement your space. The Solid Wood, Wood Veneer, construction is complemented by Weathered Oak tones for a polished look.
-Product Dimensions: 27.75"L X 21.75"W X 34"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Weathered Oak
-Weight: 84.88 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BROMOAK Right Facing Unit Base brings a Traditional look to your home with a refined, comfortable feel. As a living tv console, it is designed to complement your space. The Solid Wood, Wood Veneer, construction is complemented by Weathered Oak tones for a polished look.&lt;br&gt;
+Product Dimensions: 27.75"L X 21.75"W X 34"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Weathered Oak&lt;br&gt;
+Weight: 84.88 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1967,14 +1967,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BROMOAK Right Facing Unit Top, styled in Traditional and designed for everyday comfort. This living tv console is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Weathered Oak tones, it blends structure and softness in one clean profile.
-Product Dimensions: 32"L X 23"W X 56"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Weathered Oak
-Weight: 148.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BROMOAK Right Facing Unit Top, styled in Traditional and designed for everyday comfort. This living tv console is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Weathered Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 32"L X 23"W X 56"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Weathered Oak&lt;br&gt;
+Weight: 148.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="G12" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CERRO 59" TV Console and its Contemporary character. Built as a living tv console, it pairs well with a wide range of interiors. Finished in Black tones, the Lacquer, Metal, Wood, build balances durability with visual appeal.
-Product Dimensions: 59"W X 15 3/8"D X 15 3/4"H
-Materials: Lacquer, Metal, Wood.
-Color: Black
-Weight: 120 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CERRO 59" TV Console and its Contemporary character. Built as a living tv console, it pairs well with a wide range of interiors. Finished in Black tones, the Lacquer, Metal, Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 59"W X 15 3/8"D X 15 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 120 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H12" s="30" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="G13" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CERRO 59" TV Console brings a Contemporary look to your home with a refined, comfortable feel. As a living tv console, it is designed to complement your space. The Lacquer, Metal, Wood, construction is complemented by White tones for a polished look.
-Product Dimensions: 59"W X 15 3/8"D X 15 3/4"H
-Materials: Lacquer, Metal, Wood.
-Color: White
-Weight: 120 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CERRO 59" TV Console brings a Contemporary look to your home with a refined, comfortable feel. As a living tv console, it is designed to complement your space. The Lacquer, Metal, Wood, construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 59"W X 15 3/8"D X 15 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 120 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H13" s="30" t="inlineStr">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DIETRICH 60" TV Console brings a Contemporary look to your home with a refined, comfortable feel. As a living tv console, it is designed to complement your space. The Glass, Metal, construction is complemented by Black tones for a polished look.
-Product Dimensions: 60"W X 15 3/4"D X 19"H
-Materials: Glass, Metal.
-Color: Black
-Weight: 97.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DIETRICH 60" TV Console brings a Contemporary look to your home with a refined, comfortable feel. As a living tv console, it is designed to complement your space. The Glass, Metal, construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 60"W X 15 3/4"D X 19"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 97.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with EGALEO 55" TV Console, styled in Contemporary and designed for everyday comfort. As a living tv console, it is designed to complement your space. With Lacquer, Metal, Tempered Glass, Wood, and Black or White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 55 1/8"W X 15 3/4"D X 19 3/4"H
-Materials: Lacquer, Metal, Tempered Glass, Wood.
-Color: Black or White
-Weight: 68.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with EGALEO 55" TV Console, styled in Contemporary and designed for everyday comfort. As a living tv console, it is designed to complement your space. With Lacquer, Metal, Tempered Glass, Wood, and Black or White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 55 1/8"W X 15 3/4"D X 19 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Tempered Glass, Wood.&lt;br&gt;
+Color: Black or White&lt;br&gt;
+Weight: 68.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="G16" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ERNST 60" TV Stand adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living tv console, it is designed to complement your space. Crafted from Acrylic, Glass, Replicated Wood, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 60"L X 18"W X 21 3/4"H
-Materials: Acrylic, Glass, Replicated Wood.
-Color: Black
-Weight: 103.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ERNST 60" TV Stand adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living tv console, it is designed to complement your space. Crafted from Acrylic, Glass, Replicated Wood, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 60"L X 18"W X 21 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Acrylic, Glass, Replicated Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 103.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H16" s="33" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="G17" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ERNST 60" TV Stand and its Contemporary character. This living tv console is made to fit naturally into the room. Finished in White tones, the Acrylic, Glass, Replicated Wood, build balances durability with visual appeal.
-Product Dimensions: 60"L X 18"W X 21 3/4"H
-Materials: Acrylic, Glass, Replicated Wood.
-Color: White
-Weight: 103.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ERNST 60" TV Stand and its Contemporary character. This living tv console is made to fit naturally into the room. Finished in White tones, the Acrylic, Glass, Replicated Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 60"L X 18"W X 21 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Acrylic, Glass, Replicated Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 103.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H17" s="33" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EVOS 63" TV Console brings a Contemporary look to your home with a refined, comfortable feel. This living tv console is made to fit naturally into the room. The Lacquer, Metal, Tempered Glass, Wood, construction is complemented by Black or White tones for a polished look.
-Product Dimensions: 63"W X 19 3/4"D X 15 1/2"H
-Materials: Lacquer, Metal, Tempered Glass, Wood.
-Color: Black or White
-Weight: 99 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EVOS 63" TV Console brings a Contemporary look to your home with a refined, comfortable feel. This living tv console is made to fit naturally into the room. The Lacquer, Metal, Tempered Glass, Wood, construction is complemented by Black or White tones for a polished look.&lt;br&gt;
+Product Dimensions: 63"W X 19 3/4"D X 15 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Tempered Glass, Wood.&lt;br&gt;
+Color: Black or White&lt;br&gt;
+Weight: 99 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2989,14 +2989,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GEORGIA 60" TV Stand brings a Cottage look to your home with a refined, comfortable feel. This living tv console is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Antique White tones for a polished look.
-Product Dimensions: 72"L X 18"W X 24"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Multiple Drawers &amp; Storage
-Materials: Solid Wood, Wood Veneer.
-Color: Antique White
-Weight: 102.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GEORGIA 60" TV Stand brings a Cottage look to your home with a refined, comfortable feel. This living tv console is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Antique White tones for a polished look.&lt;br&gt;
+Product Dimensions: 72"L X 18"W X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Multiple Drawers &amp;amp; Storage&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Antique White&lt;br&gt;
+Weight: 102.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3117,14 +3117,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with GEORGIA 72" TV Stand, styled in Cottage and designed for everyday comfort. Built as a living tv console, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Antique White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 60"L X 18"W X 24"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Multiple Drawers &amp; Storage
-Materials: Solid Wood, Wood Veneer.
-Color: Antique White
-Weight: 121 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with GEORGIA 72" TV Stand, styled in Cottage and designed for everyday comfort. Built as a living tv console, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Antique White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 60"L X 18"W X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Multiple Drawers &amp;amp; Storage&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Antique White&lt;br&gt;
+Weight: 121 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KEBBYLL 60" TV Stand brings a Industrial look to your home with a refined, comfortable feel. Built as a living tv console, it pairs well with a wide range of interiors. The Metal, Paper Veneeer, Engineered Wood construction is complemented by Antique Black or Natural Tone tones for a polished look.
-Product Dimensions: 60"W X 15 1/2"D X 23"H
-Materials: Metal, Paper Veneeer, Engineered Wood.
-Color: Antique Black or Natural Tone
-Weight: 104.86 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KEBBYLL 60" TV Stand brings a Industrial look to your home with a refined, comfortable feel. Built as a living tv console, it pairs well with a wide range of interiors. The Metal, Paper Veneeer, Engineered Wood construction is complemented by Antique Black or Natural Tone tones for a polished look.&lt;br&gt;
+Product Dimensions: 60"W X 15 1/2"D X 23"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Paper Veneeer, Engineered Wood.&lt;br&gt;
+Color: Antique Black or Natural Tone&lt;br&gt;
+Weight: 104.86 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with KEBBYLL Bridge, styled in Industrial and designed for everyday comfort. As a living tv console, it is designed to complement your space. With Metal, Paper Veneeer, Engineered Wood and Antique Black or Natural Tone tones, it blends structure and softness in one clean profile.
-Product Dimensions: 68 7/8"W X 13 3/4"D X 7 1/2"H
-Materials: Metal, Paper Veneeer, Engineered Wood.
-Color: Antique Black or Natural Tone
-Weight: 48.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with KEBBYLL Bridge, styled in Industrial and designed for everyday comfort. As a living tv console, it is designed to complement your space. With Metal, Paper Veneeer, Engineered Wood and Antique Black or Natural Tone tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 68 7/8"W X 13 3/4"D X 7 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Paper Veneeer, Engineered Wood.&lt;br&gt;
+Color: Antique Black or Natural Tone&lt;br&gt;
+Weight: 48.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KEBBYLL Pier Cabinet adds a Industrial touch while keeping the room feeling warm and welcoming. This living tv console is made to fit naturally into the room. Crafted from Metal, Paper Veneeer, Engineered Wood, it is finished in Antique Black or Natural Tone tones that pair easily with surrounding decor.
-Product Dimensions: 21 1/4"W X 14"D X 62 1/2"H
-Materials: Metal, Paper Veneeer, Engineered Wood.
-Color: Antique Black or Natural Tone
-Weight: 61.42 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KEBBYLL Pier Cabinet adds a Industrial touch while keeping the room feeling warm and welcoming. This living tv console is made to fit naturally into the room. Crafted from Metal, Paper Veneeer, Engineered Wood, it is finished in Antique Black or Natural Tone tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 21 1/4"W X 14"D X 62 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Paper Veneeer, Engineered Wood.&lt;br&gt;
+Color: Antique Black or Natural Tone&lt;br&gt;
+Weight: 61.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NEAPOLI 63" TV Console brings a Contemporary look to your home with a refined, comfortable feel. As a living tv console, it is designed to complement your space. The Lacquer, Metal, Tempered Glass, Wood, construction is complemented by Black or White tones for a polished look.
-Product Dimensions: 63"W X 15 3/4"D X 19 5/8"H
-Materials: Lacquer, Metal, Tempered Glass, Wood.
-Color: Black or White
-Weight: 96.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NEAPOLI 63" TV Console brings a Contemporary look to your home with a refined, comfortable feel. As a living tv console, it is designed to complement your space. The Lacquer, Metal, Tempered Glass, Wood, construction is complemented by Black or White tones for a polished look.&lt;br&gt;
+Product Dimensions: 63"W X 15 3/4"D X 19 5/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Tempered Glass, Wood.&lt;br&gt;
+Color: Black or White&lt;br&gt;
+Weight: 96.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with NINOVE 55" TV Console and its Contemporary character. As a living tv console, it is designed to complement your space. Finished in White tones, the Lacquer, Metal, Wood, build balances durability with visual appeal.
-Product Dimensions: 55"W X 15 1/2"D X 16"H
-Materials: Lacquer, Metal, Wood.
-Color: White
-Weight: 61.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with NINOVE 55" TV Console and its Contemporary character. As a living tv console, it is designed to complement your space. Finished in White tones, the Lacquer, Metal, Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 55"W X 15 1/2"D X 16"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 61.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3867,14 +3867,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PRESHO 72" TV Stand adds a Rustic touch while keeping the room feeling warm and welcoming. This living tv console is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in Dark Oak tones that pair easily with surrounding decor.
-Product Dimensions: 72"L X 17"W X 27"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Cabinets &amp; Drawers
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Oak
-Weight: 128.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PRESHO 72" TV Stand adds a Rustic touch while keeping the room feeling warm and welcoming. This living tv console is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in Dark Oak tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 72"L X 17"W X 27"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Cabinets &amp;amp; Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Oak&lt;br&gt;
+Weight: 128.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SABUGAL 60" TV Stand, styled in Contemporary and designed for everyday comfort. As a living tv console, it is designed to complement your space. With Tempered Glass, Engineered Wood and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 60"L X 17 3/4"W X 24 1/4"H Bonus storage &amp; convenience features (from matching set pieces): No Show Drawer Pull
-Materials: Tempered Glass, Engineered Wood.
-Color: White
-Weight: 124 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SABUGAL 60" TV Stand, styled in Contemporary and designed for everyday comfort. As a living tv console, it is designed to complement your space. With Tempered Glass, Engineered Wood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 60"L X 17 3/4"W X 24 1/4"H Bonus storage &amp;amp; convenience features (from matching set pieces): No Show Drawer Pull&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 124 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SABUGAL 70" TV Stand adds a Contemporary touch while keeping the room feeling warm and welcoming. This living tv console is made to fit naturally into the room. Crafted from Tempered Glass, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 70"L X 17 3/4"W X 24 1/4"H Bonus storage &amp; convenience features (from matching set pieces): No Show Drawer Pull
-Materials: Tempered Glass, Engineered Wood.
-Color: White
-Weight: 140 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SABUGAL 70" TV Stand adds a Contemporary touch while keeping the room feeling warm and welcoming. This living tv console is made to fit naturally into the room. Crafted from Tempered Glass, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 70"L X 17 3/4"W X 24 1/4"H Bonus storage &amp;amp; convenience features (from matching set pieces): No Show Drawer Pull&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 140 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4247,12 +4247,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SILVER CREEK 2 Pc. Pier Shelves (1 Pair), styled in Contemporary and designed for everyday comfort. This living tv console is made to fit naturally into the room. With Metal, Tempered Glass and Brown or Silver tones, it blends structure and softness in one clean profile.
-Product Dimensions: 20 1/2"W X 15 1/8"D X 65"H
-Materials: Metal, Tempered Glass.
-Color: Brown or Silver
-Weight: 79 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SILVER CREEK 2 Pc. Pier Shelves (1 Pair), styled in Contemporary and designed for everyday comfort. This living tv console is made to fit naturally into the room. With Metal, Tempered Glass and Brown or Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 20 1/2"W X 15 1/8"D X 65"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass.&lt;br&gt;
+Color: Brown or Silver&lt;br&gt;
+Weight: 79 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SILVER CREEK 52" TV Console adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living tv console, it pairs well with a wide range of interiors. Crafted from Metal, Tempered Glass, it is finished in Brown or Silver tones that pair easily with surrounding decor.
-Product Dimensions: 52"W X 20"D X 22 1/2"H
-Materials: Metal, Tempered Glass.
-Color: Brown or Silver
-Weight: 82 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SILVER CREEK 52" TV Console adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living tv console, it pairs well with a wide range of interiors. Crafted from Metal, Tempered Glass, it is finished in Brown or Silver tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 52"W X 20"D X 22 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass.&lt;br&gt;
+Color: Brown or Silver&lt;br&gt;
+Weight: 82 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ALVISE Coffee Table, styled in Contemporary and designed for everyday comfort. Built as a living coffee table, it pairs well with a wide range of interiors. With Steel, Glass, and Champagne tones, it blends structure and softness in one clean profile.
-Product Dimensions: 38"DIA X 18"H
-Materials: Steel, Glass.
-Color: Champagne
-Weight: 47.74 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ALVISE Coffee Table, styled in Contemporary and designed for everyday comfort. Built as a living coffee table, it pairs well with a wide range of interiors. With Steel, Glass, and Champagne tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 38"DIA X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Glass.&lt;br&gt;
+Color: Champagne&lt;br&gt;
+Weight: 47.74 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4621,14 +4621,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ARLINGTON Coffee Table and its Rustic character. This living coffee table is made to fit naturally into the room. Finished in Antique White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 52"L X 28"W X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Antique White
-Weight: 77.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ARLINGTON Coffee Table and its Rustic character. This living coffee table is made to fit naturally into the room. Finished in Antique White tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 52"L X 28"W X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Antique White&lt;br&gt;
+Weight: 77.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4749,14 +4749,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ATWOOD II Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Tempered Glass, Solid Wood, Wood Veneer, it is finished in Dark Walnut tones that pair easily with surrounding decor.
-Product Dimensions: 48"L X 30"W X 18 1/2"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Tempered Glass, Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 65.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ATWOOD II Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Tempered Glass, Solid Wood, Wood Veneer, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"L X 30"W X 18 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 65.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4873,14 +4873,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AUGSBURG Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Metal, Solid Wood, Wood Veneer, it is finished in Walnut or Gold tones that pair easily with surrounding decor.
-Product Dimensions: 47 3/4"L X 24 3/4"W X 19"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Concealed Drawers
-Materials: Metal, Solid Wood, Wood Veneer.
-Color: Walnut or Gold
-Weight: 63.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AUGSBURG Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Metal, Solid Wood, Wood Veneer, it is finished in Walnut or Gold tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 3/4"L X 24 3/4"W X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Walnut or Gold&lt;br&gt;
+Weight: 63.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5001,16 +5001,16 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BACERRA Coffee Table adds a Rustic touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Metal, Solid Wood, it is finished in Antique White or Gold tones that pair easily with surrounding decor.
-Product Dimensions: 48"L X 24"W X 20 1/4"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Center Glide Drawers
-Pull Out Drawer
-Coffee Table Drawer Accessible from Both Sides
-Materials: Metal, Solid Wood.
-Color: Antique White or Gold
-Weight: 129.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BACERRA Coffee Table adds a Rustic touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Metal, Solid Wood, it is finished in Antique White or Gold tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"L X 24"W X 20 1/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Center Glide Drawers&lt;br&gt;
+Pull Out Drawer&lt;br&gt;
+Coffee Table Drawer Accessible from Both Sides&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Solid Wood.&lt;br&gt;
+Color: Antique White or Gold&lt;br&gt;
+Weight: 129.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BATAM II Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Metal, Tempered Glass, Paper Veneer, Engineered Wood construction is complemented by White or Natural Tone tones for a polished look.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 18 1/8"H
-Materials: Metal, Tempered Glass, Paper Veneer, Engineered Wood.
-Color: White or Natural Tone
-Weight: 68.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BATAM II Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Metal, Tempered Glass, Paper Veneer, Engineered Wood construction is complemented by White or Natural Tone tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 18 1/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: White or Natural Tone&lt;br&gt;
+Weight: 68.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BIMA II Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Tempered Glass,Paper Veneer, construction is complemented by White or Natural Tone tones for a polished look.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 17 1/8"H
-Materials: Tempered Glass,Paper Veneer.
-Color: White or Natural Tone
-Weight: 67.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BIMA II Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Tempered Glass,Paper Veneer, construction is complemented by White or Natural Tone tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 17 1/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass,Paper Veneer.&lt;br&gt;
+Color: White or Natural Tone&lt;br&gt;
+Weight: 67.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5375,12 +5375,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BISHOP Coffee Table, styled in Contemporary and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Steel, Glass and Black or Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 36"DIA X 18 "H
-Materials: Steel, Glass.
-Color: Black or Gray
-Weight: 53.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BISHOP Coffee Table, styled in Contemporary and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Steel, Glass and Black or Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 36"DIA X 18 "H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Glass.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 53.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5497,14 +5497,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CALANDRA Coffee Table brings a Rustic look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Solid Wood, construction is complemented by Antique Black tones for a polished look.
-Product Dimensions: 47 1/2"L X 28"W X 18 1/2"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Antique Black
-Weight: 82.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CALANDRA Coffee Table brings a Rustic look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Solid Wood, construction is complemented by Antique Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/2"L X 28"W X 18 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Antique Black&lt;br&gt;
+Weight: 82.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5625,14 +5625,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CARRIE Coffee Table brings a Transitional look to your home with a refined, comfortable feel. This living coffee table is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Antique Black tones for a polished look.
-Product Dimensions: 36"DIA X 18"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Antique Black
-Weight: 64.46 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CARRIE Coffee Table brings a Transitional look to your home with a refined, comfortable feel. This living coffee table is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Antique Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 36"DIA X 18"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Antique Black&lt;br&gt;
+Weight: 64.46 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CONISBROUGH Cocktail Table adds a Modern touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Modern, it is finished in Modern tones that pair easily with surrounding decor.
-Product Dimensions: 42"W X 42"D X 18"H
-Materials: Modern.
-Color: Modern
-Weight: 63.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CONISBROUGH Cocktail Table adds a Modern touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Modern, it is finished in Modern tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 42"W X 42"D X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Modern.&lt;br&gt;
+Color: Modern&lt;br&gt;
+Weight: 63.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CONISBROUGH Oval Cocktail Table and its Modern character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in Modern tones, the Modern build balances durability with visual appeal.
-Product Dimensions: 50"W X 28"D X 18"H
-Materials: Modern.
-Color: Modern
-Weight: 183.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CONISBROUGH Oval Cocktail Table and its Modern character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in Modern tones, the Modern build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 50"W X 28"D X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Modern.&lt;br&gt;
+Color: Modern&lt;br&gt;
+Weight: 183.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6015,15 +6015,15 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-COOKSHIRE Coffee Table brings a Traditional look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Rich Tobacco tones for a polished look.
-Product Dimensions: 48"W X 27.5"D X 20.5"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Rich Tobacco
-Weight: 52.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+COOKSHIRE Coffee Table brings a Traditional look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Rich Tobacco tones for a polished look.&lt;br&gt;
+Product Dimensions: 48"W X 27.5"D X 20.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rich Tobacco&lt;br&gt;
+Weight: 52.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6144,14 +6144,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CORINNE Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in White or Distressed Dark Oak tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 17"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White or Distressed Dark Oak
-Weight: 138.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CORINNE Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in White or Distressed Dark Oak tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 17"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Distressed Dark Oak&lt;br&gt;
+Weight: 138.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6272,14 +6272,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CRYSTAL COVE II Round Coffee Table w/ 4 Stools brings a Transitional look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Leatherette, Glass, Solid Wood, Wood Veneer &amp; construction is complemented by Dark Walnut tones for a polished look.
-Product Dimensions: 40"DIA X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Leatherette, Glass, Solid Wood, Wood Veneer &amp;.
-Color: Dark Walnut
-Weight: 115.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CRYSTAL COVE II Round Coffee Table w/ 4 Stools brings a Transitional look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Leatherette, Glass, Solid Wood, Wood Veneer &amp;amp; construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
+Product Dimensions: 40"DIA X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Glass, Solid Wood, Wood Veneer &amp;amp;.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 115.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6400,14 +6400,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CRYSTAL FALLS Coffee Table, styled in Transitional and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Tempered Glass, Solid Wood, Wood Veneer, and Dark Cherry tones, it blends structure and softness in one clean profile.
-Product Dimensions: 51"L X 35"W X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Tempered Glass, Solid Wood, Wood Veneer.
-Color: Dark Cherry
-Weight: 61 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CRYSTAL FALLS Coffee Table, styled in Transitional and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Tempered Glass, Solid Wood, Wood Veneer, and Dark Cherry tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 51"L X 35"W X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Cherry&lt;br&gt;
+Weight: 61 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="G47" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DUBENDORF Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Glass, construction is complemented by Black tones for a polished look.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 15"H
-Materials: Glass.
-Color: Black
-Weight: 74.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DUBENDORF Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Glass, construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 15"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 74.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H47" s="35" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="G48" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with DUBENDORF Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Glass, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 15"H
-Materials: Glass.
-Color: White
-Weight: 74.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with DUBENDORF Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Glass, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 15"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 74.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H48" s="35" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EIMEAR Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in White or Black tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 18"H
-Materials: Metal.
-Color: White or Black
-Weight: 64.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EIMEAR Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in White or Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: White or Black&lt;br&gt;
+Weight: 64.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6912,14 +6912,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FINLEY Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Glass, Solid Wood, it is finished in Espresso tones that pair easily with surrounding decor.
-Product Dimensions: 49"L X 29"W X 18"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Glass, Solid Wood.
-Color: Espresso
-Weight: 48.84 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FINLEY Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Glass, Solid Wood, it is finished in Espresso tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 49"L X 29"W X 18"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Solid Wood.&lt;br&gt;
+Color: Espresso&lt;br&gt;
+Weight: 48.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7040,14 +7040,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GIORDANI Coffee Table brings a Traditional look to your home with a refined, comfortable feel. This living coffee table is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Weathered Oak tones for a polished look.
-Product Dimensions: 52"W X 28"D X 20"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Weathered Oak
-Weight: 70.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GIORDANI Coffee Table brings a Traditional look to your home with a refined, comfortable feel. This living coffee table is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Weathered Oak tones for a polished look.&lt;br&gt;
+Product Dimensions: 52"W X 28"D X 20"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Weathered Oak&lt;br&gt;
+Weight: 70.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7173,14 +7173,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with GRANVIA Coffee Table and its Transitional character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in Dark Cherry tones, the Tempered Glass, Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 48"L X 28"W X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Tempered Glass, Solid Wood, Wood Veneer.
-Color: Dark Cherry
-Weight: 53.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with GRANVIA Coffee Table and its Transitional character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in Dark Cherry tones, the Tempered Glass, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 48"L X 28"W X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Cherry&lt;br&gt;
+Weight: 53.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GRASTEN Square Coffee Table adds a Modern Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Rubberwood, Oak Veneer, Engineered Wood, it is finished in Ash Gray tones that pair easily with surrounding decor.
-Product Dimensions: 48"W X 26"D X 18.5"H
-Materials: Rubberwood, Oak Veneer, Engineered Wood.
-Color: Ash Gray
-Weight: 135.52 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GRASTEN Square Coffee Table adds a Modern Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Rubberwood, Oak Veneer, Engineered Wood, it is finished in Ash Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"W X 26"D X 18.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
+Color: Ash Gray&lt;br&gt;
+Weight: 135.52 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -7429,14 +7429,14 @@
       </c>
       <c r="G54" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GUIS Round Coffee Table adds a Transitional touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Linen-like, Solid Wood, Wood Veneer, Engineered Wood, it is finished in Natural Tone or Beige tones that pair easily with surrounding decor.
-Product Dimensions: 40 3/4"DIA X 20 1/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Linen-like, Solid Wood, Wood Veneer, Engineered Wood.
-Color: Natural Tone or Beige
-Weight: 74.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GUIS Round Coffee Table adds a Transitional touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Linen-like, Solid Wood, Wood Veneer, Engineered Wood, it is finished in Natural Tone or Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 40 3/4"DIA X 20 1/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like, Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
+Color: Natural Tone or Beige&lt;br&gt;
+Weight: 74.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H54" s="37" t="inlineStr">
@@ -7564,14 +7564,14 @@
       </c>
       <c r="G55" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with GUIS Round Coffee Table and its Transitional character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in Natural Tone or Dark Gray tones, the Linen-like, Solid Wood, Wood Veneer, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 40 3/4"DIA X 20 1/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Linen-like, Solid Wood, Wood Veneer, Engineered Wood.
-Color: Natural Tone or Dark Gray
-Weight: 74.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with GUIS Round Coffee Table and its Transitional character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in Natural Tone or Dark Gray tones, the Linen-like, Solid Wood, Wood Veneer, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 40 3/4"DIA X 20 1/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like, Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
+Color: Natural Tone or Dark Gray&lt;br&gt;
+Weight: 74.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H55" s="37" t="inlineStr">
@@ -7698,15 +7698,15 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HALCASTER Coffee Table adds a Traditional touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in Java tones that pair easily with surrounding decor.
-Product Dimensions: 48"W X 28"D X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Java
-Weight: 69.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HALCASTER Coffee Table adds a Traditional touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in Java tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"W X 28"D X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Java&lt;br&gt;
+Weight: 69.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="G57" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HALEWOOD Cocktail Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Rubberwood, Oak Veneer, Engineered Wood, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 29"DIA X 17"H
-Materials: Rubberwood, Oak Veneer, Engineered Wood.
-Color: Black
-Weight: 41.34 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HALEWOOD Cocktail Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Rubberwood, Oak Veneer, Engineered Wood, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 29"DIA X 17"H&lt;/p&gt;
+&lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 41.34 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H57" s="39" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="G58" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with HALEWOOD Cocktail Table and its Contemporary character. As a living coffee table, it is designed to complement your space. Finished in Oak tones, the Rubberwood, Oak Veneer, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 29"DIA X 17"H
-Materials: Rubberwood, Oak Veneer, Engineered Wood.
-Color: Oak
-Weight: 44.13 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with HALEWOOD Cocktail Table and its Contemporary character. As a living coffee table, it is designed to complement your space. Finished in Oak tones, the Rubberwood, Oak Veneer, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 29"DIA X 17"H&lt;/p&gt;
+&lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
+Color: Oak&lt;br&gt;
+Weight: 44.13 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H58" s="39" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-IZAR Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Metal, Engineered Wood, it is finished in White or Gun Metal tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 18 1/8"H
-Materials: Metal, Engineered Wood.
-Color: White or Gun Metal
-Weight: 50.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+IZAR Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Metal, Engineered Wood, it is finished in White or Gun Metal tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 18 1/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Engineered Wood.&lt;br&gt;
+Color: White or Gun Metal&lt;br&gt;
+Weight: 50.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8207,14 +8207,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JOLIET Coffee Table adds a Transitional touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, Engineered Wood, it is finished in Antique White tones that pair easily with surrounding decor.
-Product Dimensions: 52"L X 28"W X 19"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Drawers
-Materials: Solid Wood, Wood Veneer, Engineered Wood.
-Color: Antique White
-Weight: 68.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JOLIET Coffee Table adds a Transitional touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, Engineered Wood, it is finished in Antique White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 52"L X 28"W X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
+Color: Antique White&lt;br&gt;
+Weight: 68.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8335,14 +8335,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JOLIET Sofa Table brings a Transitional look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Antique White tones for a polished look.
-Product Dimensions: 52"L X 18"W X 30"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Drawers
-Materials: Solid Wood, Wood Veneer.
-Color: Antique White
-Weight: 58.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JOLIET Sofa Table brings a Transitional look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Antique White tones for a polished look.&lt;br&gt;
+Product Dimensions: 52"L X 18"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Antique White&lt;br&gt;
+Weight: 58.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8464,14 +8464,14 @@
       </c>
       <c r="G62" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with KOBLENZ Coffee Table, styled in Glam and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Metal, and Light Teal tones, it blends structure and softness in one clean profile.
-Product Dimensions: 48"L X 24"W X 18"H
-Features
-- Glam design Bonus storage &amp; convenience features (from matching set pieces): Concealed Drawer
-Materials: Metal.
-Color: Light Teal
-Weight: 80 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with KOBLENZ Coffee Table, styled in Glam and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Metal, and Light Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 48"L X 24"W X 18"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Light Teal&lt;br&gt;
+Weight: 80 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H62" s="41" t="inlineStr">
@@ -8595,14 +8595,14 @@
       </c>
       <c r="G63" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KOBLENZ Coffee Table adds a Glam touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Metal, it is finished in Dark Walnut tones that pair easily with surrounding decor.
-Product Dimensions: 48"L X 24"W X 18"H
-Features
-- Glam design Bonus storage &amp; convenience features (from matching set pieces): Concealed Drawer
-Materials: Metal.
-Color: Dark Walnut
-Weight: 79 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KOBLENZ Coffee Table adds a Glam touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Metal, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"L X 24"W X 18"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 79 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H63" s="41" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LAILA Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Glass, Metal, it is finished in Chrome tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/4"L X 27 1/2"W X 16 3/4"H
-Materials: Glass, Metal.
-Color: Chrome
-Weight: 52.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LAILA Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Glass, Metal, it is finished in Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 27 1/2"W X 16 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 52.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with LOBB Coffee Table, styled in Industrial and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Steel, Paper Veneer, and Natural Tone or Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 1/4"L X 25 5/8"W X 18"H
-Materials: Steel, Paper Veneer.
-Color: Natural Tone or Black
-Weight: 65.12 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with LOBB Coffee Table, styled in Industrial and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Steel, Paper Veneer, and Natural Tone or Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 25 5/8"W X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Paper Veneer.&lt;br&gt;
+Color: Natural Tone or Black&lt;br&gt;
+Weight: 65.12 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -8978,12 +8978,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LODIA Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Tempered Glass, Paper Veneer, Engineered Wood construction is complemented by Gray tones for a polished look.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 17 1/2"H
-Materials: Tempered Glass, Paper Veneer, Engineered Wood.
-Color: Gray
-Weight: 67.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LODIA Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Tempered Glass, Paper Veneer, Engineered Wood construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 17 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 67.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="G67" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LODIA III Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Tempered Glass, Paper Veneer, Engineered Wood construction is complemented by Black tones for a polished look.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 17 3/4"H
-Materials: Tempered Glass, Paper Veneer, Engineered Wood.
-Color: Black
-Weight: 69.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LODIA III Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Tempered Glass, Paper Veneer, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 17 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 69.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H67" s="28" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="G68" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with LODIA III Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Tempered Glass, Paper Veneer, Engineered Wood and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 17 3/4"H
-Materials: Tempered Glass, Paper Veneer, Engineered Wood.
-Color: White
-Weight: 69.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with LODIA III Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Tempered Glass, Paper Veneer, Engineered Wood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 17 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 69.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H68" s="28" t="inlineStr">
@@ -9354,12 +9354,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LUDVIG Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Metal, Tempered Glass, it is finished in Chrome or Clear tones that pair easily with surrounding decor.
-Product Dimensions: 48"L X 24"W X 18"H
-Materials: Metal, Tempered Glass.
-Color: Chrome or Clear
-Weight: 63.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LUDVIG Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Metal, Tempered Glass, it is finished in Chrome or Clear tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"L X 24"W X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass.&lt;br&gt;
+Color: Chrome or Clear&lt;br&gt;
+Weight: 63.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -9480,14 +9480,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MAJKEN Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Solid Wood, it is finished in White or Natural Tone tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 18 1/8"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White or Natural Tone
-Weight: 74.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MAJKEN Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Solid Wood, it is finished in White or Natural Tone tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 18 1/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Natural Tone&lt;br&gt;
+Weight: 74.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -9608,14 +9608,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MANHATTAN IV Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Tempered Glass, Solid Wood, Wood Veneer, construction is complemented by Brown Cherry tones for a polished look.
-Product Dimensions: 48"L X 30"W X 18 3/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Tempered Glass, Solid Wood, Wood Veneer.
-Color: Brown Cherry
-Weight: 63.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MANHATTAN IV Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Tempered Glass, Solid Wood, Wood Veneer, construction is complemented by Brown Cherry tones for a polished look.&lt;br&gt;
+Product Dimensions: 48"L X 30"W X 18 3/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Brown Cherry&lt;br&gt;
+Weight: 63.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9732,14 +9732,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MANHATTAN IV End Table, styled in Contemporary and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Tempered Glass, Solid Wood, Wood Veneer, and Brown Cherry tones, it blends structure and softness in one clean profile.
-Product Dimensions: 16"DIA X 22 1/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Tempered Glass, Solid Wood, Wood Veneer.
-Color: Brown Cherry
-Weight: 37.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MANHATTAN IV End Table, styled in Contemporary and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Tempered Glass, Solid Wood, Wood Veneer, and Brown Cherry tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 16"DIA X 22 1/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Brown Cherry&lt;br&gt;
+Weight: 37.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -9856,14 +9856,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MANHATTAN IV Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Tempered Glass, Solid Wood, Wood Veneer, it is finished in Brown Cherry tones that pair easily with surrounding decor.
-Product Dimensions: 50"L X 18"W X 31"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Tempered Glass, Solid Wood, Wood Veneer.
-Color: Brown Cherry
-Weight: 61.98 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MANHATTAN IV Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Tempered Glass, Solid Wood, Wood Veneer, it is finished in Brown Cherry tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 50"L X 18"W X 31"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Brown Cherry&lt;br&gt;
+Weight: 61.98 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="G74" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MANNEDORF Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Tempered Glass,Paper Veneer, and Black or Dark Walnut tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 18 7/8"H
-Materials: Tempered Glass,Paper Veneer.
-Color: Black or Dark Walnut
-Weight: 102 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MANNEDORF Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Tempered Glass,Paper Veneer, and Black or Dark Walnut tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 18 7/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass,Paper Veneer.&lt;br&gt;
+Color: Black or Dark Walnut&lt;br&gt;
+Weight: 102 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H74" s="35" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="G75" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MANNEDORF Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Tempered Glass,Paper Veneer, it is finished in Black or White tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 18 7/8"H
-Materials: Tempered Glass,Paper Veneer.
-Color: Black or White
-Weight: 83.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MANNEDORF Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Tempered Glass,Paper Veneer, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 18 7/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass,Paper Veneer.&lt;br&gt;
+Color: Black or White&lt;br&gt;
+Weight: 83.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H75" s="35" t="inlineStr">
@@ -10239,15 +10239,15 @@
       </c>
       <c r="G76" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARSTON Coffee Table brings a Traditional look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Solid Wood, Wood Veneer, construction is complemented by Dark Walnut tones for a polished look.
-Product Dimensions: 48"W X 28"D X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 91.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARSTON Coffee Table brings a Traditional look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Solid Wood, Wood Veneer, construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
+Product Dimensions: 48"W X 28"D X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 91.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H76" s="33" t="inlineStr">
@@ -10371,15 +10371,15 @@
       </c>
       <c r="G77" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MARSTON Coffee Table, styled in Traditional and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Champagne tones, it blends structure and softness in one clean profile.
-Product Dimensions: 48"W X 28"D X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Champagne
-Weight: 60.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MARSTON Coffee Table, styled in Traditional and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Champagne tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 48"W X 28"D X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Champagne&lt;br&gt;
+Weight: 60.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H77" s="33" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MAY Coffee Table and its Traditional character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in Brown Cherry tones, the Glass, Metal, Wood build balances durability with visual appeal.
-Product Dimensions: 47 3/4"L X 33"W X 20"H
-Materials: Glass, Metal, Wood.
-Color: Brown Cherry
-Weight: 68 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MAY Coffee Table and its Traditional character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in Brown Cherry tones, the Glass, Metal, Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 47 3/4"L X 33"W X 20"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Wood.&lt;br&gt;
+Color: Brown Cherry&lt;br&gt;
+Weight: 68 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -10628,12 +10628,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MAY Side Table, styled in Traditional and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Glass, Metal, Wood and Brown Cherry tones, it blends structure and softness in one clean profile.
-Product Dimensions: 22"L X 22"W X 26 1/2"H
-Materials: Glass, Metal, Wood.
-Color: Brown Cherry
-Weight: 30.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MAY Side Table, styled in Traditional and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Glass, Metal, Wood and Brown Cherry tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 22"L X 22"W X 26 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Wood.&lt;br&gt;
+Color: Brown Cherry&lt;br&gt;
+Weight: 30.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -10754,14 +10754,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MEADOW Coffee Table and its Rustic character. As a living coffee table, it is designed to complement your space. Finished in Antique Black tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 48"L X 26"W X 18"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Antique Black
-Weight: 82.94 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MEADOW Coffee Table and its Rustic character. As a living coffee table, it is designed to complement your space. Finished in Antique Black tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 48"L X 26"W X 18"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Antique Black&lt;br&gt;
+Weight: 82.94 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -10882,14 +10882,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MEADOW Side Table brings a Rustic look to your home with a refined, comfortable feel. This living coffee table is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Antique Black tones for a polished look.
-Product Dimensions: 24"L X 14"W X 24"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Storage Drawers
-Materials: Solid Wood, Wood Veneer.
-Color: Antique Black
-Weight: 42.68 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MEADOW Side Table brings a Rustic look to your home with a refined, comfortable feel. This living coffee table is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Antique Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 24"L X 14"W X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Antique Black&lt;br&gt;
+Weight: 42.68 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -11010,12 +11010,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MEDA Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Lacquer, Metal, it is finished in White or Chrome tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 15 3/4"H
-Materials: Lacquer, Metal.
-Color: White or Chrome
-Weight: 57.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MEDA Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Lacquer, Metal, it is finished in White or Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 15 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal.&lt;br&gt;
+Color: White or Chrome&lt;br&gt;
+Weight: 57.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -11138,14 +11138,14 @@
       </c>
       <c r="G83" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MIKA Coffee Table w/ Cushion Top adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Fabric, Solid Wood, Wood Veneer, it is finished in Antique Oak tones that pair easily with surrounding decor.
-Product Dimensions: 48 1/2"DIA X 18"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Fabric, Solid Wood, Wood Veneer.
-Color: Antique Oak
-Weight: 102.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MIKA Coffee Table w/ Cushion Top adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Fabric, Solid Wood, Wood Veneer, it is finished in Antique Oak tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48 1/2"DIA X 18"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Antique Oak&lt;br&gt;
+Weight: 102.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H83" s="37" t="inlineStr">
@@ -11269,14 +11269,14 @@
       </c>
       <c r="G84" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MIKA Coffee Table w/ Cushion Top and its Rustic character. As a living coffee table, it is designed to complement your space. Finished in Antique Gray tones, the Fabric, Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 48"DIA X 20"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Fabric, Solid Wood, Wood Veneer.
-Color: Antique Gray
-Weight: 102.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MIKA Coffee Table w/ Cushion Top and its Rustic character. As a living coffee table, it is designed to complement your space. Finished in Antique Gray tones, the Fabric, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 48"DIA X 20"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Antique Gray&lt;br&gt;
+Weight: 102.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H84" s="37" t="inlineStr">
@@ -11399,14 +11399,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MOA Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in White or Natural Tone tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 18 1/8"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White or Natural Tone
-Weight: 111 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MOA Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Solid Wood, it is finished in White or Natural Tone tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 18 1/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Natural Tone&lt;br&gt;
+Weight: 111 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="G86" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with NAHARA Coffee Table, styled in Contemporary and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Glass, and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 18"H
-Materials: Glass.
-Color: Black
-Weight: 67.76 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with NAHARA Coffee Table, styled in Contemporary and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Glass, and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 67.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H86" s="39" t="inlineStr">
@@ -11655,12 +11655,12 @@
       </c>
       <c r="G87" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NAHARA Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Glass, it is finished in Gray tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 18"H
-Materials: Glass.
-Color: Gray
-Weight: 67.76 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NAHARA Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Glass, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 67.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H87" s="39" t="inlineStr">
@@ -11782,12 +11782,12 @@
       </c>
       <c r="G88" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with NAHARA Coffee Table and its Contemporary character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in White tones, the Glass, build balances durability with visual appeal.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 18"H
-Materials: Glass.
-Color: White
-Weight: 67.76 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with NAHARA Coffee Table and its Contemporary character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in White tones, the Glass, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 67.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H88" s="39" t="inlineStr">
@@ -11909,12 +11909,12 @@
       </c>
       <c r="G89" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NINOVE Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. This living coffee table is made to fit naturally into the room. The Lacquer, Metal, Wood, construction is complemented by Black or Chrome tones for a polished look.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 16"H
-Materials: Lacquer, Metal, Wood.
-Color: Black or Chrome
-Weight: 73.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NINOVE Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. This living coffee table is made to fit naturally into the room. The Lacquer, Metal, Wood, construction is complemented by Black or Chrome tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 16"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Wood.&lt;br&gt;
+Color: Black or Chrome&lt;br&gt;
+Weight: 73.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H89" s="41" t="inlineStr">
@@ -12038,12 +12038,12 @@
       </c>
       <c r="G90" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with NINOVE Coffee Table, styled in Contemporary and designed for everyday comfort. Built as a living coffee table, it pairs well with a wide range of interiors. With Lacquer, Metal, Wood, and White or Chrome tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 1/4"L X 23 1/2"W X 16"H
-Materials: Lacquer, Metal, Wood.
-Color: White or Chrome
-Weight: 73.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with NINOVE Coffee Table, styled in Contemporary and designed for everyday comfort. Built as a living coffee table, it pairs well with a wide range of interiors. With Lacquer, Metal, Wood, and White or Chrome tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 1/2"W X 16"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Wood.&lt;br&gt;
+Color: White or Chrome&lt;br&gt;
+Weight: 73.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H90" s="41" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="G91" s="44" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NORTHWICH Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Sintered Stone, Stainless Steel construction is complemented by White or Matte Gold tones for a polished look.
-Product Dimensions: 51"W X 27.5"D X 17.5"H
-Materials: Sintered Stone, Stainless Steel.
-Color: White or Matte Gold
-Weight: 124 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NORTHWICH Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Sintered Stone, Stainless Steel construction is complemented by White or Matte Gold tones for a polished look.&lt;br&gt;
+Product Dimensions: 51"W X 27.5"D X 17.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Sintered Stone, Stainless Steel.&lt;br&gt;
+Color: White or Matte Gold&lt;br&gt;
+Weight: 124 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H91" s="44" t="inlineStr">
@@ -12294,12 +12294,12 @@
       </c>
       <c r="G92" s="44" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with NORTHWICH Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Sintered Stone, Stainless Steel and Black or Gray or Matte Gold tones, it blends structure and softness in one clean profile.
-Product Dimensions: 51"W X 27.5"D X 17.5"H
-Materials: Sintered Stone, Stainless Steel.
-Color: Black or Gray or Matte Gold
-Weight: 127 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with NORTHWICH Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Sintered Stone, Stainless Steel and Black or Gray or Matte Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 51"W X 27.5"D X 17.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Sintered Stone, Stainless Steel.&lt;br&gt;
+Color: Black or Gray or Matte Gold&lt;br&gt;
+Weight: 127 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H92" s="44" t="inlineStr">
@@ -12420,12 +12420,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NORTHWICH Oval Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. This living coffee table is made to fit naturally into the room. The Sintered Stone, Stainless Steel construction is complemented by Black or Gray or Matte Gold tones for a polished look.
-Product Dimensions: 47"W X 31.5"D X 16.5"H
-Materials: Sintered Stone, Stainless Steel.
-Color: Black or Gray or Matte Gold
-Weight: 143 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NORTHWICH Oval Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. This living coffee table is made to fit naturally into the room. The Sintered Stone, Stainless Steel construction is complemented by Black or Gray or Matte Gold tones for a polished look.&lt;br&gt;
+Product Dimensions: 47"W X 31.5"D X 16.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Sintered Stone, Stainless Steel.&lt;br&gt;
+Color: Black or Gray or Matte Gold&lt;br&gt;
+Weight: 143 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with NOVA Coffee Table and its Contemporary character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in Satin Plated or Black tones, the Stainless Steel, Tempered Glass, build balances durability with visual appeal.
-Product Dimensions: 38"DIA X 16 1/4"H
-Materials: Stainless Steel, Tempered Glass.
-Color: Satin Plated or Black
-Weight: 59 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with NOVA Coffee Table and its Contemporary character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in Satin Plated or Black tones, the Stainless Steel, Tempered Glass, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 38"DIA X 16 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Satin Plated or Black&lt;br&gt;
+Weight: 59 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -12664,14 +12664,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OAKWAY Coffee Table brings a Traditional look to your home with a refined, comfortable feel. This living coffee table is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Weathered Oak tones for a polished look.
-Product Dimensions: 52"W X 32"D X 20"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Weathered Oak
-Weight: 95.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OAKWAY Coffee Table brings a Traditional look to your home with a refined, comfortable feel. This living coffee table is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Weathered Oak tones for a polished look.&lt;br&gt;
+Product Dimensions: 52"W X 32"D X 20"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Weathered Oak&lt;br&gt;
+Weight: 95.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ORLA II Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Stainless Steel, Tempered Glass, it is finished in Satin Plated or Black tones that pair easily with surrounding decor.
-Product Dimensions: 48"L X 24"W X 18"H
-Materials: Stainless Steel, Tempered Glass.
-Color: Satin Plated or Black
-Weight: 62.06 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ORLA II Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Stainless Steel, Tempered Glass, it is finished in Satin Plated or Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"L X 24"W X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Satin Plated or Black&lt;br&gt;
+Weight: 62.06 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -12914,12 +12914,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ORRIN Coffee Table, styled in Industrial and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Steel, Paper Veneer, and Gray or Walnut tones, it blends structure and softness in one clean profile.
-Product Dimensions: 35 3/8"DIA X 18"H
-Materials: Steel, Paper Veneer.
-Color: Gray or Walnut
-Weight: 45.62 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ORRIN Coffee Table, styled in Industrial and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Steel, Paper Veneer, and Gray or Walnut tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 35 3/8"DIA X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Paper Veneer.&lt;br&gt;
+Color: Gray or Walnut&lt;br&gt;
+Weight: 45.62 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -13045,12 +13045,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-POLTIMORE Round Cocktail Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Rubberwood, Oak Veneer, Engineered Wood, it is finished in Oak tones that pair easily with surrounding decor.
-Product Dimensions: 42"DIA X 15"H
-Materials: Rubberwood, Oak Veneer, Engineered Wood.
-Color: Oak
-Weight: 68.58 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+POLTIMORE Round Cocktail Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Rubberwood, Oak Veneer, Engineered Wood, it is finished in Oak tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 42"DIA X 15"H&lt;/p&gt;
+&lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
+Color: Oak&lt;br&gt;
+Weight: 68.58 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-RAYA Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Tempered Glass, Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 47"L X 23 5/8"W X 18 1/2"H
-Materials: Tempered Glass, Wood.
-Color: White
-Weight: 115.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+RAYA Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Tempered Glass, Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47"L X 23 5/8"W X 18 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 115.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -13298,15 +13298,15 @@
       </c>
       <c r="G100" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ROCHESTER Coffee Table, styled in Traditional and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Champagne tones, it blends structure and softness in one clean profile.
-Product Dimensions: 53"W X 30.5"D X 20.5"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Champagne
-Weight: 83.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ROCHESTER Coffee Table, styled in Traditional and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Champagne tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 53"W X 30.5"D X 20.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Champagne&lt;br&gt;
+Weight: 83.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H100" s="30" t="inlineStr">
@@ -13434,15 +13434,15 @@
       </c>
       <c r="G101" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ROCHESTER Coffee Table adds a Traditional touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Champagne tones that pair easily with surrounding decor.
-Product Dimensions: 53"W X 30.5"D X 20.5"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Champagne
-Weight: 73.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ROCHESTER Coffee Table adds a Traditional touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Champagne tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 53"W X 30.5"D X 20.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Champagne&lt;br&gt;
+Weight: 73.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H101" s="30" t="inlineStr">
@@ -13565,14 +13565,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ROSETTA Coffee Table, styled in Transitional and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Faux Marble, Solid Wood, Wood Veneer, and Dark Walnut tones, it blends structure and softness in one clean profile.
-Product Dimensions: 48"L X 26"W X 19 1/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Faux Marble, Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 112.42 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ROSETTA Coffee Table, styled in Transitional and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Faux Marble, Solid Wood, Wood Veneer, and Dark Walnut tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 48"L X 26"W X 19 1/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Faux Marble, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 112.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -13693,12 +13693,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ROXO Coffee Table and its Contemporary character. This living coffee table is made to fit naturally into the room. Finished in Satin Plated or Black tones, the Stainless Steel, Tempered Glass, build balances durability with visual appeal.
-Product Dimensions: 50"L X 28"W X 18 1/2"H
-Materials: Stainless Steel, Tempered Glass.
-Color: Satin Plated or Black
-Weight: 66.99 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ROXO Coffee Table and its Contemporary character. This living coffee table is made to fit naturally into the room. Finished in Satin Plated or Black tones, the Stainless Steel, Tempered Glass, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 50"L X 28"W X 18 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Satin Plated or Black&lt;br&gt;
+Weight: 66.99 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -13815,12 +13815,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-RYLEE Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Metal, Tempered Glass, it is finished in Chrome tones that pair easily with surrounding decor.
-Product Dimensions: 47-1/4"L x 23-1/2"W x 18-1/2"H
-Materials: Metal, Tempered Glass.
-Color: Chrome
-Weight: 72.16 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+RYLEE Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Metal, Tempered Glass, it is finished in Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47-1/4"L x 23-1/2"W x 18-1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 72.16 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -13941,12 +13941,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SINDAL Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Faux Marble, Engineered Wood construction is complemented by Black tones for a polished look.
-Product Dimensions: 36"W X 36"D X 18"H
-Materials: Faux Marble, Engineered Wood.
-Color: Black
-Weight: 90.52 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SINDAL Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Faux Marble, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 36"W X 36"D X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Faux Marble, Engineered Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 90.52 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -14063,12 +14063,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SINDAL Round Cocktail Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Faux Marble, Engineered Wood, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 36"W X 36"D X 18"H
-Materials: Faux Marble, Engineered Wood.
-Color: Black
-Weight: 117.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SINDAL Round Cocktail Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Faux Marble, Engineered Wood, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 36"W X 36"D X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Faux Marble, Engineered Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 117.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -14185,12 +14185,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SLOANE Coffee Table, styled in Contemporary and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Glass, Stainless Steel and White or Dark Gray or Chrome tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 17 3/4"H
-Materials: Glass, Stainless Steel.
-Color: White or Dark Gray or Chrome
-Weight: 102.52 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SLOANE Coffee Table, styled in Contemporary and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Glass, Stainless Steel and White or Dark Gray or Chrome tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 17 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Stainless Steel.&lt;br&gt;
+Color: White or Dark Gray or Chrome&lt;br&gt;
+Weight: 102.52 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -14308,12 +14308,12 @@
       </c>
       <c r="G108" s="46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with STATEN Coffee Table, styled in Contemporary and designed for everyday comfort. Built as a living coffee table, it pairs well with a wide range of interiors. With Tempered Glass, Metal, Engineered Wood and Glossy Black or Chrome tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 17 3/4"H
-Materials: Tempered Glass, Metal, Engineered Wood.
-Color: Glossy Black or Chrome
-Weight: 60.06 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with STATEN Coffee Table, styled in Contemporary and designed for everyday comfort. Built as a living coffee table, it pairs well with a wide range of interiors. With Tempered Glass, Metal, Engineered Wood and Glossy Black or Chrome tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 17 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Metal, Engineered Wood.&lt;br&gt;
+Color: Glossy Black or Chrome&lt;br&gt;
+Weight: 60.06 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H108" s="46" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="G109" s="46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-STATEN Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Tempered Glass, Metal, Engineered Wood, it is finished in Glossy White or Chrome tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 17 3/4"H
-Materials: Tempered Glass, Metal, Engineered Wood.
-Color: Glossy White or Chrome
-Weight: 60.06 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+STATEN Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Tempered Glass, Metal, Engineered Wood, it is finished in Glossy White or Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 17 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Metal, Engineered Wood.&lt;br&gt;
+Color: Glossy White or Chrome&lt;br&gt;
+Weight: 60.06 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H109" s="46" t="inlineStr">
@@ -14569,12 +14569,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SUNDANCE Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Metal, Mirror, Engineered Wood and Chrome tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 1/2"L X 23 1/2"W X 19"H
-Materials: Metal, Mirror, Engineered Wood.
-Color: Chrome
-Weight: 84 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SUNDANCE Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Metal, Mirror, Engineered Wood and Chrome tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 1/2"L X 23 1/2"W X 19"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Mirror, Engineered Wood.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 84 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SURDAL Oval Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Paper Veneer, Engineered Wood, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 50"W X 30"D X 18"H
-Materials: Paper Veneer, Engineered Wood.
-Color: Black
-Weight: 124 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SURDAL Oval Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Paper Veneer, Engineered Wood, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 50"W X 30"D X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 124 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -14817,12 +14817,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SURDAL Round Coffee Table and its Contemporary character. This living coffee table is made to fit naturally into the room. Finished in Black tones, the Paper Veneer, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 36"W X 36"D X 18"H
-Materials: Paper Veneer, Engineered Wood.
-Color: Black
-Weight: 118.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SURDAL Round Coffee Table and its Contemporary character. This living coffee table is made to fit naturally into the room. Finished in Black tones, the Paper Veneer, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 36"W X 36"D X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 118.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -14939,15 +14939,15 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with TADCASTER Coffee Table and its Traditional character. As a living coffee table, it is designed to complement your space. Finished in Dark Cherry tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 52"W X 30.5"D X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Cherry
-Weight: 61.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with TADCASTER Coffee Table and its Traditional character. As a living coffee table, it is designed to complement your space. Finished in Dark Cherry tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 52"W X 30.5"D X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Cherry&lt;br&gt;
+Weight: 61.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -15068,12 +15068,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TANIKA Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Metal, Tempered Glass construction is complemented by Chrome tones for a polished look.
-Product Dimensions: 48"W X 24"D X 18"H
-Materials: Metal, Tempered Glass.
-Color: Chrome
-Weight: 91 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TANIKA Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Metal, Tempered Glass construction is complemented by Chrome tones for a polished look.&lt;br&gt;
+Product Dimensions: 48"W X 24"D X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 91 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -15190,14 +15190,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-THISTED Rect Marble Coffee Table w/ Casters brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Marble, Solid Wood, Engineered Wood construction is complemented by White or Black tones for a polished look.
-Product Dimensions: 48"W X 26"D X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Marble, Solid Wood, Engineered Wood.
-Color: White or Black
-Weight: 110 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+THISTED Rect Marble Coffee Table w/ Casters brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Marble, Solid Wood, Engineered Wood construction is complemented by White or Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 48"W X 26"D X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Marble, Solid Wood, Engineered Wood.&lt;br&gt;
+Color: White or Black&lt;br&gt;
+Weight: 110 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -15318,14 +15318,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-THISTED Triangle Marble Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Marble, Solid Wood, Engineered Wood, it is finished in White or Black tones that pair easily with surrounding decor.
-Product Dimensions: 40"W X 40"D X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Marble, Solid Wood, Engineered Wood.
-Color: White or Black
-Weight: 94.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+THISTED Triangle Marble Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Marble, Solid Wood, Engineered Wood, it is finished in White or Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 40"W X 40"D X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Marble, Solid Wood, Engineered Wood.&lt;br&gt;
+Color: White or Black&lt;br&gt;
+Weight: 94.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -15446,12 +15446,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with TITUS Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Steel, Paper Veneer, and White or Chrome tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 1/2"L X 24"W X 19 1/4"H
-Materials: Steel, Paper Veneer.
-Color: White or Chrome
-Weight: 88.13 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with TITUS Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Steel, Paper Veneer, and White or Chrome tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 1/2"L X 24"W X 19 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Paper Veneer.&lt;br&gt;
+Color: White or Chrome&lt;br&gt;
+Weight: 88.13 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -15572,12 +15572,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with TORKEL Coffee Table, styled in Contemporary and designed for everyday comfort. Built as a living coffee table, it pairs well with a wide range of interiors. With Metal, Tempered Glass, and White or Chrome tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 1/4"L X 23 5/8"W X 15 3/4"H
-Materials: Metal, Tempered Glass.
-Color: White or Chrome
-Weight: 78.98 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with TORKEL Coffee Table, styled in Contemporary and designed for everyday comfort. Built as a living coffee table, it pairs well with a wide range of interiors. With Metal, Tempered Glass, and White or Chrome tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 15 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass.&lt;br&gt;
+Color: White or Chrome&lt;br&gt;
+Weight: 78.98 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -15698,12 +15698,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VALO Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Stainless Steel, Tempered Glass, it is finished in Satin Plated or Black tones that pair easily with surrounding decor.
-Product Dimensions: 48"L X 28"W X 20"H
-Materials: Stainless Steel, Tempered Glass.
-Color: Satin Plated or Black
-Weight: 50.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VALO Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Stainless Steel, Tempered Glass, it is finished in Satin Plated or Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"L X 28"W X 20"H&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Satin Plated or Black&lt;br&gt;
+Weight: 50.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -15820,14 +15820,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VILLARSGLANE Coffee Table brings a Glam look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Stainless Steel, Faux Marble construction is complemented by Chrome tones for a polished look.
-Product Dimensions: 51"L X 27 1/2"W X 18"H
-Features
-- Glam design
-Materials: Stainless Steel, Faux Marble.
-Color: Chrome
-Weight: 143.33 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VILLARSGLANE Coffee Table brings a Glam look to your home with a refined, comfortable feel. Built as a living coffee table, it pairs well with a wide range of interiors. The Stainless Steel, Faux Marble construction is complemented by Chrome tones for a polished look.&lt;br&gt;
+Product Dimensions: 51"L X 27 1/2"W X 18"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Faux Marble.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 143.33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -15944,12 +15944,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with VIRDEN Oval Cocktail Table, styled in Contemporary and designed for everyday comfort. Built as a living coffee table, it pairs well with a wide range of interiors. With Marble, Stainless Steel, Engineered Wood and Black or White or Gold tones, it blends structure and softness in one clean profile.
-Product Dimensions: 50"W X 26"D X 14"H
-Materials: Marble, Stainless Steel, Engineered Wood.
-Color: Black or White or Gold
-Weight: 132 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with VIRDEN Oval Cocktail Table, styled in Contemporary and designed for everyday comfort. Built as a living coffee table, it pairs well with a wide range of interiors. With Marble, Stainless Steel, Engineered Wood and Black or White or Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 50"W X 26"D X 14"H&lt;/p&gt;
+&lt;p&gt;Materials: Marble, Stainless Steel, Engineered Wood.&lt;br&gt;
+Color: Black or White or Gold&lt;br&gt;
+Weight: 132 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -16070,12 +16070,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VIRDEN Rectangle Cocktail Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Marble, Stainless Steel, Engineered Wood, it is finished in Black or White or Gold tones that pair easily with surrounding decor.
-Product Dimensions: 47.5"W X 24"D X 18"H
-Materials: Marble, Stainless Steel, Engineered Wood.
-Color: Black or White or Gold
-Weight: 162 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VIRDEN Rectangle Cocktail Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Marble, Stainless Steel, Engineered Wood, it is finished in Black or White or Gold tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47.5"W X 24"D X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Marble, Stainless Steel, Engineered Wood.&lt;br&gt;
+Color: Black or White or Gold&lt;br&gt;
+Weight: 162 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with VIRDEN Round Cocktail Table and its Contemporary character. This living coffee table is made to fit naturally into the room. Finished in Black or White or Gold tones, the Marble, Stainless Steel, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 35"W X 35"D X 14"H
-Materials: Marble, Stainless Steel, Engineered Wood.
-Color: Black or White or Gold
-Weight: 118 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with VIRDEN Round Cocktail Table and its Contemporary character. This living coffee table is made to fit naturally into the room. Finished in Black or White or Gold tones, the Marble, Stainless Steel, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 35"W X 35"D X 14"H&lt;/p&gt;
+&lt;p&gt;Materials: Marble, Stainless Steel, Engineered Wood.&lt;br&gt;
+Color: Black or White or Gold&lt;br&gt;
+Weight: 118 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -16322,12 +16322,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with VIRDEN Square Cocktail Table, styled in Contemporary and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Marble, Stainless Steel, Engineered Wood and Black or White or Gold tones, it blends structure and softness in one clean profile.
-Product Dimensions: 35"W X 35"D X 14"H
-Materials: Marble, Stainless Steel, Engineered Wood.
-Color: Black or White or Gold
-Weight: 154 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with VIRDEN Square Cocktail Table, styled in Contemporary and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Marble, Stainless Steel, Engineered Wood and Black or White or Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 35"W X 35"D X 14"H&lt;/p&gt;
+&lt;p&gt;Materials: Marble, Stainless Steel, Engineered Wood.&lt;br&gt;
+Color: Black or White or Gold&lt;br&gt;
+Weight: 154 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -16448,15 +16448,15 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with WALWORTH Coffee Table and its Traditional character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in Dark Oak tones, the Tempered Glass, Solid Wood build balances durability with visual appeal.
-Product Dimensions: 52"L X 30"W X 20 1/2"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Tempered Glass, Solid Wood.
-Color: Dark Oak
-Weight: 85.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with WALWORTH Coffee Table and its Traditional character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in Dark Oak tones, the Tempered Glass, Solid Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 52"L X 30"W X 20 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood.&lt;br&gt;
+Color: Dark Oak&lt;br&gt;
+Weight: 85.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -16577,11 +16577,11 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WESTERHAM Oval Cocktail Table adds a Modern touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Solid Rubberwood, Cherry Veneer, Poplar Burl Veneer, it is finished in Dark Cherry tones that pair easily with surrounding decor.
-Product Dimensions: 52"W X 28"D X 18"H Bonus storage &amp; convenience features (from matching set pieces): Felt-Lined Drawer and LED on End Table
-Materials: Solid Rubberwood, Cherry Veneer, Poplar Burl Veneer.
-Color: Dark Cherry</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WESTERHAM Oval Cocktail Table adds a Modern touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Solid Rubberwood, Cherry Veneer, Poplar Burl Veneer, it is finished in Dark Cherry tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 52"W X 28"D X 18"H Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-Lined Drawer and LED on End Table&lt;/p&gt;
+&lt;p&gt;Materials: Solid Rubberwood, Cherry Veneer, Poplar Burl Veneer.&lt;br&gt;
+Color: Dark Cherry&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -16699,14 +16699,14 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WETTINGEN Coffee Table adds a Glam touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Stainless Steel, Faux Marble, it is finished in Chrome tones that pair easily with surrounding decor.
-Product Dimensions: 51"L X 27 1/2"W X 18"H
-Features
-- Glam design
-Materials: Stainless Steel, Faux Marble.
-Color: Chrome
-Weight: 130.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WETTINGEN Coffee Table adds a Glam touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Stainless Steel, Faux Marble, it is finished in Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 51"L X 27 1/2"W X 18"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Faux Marble.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 130.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -16824,14 +16824,14 @@
       </c>
       <c r="G128" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with WETZIKON Coffee Table, styled in Glam and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Metal, Glass and Black or Silver tones, it blends structure and softness in one clean profile.
-Product Dimensions: 51"L X 27 1/2"W X 18"H
-Features
-- Glam design
-Materials: Metal, Glass.
-Color: Black or Silver
-Weight: 78.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with WETZIKON Coffee Table, styled in Glam and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Metal, Glass and Black or Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 51"L X 27 1/2"W X 18"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Glass.&lt;br&gt;
+Color: Black or Silver&lt;br&gt;
+Weight: 78.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H128" s="37" t="inlineStr">
@@ -16957,14 +16957,14 @@
       </c>
       <c r="G129" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WETZIKON Coffee Table adds a Glam touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Metal, Glass, it is finished in White or Silver tones that pair easily with surrounding decor.
-Product Dimensions: 51"L X 27 1/2"W X 18"H
-Features
-- Glam design
-Materials: Metal, Glass.
-Color: White or Silver
-Weight: 78.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WETZIKON Coffee Table adds a Glam touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Metal, Glass, it is finished in White or Silver tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 51"L X 27 1/2"W X 18"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Glass.&lt;br&gt;
+Color: White or Silver&lt;br&gt;
+Weight: 78.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H129" s="37" t="inlineStr">
@@ -17089,12 +17089,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-XANTHUS Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Steel, Glass, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 48"L X 24"W X 18"H
-Materials: Steel, Glass.
-Color: Black
-Weight: 54.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+XANTHUS Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Steel, Glass, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"L X 24"W X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Glass.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 54.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -17211,12 +17211,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZOLA Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Metal, Tempered Glass, it is finished in Chrome tones that pair easily with surrounding decor.
-Product Dimensions: 40"L X 40"W X 18"H
-Materials: Metal, Tempered Glass.
-Color: Chrome
-Weight: 56.32 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZOLA Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Metal, Tempered Glass, it is finished in Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 40"L X 40"W X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 56.32 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -17337,12 +17337,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALVISE End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living end table, it is designed to complement your space. Crafted from Steel, Glass, it is finished in Champagne tones that pair easily with surrounding decor.
-Product Dimensions: 24"DIA X 22"H
-Materials: Steel, Glass.
-Color: Champagne
-Weight: 25.08 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALVISE End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living end table, it is designed to complement your space. Crafted from Steel, Glass, it is finished in Champagne tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 24"DIA X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Glass.&lt;br&gt;
+Color: Champagne&lt;br&gt;
+Weight: 25.08 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -17459,14 +17459,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARLINGTON End Table brings a Rustic look to your home with a refined, comfortable feel. Built as a living end table, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Antique White tones for a polished look.
-Product Dimensions: 26"L X 19"W X 26"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Antique White
-Weight: 42.33 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARLINGTON End Table brings a Rustic look to your home with a refined, comfortable feel. Built as a living end table, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Antique White tones for a polished look.&lt;br&gt;
+Product Dimensions: 26"L X 19"W X 26"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Antique White&lt;br&gt;
+Weight: 42.33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -17587,14 +17587,14 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ATWOOD II End Table and its Contemporary character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Dark Walnut tones, the Tempered Glass, Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 26"DIA X 22 1/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Tempered Glass, Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 35.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ATWOOD II End Table and its Contemporary character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Dark Walnut tones, the Tempered Glass, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 26"DIA X 22 1/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 35.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -17711,14 +17711,14 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with AUGSBURG End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in Walnut or Gold tones, the Metal, Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 23"L X 23"W X 24"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Concealed Drawers
-Materials: Metal, Solid Wood, Wood Veneer.
-Color: Walnut or Gold
-Weight: 34.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with AUGSBURG End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in Walnut or Gold tones, the Metal, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 23"L X 23"W X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Walnut or Gold&lt;br&gt;
+Weight: 34.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -17839,14 +17839,14 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with BACERRA End Table and its Rustic character. This living end table is made to fit naturally into the room. Finished in Antique White or Gold tones, the Metal, Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 22"L X 26"W X 24"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Center Glide Drawers
-Materials: Metal, Solid Wood.
-Color: Antique White or Gold
-Weight: 77 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with BACERRA End Table and its Rustic character. This living end table is made to fit naturally into the room. Finished in Antique White or Gold tones, the Metal, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 22"L X 26"W X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Center Glide Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Solid Wood.&lt;br&gt;
+Color: Antique White or Gold&lt;br&gt;
+Weight: 77 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -17967,12 +17967,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BATAM II End Table, styled in Contemporary and designed for everyday comfort. This living end table is made to fit naturally into the room. With Metal, Tempered Glass, Paper Veneer, Engineered Wood and White or Natural Tone tones, it blends structure and softness in one clean profile.
-Product Dimensions: 22"L X 22"W X 22"H
-Materials: Metal, Tempered Glass, Paper Veneer, Engineered Wood.
-Color: White or Natural Tone
-Weight: 44.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BATAM II End Table, styled in Contemporary and designed for everyday comfort. This living end table is made to fit naturally into the room. With Metal, Tempered Glass, Paper Veneer, Engineered Wood and White or Natural Tone tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 22"L X 22"W X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: White or Natural Tone&lt;br&gt;
+Weight: 44.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -18089,12 +18089,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BIMA II End Table, styled in Contemporary and designed for everyday comfort. As a living end table, it is designed to complement your space. With Tempered Glass,Paper Veneer, and White or Natural Tone tones, it blends structure and softness in one clean profile.
-Product Dimensions: 20"L X 20"W X 22"H
-Materials: Tempered Glass,Paper Veneer.
-Color: White or Natural Tone
-Weight: 38.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BIMA II End Table, styled in Contemporary and designed for everyday comfort. As a living end table, it is designed to complement your space. With Tempered Glass,Paper Veneer, and White or Natural Tone tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 20"L X 20"W X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass,Paper Veneer.&lt;br&gt;
+Color: White or Natural Tone&lt;br&gt;
+Weight: 38.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -18215,12 +18215,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BISHOP End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living end table is made to fit naturally into the room. Crafted from Steel, Glass, it is finished in Black or Gray tones that pair easily with surrounding decor.
-Product Dimensions: 24"DIA X 23 "H
-Materials: Steel, Glass.
-Color: Black or Gray
-Weight: 31.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BISHOP End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living end table is made to fit naturally into the room. Crafted from Steel, Glass, it is finished in Black or Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 24"DIA X 23 "H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Glass.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 31.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -18337,14 +18337,14 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CALANDRA End Table, styled in Rustic and designed for everyday comfort. As a living end table, it is designed to complement your space. With Solid Wood, and Antique Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 24"L X 24"W X 24"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Antique Black
-Weight: 45.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CALANDRA End Table, styled in Rustic and designed for everyday comfort. As a living end table, it is designed to complement your space. With Solid Wood, and Antique Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 24"L X 24"W X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Antique Black&lt;br&gt;
+Weight: 45.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -18465,14 +18465,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CARRIE End Table, styled in Transitional and designed for everyday comfort. Built as a living end table, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Antique Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 22"DIA X 23 1/2"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Antique Black
-Weight: 33.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CARRIE End Table, styled in Transitional and designed for everyday comfort. Built as a living end table, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Antique Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 22"DIA X 23 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Antique Black&lt;br&gt;
+Weight: 33.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -18593,12 +18593,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CONISBROUGH Round End Table brings a Modern look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Modern construction is complemented by Modern tones for a polished look.
-Product Dimensions: 24"DIA X 24"H
-Materials: Modern.
-Color: Modern
-Weight: 184.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CONISBROUGH Round End Table brings a Modern look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Modern construction is complemented by Modern tones for a polished look.&lt;br&gt;
+Product Dimensions: 24"DIA X 24"H&lt;/p&gt;
+&lt;p&gt;Materials: Modern.&lt;br&gt;
+Color: Modern&lt;br&gt;
+Weight: 184.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -18724,15 +18724,15 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with COOKSHIRE End Table, styled in Traditional and designed for everyday comfort. As a living end table, it is designed to complement your space. With Solid Wood, Wood Veneer, and Rich Tobacco tones, it blends structure and softness in one clean profile.
-Product Dimensions: 26.5"W X 28.5"D X 24.5"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Rich Tobacco
-Weight: 47.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with COOKSHIRE End Table, styled in Traditional and designed for everyday comfort. As a living end table, it is designed to complement your space. With Solid Wood, Wood Veneer, and Rich Tobacco tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 26.5"W X 28.5"D X 24.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Rich Tobacco&lt;br&gt;
+Weight: 47.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -18853,14 +18853,14 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CORINNE End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in White or Distressed Dark Oak tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 22"L X 15 3/4"W X 22 1/8"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White or Distressed Dark Oak
-Weight: 51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CORINNE End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in White or Distressed Dark Oak tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 22"L X 15 3/4"W X 22 1/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Distressed Dark Oak&lt;br&gt;
+Weight: 51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -18981,14 +18981,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CRYSTAL FALLS End Table adds a Transitional touch while keeping the room feeling warm and welcoming. This living end table is made to fit naturally into the room. Crafted from Tempered Glass, Solid Wood, Wood Veneer, it is finished in Dark Cherry tones that pair easily with surrounding decor.
-Product Dimensions: 28"DIA X 25"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Tempered Glass, Solid Wood, Wood Veneer.
-Color: Dark Cherry
-Weight: 34 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CRYSTAL FALLS End Table adds a Transitional touch while keeping the room feeling warm and welcoming. This living end table is made to fit naturally into the room. Crafted from Tempered Glass, Solid Wood, Wood Veneer, it is finished in Dark Cherry tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 28"DIA X 25"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Cherry&lt;br&gt;
+Weight: 34 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -19110,12 +19110,12 @@
       </c>
       <c r="G146" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DUBENDORF End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Glass, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 22"L X 22"W X 23 5/8"H
-Materials: Glass.
-Color: Black
-Weight: 44 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DUBENDORF End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Glass, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 22"L X 22"W X 23 5/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H146" s="24" t="inlineStr">
@@ -19239,12 +19239,12 @@
       </c>
       <c r="G147" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with DUBENDORF End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in White tones, the Glass, build balances durability with visual appeal.
-Product Dimensions: 22"L X 22"W X 23 5/8"H
-Materials: Glass.
-Color: White
-Weight: 44 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with DUBENDORF End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in White tones, the Glass, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 22"L X 22"W X 23 5/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H147" s="24" t="inlineStr">
@@ -19367,12 +19367,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with EIMEAR End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in White or Black tones, the Metal, build balances durability with visual appeal.
-Product Dimensions: 22"L X 22"W X 24"H
-Materials: Metal.
-Color: White or Black
-Weight: 37 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with EIMEAR End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in White or Black tones, the Metal, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 22"L X 22"W X 24"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: White or Black&lt;br&gt;
+Weight: 37 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -19493,14 +19493,14 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with FINLEY End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in Espresso tones, the Glass, Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 28"L X 24"W X 24"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Glass, Solid Wood.
-Color: Espresso
-Weight: 29.04 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with FINLEY End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in Espresso tones, the Glass, Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 28"L X 24"W X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Solid Wood.&lt;br&gt;
+Color: Espresso&lt;br&gt;
+Weight: 29.04 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -19621,14 +19621,14 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with GIORDANI End Table, styled in Traditional and designed for everyday comfort. Built as a living end table, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Weathered Oak tones, it blends structure and softness in one clean profile.
-Product Dimensions: 27"W X 27"D X 25"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Weathered Oak
-Weight: 50.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with GIORDANI End Table, styled in Traditional and designed for everyday comfort. Built as a living end table, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Weathered Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 27"W X 27"D X 25"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Weathered Oak&lt;br&gt;
+Weight: 50.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -19754,14 +19754,14 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GRANVIA End Table brings a Transitional look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Tempered Glass, Solid Wood, Wood Veneer, construction is complemented by Dark Cherry tones for a polished look.
-Product Dimensions: 25"DIA X 24"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Tempered Glass, Solid Wood, Wood Veneer.
-Color: Dark Cherry
-Weight: 30.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GRANVIA End Table brings a Transitional look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Tempered Glass, Solid Wood, Wood Veneer, construction is complemented by Dark Cherry tones for a polished look.&lt;br&gt;
+Product Dimensions: 25"DIA X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Cherry&lt;br&gt;
+Weight: 30.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -19882,12 +19882,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with GRASTEN Square End Table and its Modern Contemporary character. This living end table is made to fit naturally into the room. Finished in Ash Gray tones, the Rubberwood, Oak Veneer, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 22"W X 22"D X 24.5"H
-Materials: Rubberwood, Oak Veneer, Engineered Wood.
-Color: Ash Gray
-Weight: 72.16 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with GRASTEN Square End Table and its Modern Contemporary character. This living end table is made to fit naturally into the room. Finished in Ash Gray tones, the Rubberwood, Oak Veneer, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 22"W X 22"D X 24.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
+Color: Ash Gray&lt;br&gt;
+Weight: 72.16 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -20013,15 +20013,15 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with HALCASTER End Table and its Traditional character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Java tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 26"W X 27.5"D X 23.5"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Java
-Weight: 51.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with HALCASTER End Table and its Traditional character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Java tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 26"W X 27.5"D X 23.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Java&lt;br&gt;
+Weight: 51.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -20143,12 +20143,12 @@
       </c>
       <c r="G154" s="48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HALEWOOD End Table brings a Contemporary look to your home with a refined, comfortable feel. This living end table is made to fit naturally into the room. The Rubberwood, Oak Veneer, Engineered Wood construction is complemented by Black tones for a polished look.
-Product Dimensions: 20"DIA X 21"H
-Materials: Rubberwood, Oak Veneer, Engineered Wood.
-Color: Black
-Weight: 28.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HALEWOOD End Table brings a Contemporary look to your home with a refined, comfortable feel. This living end table is made to fit naturally into the room. The Rubberwood, Oak Veneer, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 20"DIA X 21"H&lt;/p&gt;
+&lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 28.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H154" s="48" t="inlineStr">
@@ -20274,12 +20274,12 @@
       </c>
       <c r="G155" s="48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with HALEWOOD End Table, styled in Contemporary and designed for everyday comfort. Built as a living end table, it pairs well with a wide range of interiors. With Rubberwood, Oak Veneer, Engineered Wood and Oak tones, it blends structure and softness in one clean profile.
-Product Dimensions: 20"DIA X 21"H
-Materials: Rubberwood, Oak Veneer, Engineered Wood.
-Color: Oak
-Weight: 26.66 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with HALEWOOD End Table, styled in Contemporary and designed for everyday comfort. Built as a living end table, it pairs well with a wide range of interiors. With Rubberwood, Oak Veneer, Engineered Wood and Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 20"DIA X 21"H&lt;/p&gt;
+&lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
+Color: Oak&lt;br&gt;
+Weight: 26.66 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H155" s="48" t="inlineStr">
@@ -20400,12 +20400,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with IZAR End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in White or Gun Metal tones, the Metal, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 22"L X 22"W X 21 3/4"H
-Materials: Metal, Engineered Wood.
-Color: White or Gun Metal
-Weight: 25 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with IZAR End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in White or Gun Metal tones, the Metal, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 22"L X 22"W X 21 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Engineered Wood.&lt;br&gt;
+Color: White or Gun Metal&lt;br&gt;
+Weight: 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with JOLIET End Table and its Transitional character. This living end table is made to fit naturally into the room. Finished in Antique White tones, the Solid Wood, Wood Veneer, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 24"L X 22"W X 24"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Felt-lined Drawers
-Materials: Solid Wood, Wood Veneer, Engineered Wood.
-Color: Antique White
-Weight: 37.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with JOLIET End Table and its Transitional character. This living end table is made to fit naturally into the room. Finished in Antique White tones, the Solid Wood, Wood Veneer, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 24"L X 22"W X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-lined Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
+Color: Antique White&lt;br&gt;
+Weight: 37.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -20651,14 +20651,14 @@
       </c>
       <c r="G158" s="50" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with KOBLENZ End Table and its Glam character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Light Teal tones, the Metal, build balances durability with visual appeal.
-Product Dimensions: 23"DIA X 24"H
-Features
-- Glam design Bonus storage &amp; convenience features (from matching set pieces): Concealed Drawer
-Materials: Metal.
-Color: Light Teal
-Weight: 41.14 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with KOBLENZ End Table and its Glam character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Light Teal tones, the Metal, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 23"DIA X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Light Teal&lt;br&gt;
+Weight: 41.14 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H158" s="50" t="inlineStr">
@@ -20782,14 +20782,14 @@
       </c>
       <c r="G159" s="50" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KOBLENZ End Table brings a Glam look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Metal, construction is complemented by Dark Walnut tones for a polished look.
-Product Dimensions: 23"DIA X 24"H
-Features
-- Glam design Bonus storage &amp; convenience features (from matching set pieces): Concealed Drawer
-Materials: Metal.
-Color: Dark Walnut
-Weight: 41.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KOBLENZ End Table brings a Glam look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Metal, construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
+Product Dimensions: 23"DIA X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 41.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H159" s="50" t="inlineStr">
@@ -20912,12 +20912,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with LAILA End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in Chrome tones, the Glass, Metal build balances durability with visual appeal.
-Product Dimensions: 21 5/8"DIA X 21 5/8"H
-Materials: Glass, Metal.
-Color: Chrome
-Weight: 22.44 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with LAILA End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in Chrome tones, the Glass, Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 21 5/8"DIA X 21 5/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 22.44 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -21034,12 +21034,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LOBB End Table adds a Industrial touch while keeping the room feeling warm and welcoming. This living end table is made to fit naturally into the room. Crafted from Steel, Paper Veneer, it is finished in Natural Tone or Black tones that pair easily with surrounding decor.
-Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H
-Materials: Steel, Paper Veneer.
-Color: Natural Tone or Black
-Weight: 32.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LOBB End Table adds a Industrial touch while keeping the room feeling warm and welcoming. This living end table is made to fit naturally into the room. Crafted from Steel, Paper Veneer, it is finished in Natural Tone or Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Paper Veneer.&lt;br&gt;
+Color: Natural Tone or Black&lt;br&gt;
+Weight: 32.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -21165,12 +21165,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with LODIA End Table, styled in Contemporary and designed for everyday comfort. This living end table is made to fit naturally into the room. With Tempered Glass, Paper Veneer, Engineered Wood and Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 23 1/2"L X 23 1/2"W X 21 7/8"H
-Materials: Tempered Glass, Paper Veneer, Engineered Wood.
-Color: Gray
-Weight: 44.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with LODIA End Table, styled in Contemporary and designed for everyday comfort. This living end table is made to fit naturally into the room. With Tempered Glass, Paper Veneer, Engineered Wood and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 23 1/2"L X 23 1/2"W X 21 7/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 44.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -21288,12 +21288,12 @@
       </c>
       <c r="G163" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LODIA III End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Tempered Glass, Paper Veneer, Engineered Wood, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 23 5/8"DIA X 22"H
-Materials: Tempered Glass, Paper Veneer, Engineered Wood.
-Color: Black
-Weight: 47.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LODIA III End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Tempered Glass, Paper Veneer, Engineered Wood, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 23 5/8"DIA X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 47.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H163" s="52" t="inlineStr">
@@ -21415,12 +21415,12 @@
       </c>
       <c r="G164" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with LODIA III End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in White tones, the Tempered Glass, Paper Veneer, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 23 5/8"DIA X 22"H
-Materials: Tempered Glass, Paper Veneer, Engineered Wood.
-Color: White
-Weight: 47.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with LODIA III End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in White tones, the Tempered Glass, Paper Veneer, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 23 5/8"DIA X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 47.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H164" s="52" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with LUDVIG End Table and its Contemporary character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Chrome or Clear tones, the Metal, Tempered Glass, build balances durability with visual appeal.
-Product Dimensions: 24"L X 24"W X 24"H
-Materials: Metal, Tempered Glass.
-Color: Chrome or Clear
-Weight: 36.96 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with LUDVIG End Table and its Contemporary character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Chrome or Clear tones, the Metal, Tempered Glass, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 24"L X 24"W X 24"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass.&lt;br&gt;
+Color: Chrome or Clear&lt;br&gt;
+Weight: 36.96 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -21667,14 +21667,14 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MAJKEN End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in White or Natural Tone tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 22"L X 22"W X 23 5/8"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White or Natural Tone
-Weight: 51.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MAJKEN End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in White or Natural Tone tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 22"L X 22"W X 23 5/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Natural Tone&lt;br&gt;
+Weight: 51.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -21796,12 +21796,12 @@
       </c>
       <c r="G167" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MANNEDORF End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in Black or Dark Walnut tones, the Tempered Glass,Paper Veneer, build balances durability with visual appeal.
-Product Dimensions: 22"L X 22"W X 24 3/8"H
-Materials: Tempered Glass,Paper Veneer.
-Color: Black or Dark Walnut
-Weight: 57 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MANNEDORF End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in Black or Dark Walnut tones, the Tempered Glass,Paper Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 22"L X 22"W X 24 3/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass,Paper Veneer.&lt;br&gt;
+Color: Black or Dark Walnut&lt;br&gt;
+Weight: 57 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H167" s="24" t="inlineStr">
@@ -21925,12 +21925,12 @@
       </c>
       <c r="G168" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MANNEDORF End Table brings a Contemporary look to your home with a refined, comfortable feel. This living end table is made to fit naturally into the room. The Tempered Glass,Paper Veneer, construction is complemented by Black or White tones for a polished look.
-Product Dimensions: 22"L X 22"W X 24 3/8"H
-Materials: Tempered Glass,Paper Veneer.
-Color: Black or White
-Weight: 47.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MANNEDORF End Table brings a Contemporary look to your home with a refined, comfortable feel. This living end table is made to fit naturally into the room. The Tempered Glass,Paper Veneer, construction is complemented by Black or White tones for a polished look.&lt;br&gt;
+Product Dimensions: 22"L X 22"W X 24 3/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass,Paper Veneer.&lt;br&gt;
+Color: Black or White&lt;br&gt;
+Weight: 47.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H168" s="24" t="inlineStr">
@@ -22054,15 +22054,15 @@
       </c>
       <c r="G169" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARSTON End Table adds a Traditional touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Dark Walnut tones that pair easily with surrounding decor.
-Product Dimensions: 27.5"W X 26"D X 23.5"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 67.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARSTON End Table adds a Traditional touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 27.5"W X 26"D X 23.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 67.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H169" s="54" t="inlineStr">
@@ -22186,15 +22186,15 @@
       </c>
       <c r="G170" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MARSTON End Table and its Traditional character. As a living end table, it is designed to complement your space. Finished in Champagne tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 27.5"W X 26"D X 23.5"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Champagne
-Weight: 48.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MARSTON End Table and its Traditional character. As a living end table, it is designed to complement your space. Finished in Champagne tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 27.5"W X 26"D X 23.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Champagne&lt;br&gt;
+Weight: 48.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H170" s="54" t="inlineStr">
@@ -22317,12 +22317,12 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MAY End Table brings a Traditional look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Glass, Metal, Wood construction is complemented by Brown Cherry tones for a polished look.
-Product Dimensions: 28"L X 28"W X 26 1/2"H
-Materials: Glass, Metal, Wood.
-Color: Brown Cherry
-Weight: 35.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MAY End Table brings a Traditional look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Glass, Metal, Wood construction is complemented by Brown Cherry tones for a polished look.&lt;br&gt;
+Product Dimensions: 28"L X 28"W X 26 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Wood.&lt;br&gt;
+Color: Brown Cherry&lt;br&gt;
+Weight: 35.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -22443,12 +22443,12 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MEDA End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in White or Chrome tones, the Lacquer, Metal, build balances durability with visual appeal.
-Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H
-Materials: Lacquer, Metal.
-Color: White or Chrome
-Weight: 34.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MEDA End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in White or Chrome tones, the Lacquer, Metal, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal.&lt;br&gt;
+Color: White or Chrome&lt;br&gt;
+Weight: 34.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -22570,14 +22570,14 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MOA End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in White or Natural Tone tones, the Solid Wood, build balances durability with visual appeal.
-Product Dimensions: 22"L X 22"W X 23 5/8"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White or Natural Tone
-Weight: 59.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MOA End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in White or Natural Tone tones, the Solid Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 22"L X 22"W X 23 5/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Natural Tone&lt;br&gt;
+Weight: 59.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -22699,12 +22699,12 @@
       </c>
       <c r="G174" s="48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NAHARA End Table brings a Contemporary look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Glass, construction is complemented by Black tones for a polished look.
-Product Dimensions: 22"DIA X 23 3/8"H
-Materials: Glass.
-Color: Black
-Weight: 53.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NAHARA End Table brings a Contemporary look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Glass, construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 22"DIA X 23 3/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 53.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H174" s="48" t="inlineStr">
@@ -22826,12 +22826,12 @@
       </c>
       <c r="G175" s="48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with NAHARA End Table, styled in Contemporary and designed for everyday comfort. This living end table is made to fit naturally into the room. With Glass, and Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 22"DIA X 23 3/8"H
-Materials: Glass.
-Color: Gray
-Weight: 53.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with NAHARA End Table, styled in Contemporary and designed for everyday comfort. This living end table is made to fit naturally into the room. With Glass, and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 22"DIA X 23 3/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 53.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H175" s="48" t="inlineStr">
@@ -22953,12 +22953,12 @@
       </c>
       <c r="G176" s="48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NAHARA End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Glass, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: 22"DIA X 23 3/8"H
-Materials: Glass.
-Color: White
-Weight: 53.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NAHARA End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Glass, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 22"DIA X 23 3/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 53.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H176" s="48" t="inlineStr">
@@ -23080,12 +23080,12 @@
       </c>
       <c r="G177" s="50" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NINOVE End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living end table, it is designed to complement your space. Crafted from Lacquer, Metal, Wood, it is finished in Black or Chrome tones that pair easily with surrounding decor.
-Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H
-Materials: Lacquer, Metal, Wood.
-Color: Black or Chrome
-Weight: 53.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NINOVE End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living end table, it is designed to complement your space. Crafted from Lacquer, Metal, Wood, it is finished in Black or Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Wood.&lt;br&gt;
+Color: Black or Chrome&lt;br&gt;
+Weight: 53.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H177" s="50" t="inlineStr">
@@ -23209,12 +23209,12 @@
       </c>
       <c r="G178" s="50" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with NINOVE End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in White or Chrome tones, the Lacquer, Metal, Wood, build balances durability with visual appeal.
-Product Dimensions: 23 1/2"L X 23 1/2"W X 22"H
-Materials: Lacquer, Metal, Wood.
-Color: White or Chrome
-Weight: 53.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with NINOVE End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in White or Chrome tones, the Lacquer, Metal, Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 23 1/2"L X 23 1/2"W X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Wood.&lt;br&gt;
+Color: White or Chrome&lt;br&gt;
+Weight: 53.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H178" s="50" t="inlineStr">
@@ -23337,12 +23337,12 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with NORTHWICH End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in Black or Gray or Matte Gold tones, the Sintered Stone, Stainless Steel build balances durability with visual appeal.
-Product Dimensions: 31.5"W X 23.5"D X 19.5"H
-Materials: Sintered Stone, Stainless Steel.
-Color: Black or Gray or Matte Gold
-Weight: 82 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with NORTHWICH End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in Black or Gray or Matte Gold tones, the Sintered Stone, Stainless Steel build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 31.5"W X 23.5"D X 19.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Sintered Stone, Stainless Steel.&lt;br&gt;
+Color: Black or Gray or Matte Gold&lt;br&gt;
+Weight: 82 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -23459,12 +23459,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with NOVA End Table, styled in Contemporary and designed for everyday comfort. This living end table is made to fit naturally into the room. With Stainless Steel, Tempered Glass, and Satin Plated or Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 26"DIA X 22 1/2"H
-Materials: Stainless Steel, Tempered Glass.
-Color: Satin Plated or Black
-Weight: 40.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with NOVA End Table, styled in Contemporary and designed for everyday comfort. This living end table is made to fit naturally into the room. With Stainless Steel, Tempered Glass, and Satin Plated or Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 26"DIA X 22 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Satin Plated or Black&lt;br&gt;
+Weight: 40.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -23581,14 +23581,14 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with OAKWAY End Table, styled in Traditional and designed for everyday comfort. Built as a living end table, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Weathered Oak tones, it blends structure and softness in one clean profile.
-Product Dimensions: 26"W X 26"D X 24"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Weathered Oak
-Weight: 60.84 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with OAKWAY End Table, styled in Traditional and designed for everyday comfort. Built as a living end table, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Weathered Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 26"W X 26"D X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Weathered Oak&lt;br&gt;
+Weight: 60.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -23709,12 +23709,12 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ORLA II End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in Satin Plated or Black tones, the Stainless Steel, Tempered Glass, build balances durability with visual appeal.
-Product Dimensions: 24"L X 24"W X 23"H
-Materials: Stainless Steel, Tempered Glass.
-Color: Satin Plated or Black
-Weight: 39.25 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ORLA II End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in Satin Plated or Black tones, the Stainless Steel, Tempered Glass, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 24"L X 24"W X 23"H&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Satin Plated or Black&lt;br&gt;
+Weight: 39.25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -23831,12 +23831,12 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ORRIN End Table adds a Industrial touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Steel, Paper Veneer, it is finished in Gray or Walnut tones that pair easily with surrounding decor.
-Product Dimensions: 24"DIA X 24"H
-Materials: Steel, Paper Veneer.
-Color: Gray or Walnut
-Weight: 23.84 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ORRIN End Table adds a Industrial touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Steel, Paper Veneer, it is finished in Gray or Walnut tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 24"DIA X 24"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Paper Veneer.&lt;br&gt;
+Color: Gray or Walnut&lt;br&gt;
+Weight: 23.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -23962,12 +23962,12 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with POLTIMORE Round End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in Oak tones, the Rubberwood, Oak Veneer, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 20"DIA X 18"H
-Materials: Rubberwood, Oak Veneer, Engineered Wood.
-Color: Oak
-Weight: 30.32 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with POLTIMORE Round End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in Oak tones, the Rubberwood, Oak Veneer, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 20"DIA X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
+Color: Oak&lt;br&gt;
+Weight: 30.32 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -24088,12 +24088,12 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with RAYA End Table and its Contemporary character. Built as a living end table, it pairs well with a wide range of interiors. Finished in White tones, the Tempered Glass, Wood, build balances durability with visual appeal.
-Product Dimensions: 23 1/4"L X 20"W X 22 1/2"H
-Materials: Tempered Glass, Wood.
-Color: White
-Weight: 60 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with RAYA End Table and its Contemporary character. Built as a living end table, it pairs well with a wide range of interiors. Finished in White tones, the Tempered Glass, Wood, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 23 1/4"L X 20"W X 22 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 60 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -24215,15 +24215,15 @@
       </c>
       <c r="G186" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ROCHESTER End Table and its Traditional character. As a living end table, it is designed to complement your space. Finished in Champagne tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 26.5"W X 28.5"D X 24.5"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Champagne
-Weight: 61.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ROCHESTER End Table and its Traditional character. As a living end table, it is designed to complement your space. Finished in Champagne tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 26.5"W X 28.5"D X 24.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Champagne&lt;br&gt;
+Weight: 61.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H186" s="35" t="inlineStr">
@@ -24351,15 +24351,15 @@
       </c>
       <c r="G187" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ROCHESTER End Table brings a Traditional look to your home with a refined, comfortable feel. This living end table is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Champagne tones for a polished look.
-Product Dimensions: 26.5"W X 28.5"D X 24.5"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Champagne
-Weight: 50 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ROCHESTER End Table brings a Traditional look to your home with a refined, comfortable feel. This living end table is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Champagne tones for a polished look.&lt;br&gt;
+Product Dimensions: 26.5"W X 28.5"D X 24.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Champagne&lt;br&gt;
+Weight: 50 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H187" s="35" t="inlineStr">
@@ -24482,14 +24482,14 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ROSETTA End Table adds a Transitional touch while keeping the room feeling warm and welcoming. This living end table is made to fit naturally into the room. Crafted from Faux Marble, Solid Wood, Wood Veneer, it is finished in Dark Walnut tones that pair easily with surrounding decor.
-Product Dimensions: 22"L X 22"W X 24 1/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Faux Marble, Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 54.12 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ROSETTA End Table adds a Transitional touch while keeping the room feeling warm and welcoming. This living end table is made to fit naturally into the room. Crafted from Faux Marble, Solid Wood, Wood Veneer, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 22"L X 22"W X 24 1/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Faux Marble, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 54.12 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -24610,12 +24610,12 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ROXO End Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living end table, it pairs well with a wide range of interiors. The Stainless Steel, Tempered Glass, construction is complemented by Satin Plated or Black tones for a polished look.
-Product Dimensions: 24"L X 22"W X 23 1/2"H
-Materials: Stainless Steel, Tempered Glass.
-Color: Satin Plated or Black
-Weight: 34.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ROXO End Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living end table, it pairs well with a wide range of interiors. The Stainless Steel, Tempered Glass, construction is complemented by Satin Plated or Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 24"L X 22"W X 23 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Satin Plated or Black&lt;br&gt;
+Weight: 34.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -24732,12 +24732,12 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with RYLEE End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in Chrome tones, the Metal, Tempered Glass, build balances durability with visual appeal.
-Product Dimensions: 23 1/2"L X 23 1/2"W X 22 1/2"H
-Materials: Metal, Tempered Glass.
-Color: Chrome
-Weight: 46.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with RYLEE End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in Chrome tones, the Metal, Tempered Glass, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 23 1/2"L X 23 1/2"W X 22 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 46.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SINDAL End Table, styled in Contemporary and designed for everyday comfort. As a living end table, it is designed to complement your space. With Faux Marble, Engineered Wood and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 22"W X 22"D X 22"H
-Materials: Faux Marble, Engineered Wood.
-Color: Black
-Weight: 53.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SINDAL End Table, styled in Contemporary and designed for everyday comfort. As a living end table, it is designed to complement your space. With Faux Marble, Engineered Wood and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 22"W X 22"D X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Faux Marble, Engineered Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 53.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -24980,12 +24980,12 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SINDAL Round End Table and its Contemporary character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Black tones, the Faux Marble, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 22"W X 22"D X 22"H
-Materials: Faux Marble, Engineered Wood.
-Color: Black
-Weight: 35.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SINDAL Round End Table and its Contemporary character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Black tones, the Faux Marble, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 22"W X 22"D X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Faux Marble, Engineered Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 35.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -25102,12 +25102,12 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SLOANE End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living end table is made to fit naturally into the room. Crafted from Glass, Stainless Steel, it is finished in White or Dark Gray or Chrome tones that pair easily with surrounding decor.
-Product Dimensions: 23 5/8"L X 23 5/8"W X 21 5/8"H
-Materials: Glass, Stainless Steel.
-Color: White or Dark Gray or Chrome
-Weight: 67.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SLOANE End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living end table is made to fit naturally into the room. Crafted from Glass, Stainless Steel, it is finished in White or Dark Gray or Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 23 5/8"L X 23 5/8"W X 21 5/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Stainless Steel.&lt;br&gt;
+Color: White or Dark Gray or Chrome&lt;br&gt;
+Weight: 67.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -25225,12 +25225,12 @@
       </c>
       <c r="G194" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with STATEN End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in Glossy Black or Chrome tones, the Tempered Glass, Metal, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H
-Materials: Tempered Glass, Metal, Engineered Wood.
-Color: Glossy Black or Chrome
-Weight: 43.56 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with STATEN End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in Glossy Black or Chrome tones, the Tempered Glass, Metal, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Metal, Engineered Wood.&lt;br&gt;
+Color: Glossy Black or Chrome&lt;br&gt;
+Weight: 43.56 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H194" s="33" t="inlineStr">
@@ -25356,12 +25356,12 @@
       </c>
       <c r="G195" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-STATEN End Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living end table, it pairs well with a wide range of interiors. The Tempered Glass, Metal, Engineered Wood construction is complemented by Glossy White or Chrome tones for a polished look.
-Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H
-Materials: Tempered Glass, Metal, Engineered Wood.
-Color: Glossy White or Chrome
-Weight: 43.56 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+STATEN End Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living end table, it pairs well with a wide range of interiors. The Tempered Glass, Metal, Engineered Wood construction is complemented by Glossy White or Chrome tones for a polished look.&lt;br&gt;
+Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Metal, Engineered Wood.&lt;br&gt;
+Color: Glossy White or Chrome&lt;br&gt;
+Weight: 43.56 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H195" s="33" t="inlineStr">
@@ -25486,12 +25486,12 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SUNDANCE End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Metal, Mirror, it is finished in Chrome tones that pair easily with surrounding decor.
-Product Dimensions: 23 1/2"L X 23 1/2"W X 23 1/2"H
-Materials: Metal, Mirror.
-Color: Chrome
-Weight: 48.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SUNDANCE End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Metal, Mirror, it is finished in Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 23 1/2"L X 23 1/2"W X 23 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Mirror.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 48.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -25612,12 +25612,12 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SURDAL End Table, styled in Contemporary and designed for everyday comfort. Built as a living end table, it pairs well with a wide range of interiors. With Paper Veneer, Engineered Wood and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 22"W X 22"D X 22"H
-Materials: Paper Veneer, Engineered Wood.
-Color: Black
-Weight: 37.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SURDAL End Table, styled in Contemporary and designed for everyday comfort. Built as a living end table, it pairs well with a wide range of interiors. With Paper Veneer, Engineered Wood and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 22"W X 22"D X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 37.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -25734,15 +25734,15 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TADCASTER End Table brings a Traditional look to your home with a refined, comfortable feel. This living end table is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Dark Cherry tones for a polished look.
-Product Dimensions: 28.5"W X 26.5"D X 24.5"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Cherry
-Weight: 48.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TADCASTER End Table brings a Traditional look to your home with a refined, comfortable feel. This living end table is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Dark Cherry tones for a polished look.&lt;br&gt;
+Product Dimensions: 28.5"W X 26.5"D X 24.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Cherry&lt;br&gt;
+Weight: 48.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -25863,12 +25863,12 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with TANIKA End Table, styled in Contemporary and designed for everyday comfort. As a living end table, it is designed to complement your space. With Metal, Tempered Glass and Chrome tones, it blends structure and softness in one clean profile.
-Product Dimensions: 22"W X 22"D X 22"H
-Materials: Metal, Tempered Glass.
-Color: Chrome
-Weight: 43.04 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with TANIKA End Table, styled in Contemporary and designed for everyday comfort. As a living end table, it is designed to complement your space. With Metal, Tempered Glass and Chrome tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 22"W X 22"D X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 43.04 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -25985,14 +25985,14 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with THISTED Square Marble End Table, styled in Contemporary and designed for everyday comfort. This living end table is made to fit naturally into the room. With Marble, Solid Wood, Engineered Wood and White or Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 22"W X 22"D X 24"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Marble, Solid Wood, Engineered Wood.
-Color: White or Black
-Weight: 46.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with THISTED Square Marble End Table, styled in Contemporary and designed for everyday comfort. This living end table is made to fit naturally into the room. With Marble, Solid Wood, Engineered Wood and White or Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 22"W X 22"D X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Marble, Solid Wood, Engineered Wood.&lt;br&gt;
+Color: White or Black&lt;br&gt;
+Weight: 46.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -26113,12 +26113,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TITUS End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Steel, Paper Veneer, it is finished in White or Chrome tones that pair easily with surrounding decor.
-Product Dimensions: 26"L X 23 1/2"W X 23 3/4"H
-Materials: Steel, Paper Veneer.
-Color: White or Chrome
-Weight: 38.06 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TITUS End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Steel, Paper Veneer, it is finished in White or Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 26"L X 23 1/2"W X 23 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Paper Veneer.&lt;br&gt;
+Color: White or Chrome&lt;br&gt;
+Weight: 38.06 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -26239,12 +26239,12 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TORKEL End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living end table, it is designed to complement your space. Crafted from Metal, Tempered Glass, it is finished in White or Chrome tones that pair easily with surrounding decor.
-Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H
-Materials: Metal, Tempered Glass.
-Color: White or Chrome
-Weight: 62.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TORKEL End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living end table, it is designed to complement your space. Crafted from Metal, Tempered Glass, it is finished in White or Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass.&lt;br&gt;
+Color: White or Chrome&lt;br&gt;
+Weight: 62.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -26365,12 +26365,12 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with VALO End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in Satin Plated or Black tones, the Stainless Steel, Tempered Glass, build balances durability with visual appeal.
-Product Dimensions: 22"DIA X 22 3/8"H
-Materials: Stainless Steel, Tempered Glass.
-Color: Satin Plated or Black
-Weight: 24.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with VALO End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in Satin Plated or Black tones, the Stainless Steel, Tempered Glass, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 22"DIA X 22 3/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Satin Plated or Black&lt;br&gt;
+Weight: 24.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -26487,14 +26487,14 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with VILLARSGLANE End Table, styled in Glam and designed for everyday comfort. As a living end table, it is designed to complement your space. With Stainless Steel, Faux Marble and Chrome tones, it blends structure and softness in one clean profile.
-Product Dimensions: 23 1/2"L X 23 1/2"W X 23"H
-Features
-- Glam design
-Materials: Stainless Steel, Faux Marble.
-Color: Chrome
-Weight: 74.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with VILLARSGLANE End Table, styled in Glam and designed for everyday comfort. As a living end table, it is designed to complement your space. With Stainless Steel, Faux Marble and Chrome tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 23 1/2"L X 23 1/2"W X 23"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Faux Marble.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 74.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -26611,12 +26611,12 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VIRDEN Round End Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living end table, it pairs well with a wide range of interiors. The Marble, Stainless Steel, Engineered Wood construction is complemented by Black or White or Gold tones for a polished look.
-Product Dimensions: 19.5"W X 19.5"D X 19.5"H
-Materials: Marble, Stainless Steel, Engineered Wood.
-Color: Black or White or Gold
-Weight: 55 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VIRDEN Round End Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living end table, it pairs well with a wide range of interiors. The Marble, Stainless Steel, Engineered Wood construction is complemented by Black or White or Gold tones for a polished look.&lt;br&gt;
+Product Dimensions: 19.5"W X 19.5"D X 19.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Marble, Stainless Steel, Engineered Wood.&lt;br&gt;
+Color: Black or White or Gold&lt;br&gt;
+Weight: 55 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -26737,12 +26737,12 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VIRDEN Square End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living end table is made to fit naturally into the room. Crafted from Marble, Stainless Steel, Engineered Wood, it is finished in Black or White or Gold tones that pair easily with surrounding decor.
-Product Dimensions: 19.5"W X 19.5"D X 19.5"H
-Materials: Marble, Stainless Steel, Engineered Wood.
-Color: Black or White or Gold
-Weight: 66 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VIRDEN Square End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living end table is made to fit naturally into the room. Crafted from Marble, Stainless Steel, Engineered Wood, it is finished in Black or White or Gold tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 19.5"W X 19.5"D X 19.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Marble, Stainless Steel, Engineered Wood.&lt;br&gt;
+Color: Black or White or Gold&lt;br&gt;
+Weight: 66 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -26863,15 +26863,15 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WALWORTH End Table brings a Traditional look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Tempered Glass, Solid Wood construction is complemented by Dark Oak tones for a polished look.
-Product Dimensions: 26"L X 24"W X 24 3/8"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Tempered Glass, Solid Wood.
-Color: Dark Oak
-Weight: 51.26 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WALWORTH End Table brings a Traditional look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Tempered Glass, Solid Wood construction is complemented by Dark Oak tones for a polished look.&lt;br&gt;
+Product Dimensions: 26"L X 24"W X 24 3/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood.&lt;br&gt;
+Color: Dark Oak&lt;br&gt;
+Weight: 51.26 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -26992,11 +26992,11 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WESTERHAM End Table w/ LED adds a Modern touch while keeping the room feeling warm and welcoming. This living end table is made to fit naturally into the room. Crafted from Solid Rubberwood, Cherry Veneer, Poplar Burl Veneer, it is finished in Dark Cherry tones that pair easily with surrounding decor.
-Product Dimensions: 24"W X 20"D X 24"H Bonus storage &amp; convenience features (from matching set pieces): Felt-Lined Drawer and LED on End Table
-Materials: Solid Rubberwood, Cherry Veneer, Poplar Burl Veneer.
-Color: Dark Cherry</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WESTERHAM End Table w/ LED adds a Modern touch while keeping the room feeling warm and welcoming. This living end table is made to fit naturally into the room. Crafted from Solid Rubberwood, Cherry Veneer, Poplar Burl Veneer, it is finished in Dark Cherry tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 24"W X 20"D X 24"H Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-Lined Drawer and LED on End Table&lt;/p&gt;
+&lt;p&gt;Materials: Solid Rubberwood, Cherry Veneer, Poplar Burl Veneer.&lt;br&gt;
+Color: Dark Cherry&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -27114,14 +27114,14 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with WETTINGEN End Table and its Glam character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Chrome tones, the Stainless Steel, Faux Marble build balances durability with visual appeal.
-Product Dimensions: 23 1/2"L X 23 1/2"W X 23"H
-Features
-- Glam design
-Materials: Stainless Steel, Faux Marble.
-Color: Chrome
-Weight: 70.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with WETTINGEN End Table and its Glam character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Chrome tones, the Stainless Steel, Faux Marble build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 23 1/2"L X 23 1/2"W X 23"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Faux Marble.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 70.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -27239,14 +27239,14 @@
       </c>
       <c r="G210" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with WETZIKON End Table and its Glam character. As a living end table, it is designed to complement your space. Finished in Black or Silver tones, the Metal, Glass build balances durability with visual appeal.
-Product Dimensions: 23 1/2"L X 23 1/2"W X 23"H
-Features
-- Glam design
-Materials: Metal, Glass.
-Color: Black or Silver
-Weight: 53.95 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with WETZIKON End Table and its Glam character. As a living end table, it is designed to complement your space. Finished in Black or Silver tones, the Metal, Glass build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 23 1/2"L X 23 1/2"W X 23"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Glass.&lt;br&gt;
+Color: Black or Silver&lt;br&gt;
+Weight: 53.95 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H210" s="39" t="inlineStr">
@@ -27372,14 +27372,14 @@
       </c>
       <c r="G211" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WETZIKON End Table brings a Glam look to your home with a refined, comfortable feel. This living end table is made to fit naturally into the room. The Metal, Glass construction is complemented by White or Silver tones for a polished look.
-Product Dimensions: 23 1/2"L X 23 1/2"W X 23"H
-Features
-- Glam design
-Materials: Metal, Glass.
-Color: White or Silver
-Weight: 53.95 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WETZIKON End Table brings a Glam look to your home with a refined, comfortable feel. This living end table is made to fit naturally into the room. The Metal, Glass construction is complemented by White or Silver tones for a polished look.&lt;br&gt;
+Product Dimensions: 23 1/2"L X 23 1/2"W X 23"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Glass.&lt;br&gt;
+Color: White or Silver&lt;br&gt;
+Weight: 53.95 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H211" s="39" t="inlineStr">
@@ -27504,12 +27504,12 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with XANTHUS End Table and its Contemporary character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Black tones, the Steel, Glass, build balances durability with visual appeal.
-Product Dimensions: 24"L X 24"W X 23"H
-Materials: Steel, Glass.
-Color: Black
-Weight: 35.93 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with XANTHUS End Table and its Contemporary character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Black tones, the Steel, Glass, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 24"L X 24"W X 23"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Glass.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 35.93 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -27626,12 +27626,12 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ZOLA End Table and its Contemporary character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Chrome tones, the Metal, Tempered Glass, build balances durability with visual appeal.
-Product Dimensions: 26"L X 26"W X 24"H
-Materials: Metal, Tempered Glass.
-Color: Chrome
-Weight: 30.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ZOLA End Table and its Contemporary character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Chrome tones, the Metal, Tempered Glass, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 26"L X 26"W X 24"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 30.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -27752,14 +27752,14 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ARLINGTON Sofa Table, styled in Rustic and designed for everyday comfort. As a living sofa table, it is designed to complement your space. With Solid Wood, Wood Veneer, and Antique White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 53"L X 20"W X 32"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Antique White
-Weight: 73.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ARLINGTON Sofa Table, styled in Rustic and designed for everyday comfort. As a living sofa table, it is designed to complement your space. With Solid Wood, Wood Veneer, and Antique White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 53"L X 20"W X 32"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Antique White&lt;br&gt;
+Weight: 73.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -27880,14 +27880,14 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ATWOOD II Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. As a living sofa table, it is designed to complement your space. The Tempered Glass, Solid Wood, Wood Veneer, construction is complemented by Dark Walnut tones for a polished look.
-Product Dimensions: 48"L X 18"W X 30"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Tempered Glass, Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 54.24 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ATWOOD II Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. As a living sofa table, it is designed to complement your space. The Tempered Glass, Solid Wood, Wood Veneer, construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
+Product Dimensions: 48"L X 18"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 54.24 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -28004,14 +28004,14 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AUGSBURG Side Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Metal, Solid Wood, Wood Veneer, construction is complemented by Walnut or Gold tones for a polished look.
-Product Dimensions: 19"L X 16 3/4"W X 24"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Concealed Drawers
-Materials: Metal, Solid Wood, Wood Veneer.
-Color: Walnut or Gold
-Weight: 26.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AUGSBURG Side Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Metal, Solid Wood, Wood Veneer, construction is complemented by Walnut or Gold tones for a polished look.&lt;br&gt;
+Product Dimensions: 19"L X 16 3/4"W X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Walnut or Gold&lt;br&gt;
+Weight: 26.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -28132,14 +28132,14 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with AUGSBURG Sofa Table, styled in Contemporary and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Metal, Solid Wood, Wood Veneer, and Walnut or Gold tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 3/4"L X 16 3/4"W X 30"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Concealed Drawers
-Materials: Metal, Solid Wood, Wood Veneer.
-Color: Walnut or Gold
-Weight: 65 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with AUGSBURG Sofa Table, styled in Contemporary and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Metal, Solid Wood, Wood Veneer, and Walnut or Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 3/4"L X 16 3/4"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Walnut or Gold&lt;br&gt;
+Weight: 65 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -28260,15 +28260,15 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BACERRA Sofa Table brings a Rustic look to your home with a refined, comfortable feel. Built as a living sofa table, it pairs well with a wide range of interiors. The Metal, Solid Wood, construction is complemented by Antique White or Gold tones for a polished look.
-Product Dimensions: 36"L X 15"W X 30"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Center Glide Drawers
-Pull Out Drawer
-Materials: Metal, Solid Wood.
-Color: Antique White or Gold
-Weight: 91.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BACERRA Sofa Table brings a Rustic look to your home with a refined, comfortable feel. Built as a living sofa table, it pairs well with a wide range of interiors. The Metal, Solid Wood, construction is complemented by Antique White or Gold tones for a polished look.&lt;br&gt;
+Product Dimensions: 36"L X 15"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Center Glide Drawers&lt;br&gt;
+Pull Out Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Solid Wood.&lt;br&gt;
+Color: Antique White or Gold&lt;br&gt;
+Weight: 91.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -28389,12 +28389,12 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BATAM II Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living sofa table, it pairs well with a wide range of interiors. Crafted from Metal, Replicated Wood, Tempered Glass, it is finished in White or Natural Tone tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/4"L X 18"W X 30"H
-Materials: Metal, Replicated Wood, Tempered Glass.
-Color: White or Natural Tone
-Weight: 79.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BATAM II Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living sofa table, it pairs well with a wide range of interiors. Crafted from Metal, Replicated Wood, Tempered Glass, it is finished in White or Natural Tone tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 18"W X 30"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Replicated Wood, Tempered Glass.&lt;br&gt;
+Color: White or Natural Tone&lt;br&gt;
+Weight: 79.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -28511,12 +28511,12 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BIMA II Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living sofa table is made to fit naturally into the room. Crafted from Tempered Glass,Paper Veneer, it is finished in White or Natural Tone tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/4"L X 18"W X 29 1/2"H
-Materials: Tempered Glass,Paper Veneer.
-Color: White or Natural Tone
-Weight: 71.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BIMA II Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living sofa table is made to fit naturally into the room. Crafted from Tempered Glass,Paper Veneer, it is finished in White or Natural Tone tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 18"W X 29 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass,Paper Veneer.&lt;br&gt;
+Color: White or Natural Tone&lt;br&gt;
+Weight: 71.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -28633,14 +28633,14 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BRAMPTON Sofa Table, styled in Traditional and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Faux Marble, Solid Wood, Wood Veneer, and Espresso or Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 48"L X 18"W X 28"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Faux Marble, Solid Wood, Wood Veneer.
-Color: Espresso or Black
-Weight: 39.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BRAMPTON Sofa Table, styled in Traditional and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Faux Marble, Solid Wood, Wood Veneer, and Espresso or Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 48"L X 18"W X 28"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Faux Marble, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Espresso or Black&lt;br&gt;
+Weight: 39.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -28761,14 +28761,14 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BRYANNA Sofa Table adds a Transitional touch while keeping the room feeling warm and welcoming. This living sofa table is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in Antique Light Oak tones that pair easily with surrounding decor.
-Product Dimensions: 48"L X 18"W X 30"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Antique Light Oak
-Weight: 46.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BRYANNA Sofa Table adds a Transitional touch while keeping the room feeling warm and welcoming. This living sofa table is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in Antique Light Oak tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"L X 18"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Antique Light Oak&lt;br&gt;
+Weight: 46.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -28889,14 +28889,14 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BUNBURY Sofa Table brings a Traditional look to your home with a refined, comfortable feel. Built as a living sofa table, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Cherry tones for a polished look.
-Product Dimensions: 48"L X 16"W X 27"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Cherry
-Weight: 46.86 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BUNBURY Sofa Table brings a Traditional look to your home with a refined, comfortable feel. Built as a living sofa table, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by Cherry tones for a polished look.&lt;br&gt;
+Product Dimensions: 48"L X 16"W X 27"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Cherry&lt;br&gt;
+Weight: 46.86 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -29017,14 +29017,14 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CALANDRA Sofa Table adds a Rustic touch while keeping the room feeling warm and welcoming. This living sofa table is made to fit naturally into the room. Crafted from Solid Wood, it is finished in Antique Black tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/2"L X 19"W X 29 1/2"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: Antique Black
-Weight: 61.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CALANDRA Sofa Table adds a Rustic touch while keeping the room feeling warm and welcoming. This living sofa table is made to fit naturally into the room. Crafted from Solid Wood, it is finished in Antique Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/2"L X 19"W X 29 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: Antique Black&lt;br&gt;
+Weight: 61.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -29145,15 +29145,15 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CHESHIRE Sofa Table, styled in Traditional and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Dark Cherry tones, it blends structure and softness in one clean profile.
-Product Dimensions: 48"L X 17"W X 29 1/2"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Cherry
-Weight: 34.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CHESHIRE Sofa Table, styled in Traditional and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Dark Cherry tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 48"L X 17"W X 29 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Cherry&lt;br&gt;
+Weight: 34.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -29274,14 +29274,14 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CRYSTAL FALLS Sofa Table and its Transitional character. Built as a living sofa table, it pairs well with a wide range of interiors. Finished in Dark Cherry tones, the Tempered Glass, Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 51"L X 20"W X 29"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Tempered Glass, Solid Wood, Wood Veneer.
-Color: Dark Cherry
-Weight: 48.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CRYSTAL FALLS Sofa Table and its Transitional character. Built as a living sofa table, it pairs well with a wide range of interiors. Finished in Dark Cherry tones, the Tempered Glass, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 51"L X 20"W X 29"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Cherry&lt;br&gt;
+Weight: 48.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -29403,12 +29403,12 @@
       </c>
       <c r="G227" s="46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DUBENDORF Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Glass, construction is complemented by Black tones for a polished look.
-Product Dimensions: 47 1/4"L X 17 7/8"W X 29 7/8"H
-Materials: Glass.
-Color: Black
-Weight: 88 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DUBENDORF Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Glass, construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 17 7/8"W X 29 7/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 88 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H227" s="46" t="inlineStr">
@@ -29532,12 +29532,12 @@
       </c>
       <c r="G228" s="46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with DUBENDORF Sofa Table, styled in Contemporary and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Glass, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 1/4"L X 17 7/8"W X 29 7/8"H
-Materials: Glass.
-Color: White
-Weight: 88 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with DUBENDORF Sofa Table, styled in Contemporary and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Glass, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 17 7/8"W X 29 7/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 88 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H228" s="46" t="inlineStr">
@@ -29660,12 +29660,12 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EIMEAR Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Metal, construction is complemented by White or Black tones for a polished look.
-Product Dimensions: 47 1/4"L X 15 3/4"W X 30"H
-Materials: Metal.
-Color: White or Black
-Weight: 50.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EIMEAR Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Metal, construction is complemented by White or Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 15 3/4"W X 30"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: White or Black&lt;br&gt;
+Weight: 50.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -29786,14 +29786,14 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GIORDANI Sofa Table adds a Traditional touch while keeping the room feeling warm and welcoming. As a living sofa table, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Weathered Oak tones that pair easily with surrounding decor.
-Product Dimensions: 50"W X 17"D X 30"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Weathered Oak
-Weight: 55 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GIORDANI Sofa Table adds a Traditional touch while keeping the room feeling warm and welcoming. As a living sofa table, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Weathered Oak tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 50"W X 17"D X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Weathered Oak&lt;br&gt;
+Weight: 55 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -29919,14 +29919,14 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with GRANVIA Sofa Table, styled in Transitional and designed for everyday comfort. This living sofa table is made to fit naturally into the room. With Tempered Glass, Solid Wood, Wood Veneer, and Dark Cherry tones, it blends structure and softness in one clean profile.
-Product Dimensions: 48"L X 18"W X 29"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Tempered Glass, Solid Wood, Wood Veneer.
-Color: Dark Cherry
-Weight: 36.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with GRANVIA Sofa Table, styled in Transitional and designed for everyday comfort. This living sofa table is made to fit naturally into the room. With Tempered Glass, Solid Wood, Wood Veneer, and Dark Cherry tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 48"L X 18"W X 29"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Cherry&lt;br&gt;
+Weight: 36.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -30047,12 +30047,12 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-IZAR Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living sofa table, it pairs well with a wide range of interiors. The Metal, Engineered Wood construction is complemented by White or Gun Metal tones for a polished look.
-Product Dimensions: 47 1/4"L X 15 3/4"W X 29 1/2"H
-Materials: Metal, Engineered Wood.
-Color: White or Gun Metal
-Weight: 42.64 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+IZAR Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living sofa table, it pairs well with a wide range of interiors. The Metal, Engineered Wood construction is complemented by White or Gun Metal tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 15 3/4"W X 29 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Engineered Wood.&lt;br&gt;
+Color: White or Gun Metal&lt;br&gt;
+Weight: 42.64 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -30170,14 +30170,14 @@
       </c>
       <c r="G233" s="44" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with KOBLENZ Sofa Table, styled in Glam and designed for everyday comfort. This living sofa table is made to fit naturally into the room. With Metal, and Light Teal tones, it blends structure and softness in one clean profile.
-Product Dimensions: 48"L X 16"W X 30"H
-Features
-- Glam design Bonus storage &amp; convenience features (from matching set pieces): Concealed Drawer
-Materials: Metal.
-Color: Light Teal
-Weight: 64.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with KOBLENZ Sofa Table, styled in Glam and designed for everyday comfort. This living sofa table is made to fit naturally into the room. With Metal, and Light Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 48"L X 16"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Light Teal&lt;br&gt;
+Weight: 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H233" s="44" t="inlineStr">
@@ -30301,14 +30301,14 @@
       </c>
       <c r="G234" s="44" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KOBLENZ Sofa Table adds a Glam touch while keeping the room feeling warm and welcoming. Built as a living sofa table, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Dark Walnut tones that pair easily with surrounding decor.
-Product Dimensions: 48"L X 16"W X 30"H
-Features
-- Glam design Bonus storage &amp; convenience features (from matching set pieces): Concealed Drawer
-Materials: Metal.
-Color: Dark Walnut
-Weight: 65.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KOBLENZ Sofa Table adds a Glam touch while keeping the room feeling warm and welcoming. Built as a living sofa table, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"L X 16"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 65.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H234" s="44" t="inlineStr">
@@ -30431,12 +30431,12 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LAILA Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Glass, Metal construction is complemented by Chrome tones for a polished look.
-Product Dimensions: 45 1/4"L X 17 3/4"W X 29 3/4"H
-Materials: Glass, Metal.
-Color: Chrome
-Weight: 47.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LAILA Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Glass, Metal construction is complemented by Chrome tones for a polished look.&lt;br&gt;
+Product Dimensions: 45 1/4"L X 17 3/4"W X 29 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 47.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -30553,12 +30553,12 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with LOBB Sofa Table and its Industrial character. Built as a living sofa table, it pairs well with a wide range of interiors. Finished in Natural Tone or Black tones, the Steel, Paper Veneer, build balances durability with visual appeal.
-Product Dimensions: 47 1/4"L X 17 3/4"W X 30"H
-Materials: Steel, Paper Veneer.
-Color: Natural Tone or Black
-Weight: 49 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with LOBB Sofa Table and its Industrial character. Built as a living sofa table, it pairs well with a wide range of interiors. Finished in Natural Tone or Black tones, the Steel, Paper Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 17 3/4"W X 30"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Paper Veneer.&lt;br&gt;
+Color: Natural Tone or Black&lt;br&gt;
+Weight: 49 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -30685,12 +30685,12 @@
       </c>
       <c r="G237" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LODIA III Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Tempered Glass, Paper Veneer, Engineered Wood construction is complemented by Black tones for a polished look.
-Product Dimensions: 47 1/4"L X 18"W X 29 7/8"H
-Materials: Tempered Glass, Paper Veneer, Engineered Wood.
-Color: Black
-Weight: 65.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LODIA III Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Tempered Glass, Paper Veneer, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 18"W X 29 7/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 65.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H237" s="30" t="inlineStr">
@@ -30812,12 +30812,12 @@
       </c>
       <c r="G238" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with LODIA III Sofa Table, styled in Contemporary and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Tempered Glass, Paper Veneer, Engineered Wood and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 1/4"L X 18"W X 29 7/8"H
-Materials: Tempered Glass, Paper Veneer, Engineered Wood.
-Color: White
-Weight: 65.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with LODIA III Sofa Table, styled in Contemporary and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Tempered Glass, Paper Veneer, Engineered Wood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 18"W X 29 7/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 65.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H238" s="30" t="inlineStr">
@@ -30938,12 +30938,12 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LODIA Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living sofa table, it is designed to complement your space. Crafted from Tempered Glass, Paper Veneer, Engineered Wood, it is finished in Gray tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/4"L X 18"W X 29 5/8"H
-Materials: Tempered Glass, Paper Veneer, Engineered Wood.
-Color: Gray
-Weight: 39.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LODIA Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living sofa table, it is designed to complement your space. Crafted from Tempered Glass, Paper Veneer, Engineered Wood, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 18"W X 29 5/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 39.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -31060,12 +31060,12 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LUDVIG Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. As a living sofa table, it is designed to complement your space. The Metal, Tempered Glass, construction is complemented by Chrome or Clear tones for a polished look.
-Product Dimensions: 47 1/2"L X 16"W X 30"H
-Materials: Metal, Tempered Glass.
-Color: Chrome or Clear
-Weight: 69.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LUDVIG Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. As a living sofa table, it is designed to complement your space. The Metal, Tempered Glass, construction is complemented by Chrome or Clear tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/2"L X 16"W X 30"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass.&lt;br&gt;
+Color: Chrome or Clear&lt;br&gt;
+Weight: 69.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -31186,14 +31186,14 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MAJKEN Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living sofa table, it pairs well with a wide range of interiors. The Solid Wood, construction is complemented by White or Natural Tone tones for a polished look.
-Product Dimensions: 47 1/4"L X 15 1/2"W X 30"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White or Natural Tone
-Weight: 85.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MAJKEN Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living sofa table, it pairs well with a wide range of interiors. The Solid Wood, construction is complemented by White or Natural Tone tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 15 1/2"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Natural Tone&lt;br&gt;
+Weight: 85.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -31315,12 +31315,12 @@
       </c>
       <c r="G242" s="46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MANNEDORF Sofa Table, styled in Contemporary and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Tempered Glass,Paper Veneer, and Black or Dark Walnut tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 1/4"L X 15 5/8"W X 3"H
-Materials: Tempered Glass,Paper Veneer.
-Color: Black or Dark Walnut
-Weight: 85 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MANNEDORF Sofa Table, styled in Contemporary and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Tempered Glass,Paper Veneer, and Black or Dark Walnut tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 15 5/8"W X 3"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass,Paper Veneer.&lt;br&gt;
+Color: Black or Dark Walnut&lt;br&gt;
+Weight: 85 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H242" s="46" t="inlineStr">
@@ -31448,12 +31448,12 @@
       </c>
       <c r="G243" s="46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MANNEDORF Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living sofa table, it is designed to complement your space. Crafted from Tempered Glass,Paper Veneer, it is finished in Black or White tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/4"L X 15 5/8"W X 3"H
-Materials: Tempered Glass,Paper Veneer.
-Color: Black or White
-Weight: 72.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MANNEDORF Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living sofa table, it is designed to complement your space. Crafted from Tempered Glass,Paper Veneer, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 15 5/8"W X 3"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass,Paper Veneer.&lt;br&gt;
+Color: Black or White&lt;br&gt;
+Weight: 72.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H243" s="46" t="inlineStr">
@@ -31576,12 +31576,12 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MAY Sofa Table adds a Traditional touch while keeping the room feeling warm and welcoming. Built as a living sofa table, it pairs well with a wide range of interiors. Crafted from Glass, Metal, Wood, it is finished in Brown Cherry tones that pair easily with surrounding decor.
-Product Dimensions: 48"L X 19"W X 30"H
-Materials: Glass, Metal, Wood.
-Color: Brown Cherry
-Weight: 56.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MAY Sofa Table adds a Traditional touch while keeping the room feeling warm and welcoming. Built as a living sofa table, it pairs well with a wide range of interiors. Crafted from Glass, Metal, Wood, it is finished in Brown Cherry tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"L X 19"W X 30"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Wood.&lt;br&gt;
+Color: Brown Cherry&lt;br&gt;
+Weight: 56.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -31702,14 +31702,14 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MEADOW Sofa Table, styled in Rustic and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Antique Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 64"L X 15"W X 30"H
-Features
-- Made with solid wood &amp; wood veneer Bonus storage &amp; convenience features (from matching set pieces): Storage Drawers
-Materials: Solid Wood, Wood Veneer.
-Color: Antique Black
-Weight: 105.82 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MEADOW Sofa Table, styled in Rustic and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Solid Wood, Wood Veneer, and Antique Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 64"L X 15"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Antique Black&lt;br&gt;
+Weight: 105.82 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -31830,14 +31830,14 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MOA Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Solid Wood, construction is complemented by White or Natural Tone tones for a polished look.
-Product Dimensions: 47 1/4"L X 15 1/2"W X 30"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood.
-Color: White or Natural Tone
-Weight: 131.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MOA Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Solid Wood, construction is complemented by White or Natural Tone tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 15 1/2"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood.&lt;br&gt;
+Color: White or Natural Tone&lt;br&gt;
+Weight: 131.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -31959,12 +31959,12 @@
       </c>
       <c r="G247" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with NAHARA Sofa Table and its Contemporary character. As a living sofa table, it is designed to complement your space. Finished in Black tones, the Glass, build balances durability with visual appeal.
-Product Dimensions: 47 1/4"L X 18"W X 29 3/4"H
-Materials: Glass.
-Color: Black
-Weight: 83.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with NAHARA Sofa Table and its Contemporary character. As a living sofa table, it is designed to complement your space. Finished in Black tones, the Glass, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 18"W X 29 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 83.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H247" s="56" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="G248" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NAHARA Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Glass, construction is complemented by Gray tones for a polished look.
-Product Dimensions: 47 1/4"L X 18"W X 29 3/4"H
-Materials: Glass.
-Color: Gray
-Weight: 83.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NAHARA Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Glass, construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 18"W X 29 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 83.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H248" s="56" t="inlineStr">
@@ -32213,12 +32213,12 @@
       </c>
       <c r="G249" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with NAHARA Sofa Table, styled in Contemporary and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Glass, and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: 47 1/4"L X 18"W X 29 3/4"H
-Materials: Glass.
-Color: White
-Weight: 83.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with NAHARA Sofa Table, styled in Contemporary and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Glass, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 18"W X 29 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 83.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H249" s="56" t="inlineStr">
@@ -32339,12 +32339,12 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with NOVA Sofa Table and its Contemporary character. As a living sofa table, it is designed to complement your space. Finished in Satin Plated or Black tones, the Stainless Steel, Tempered Glass, build balances durability with visual appeal.
-Product Dimensions: 45"L X 18"W X 28 3/4"H
-Materials: Stainless Steel, Tempered Glass.
-Color: Satin Plated or Black
-Weight: 54.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with NOVA Sofa Table and its Contemporary character. As a living sofa table, it is designed to complement your space. Finished in Satin Plated or Black tones, the Stainless Steel, Tempered Glass, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 45"L X 18"W X 28 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Satin Plated or Black&lt;br&gt;
+Weight: 54.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -32461,14 +32461,14 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OAKWAY Sofa Table adds a Traditional touch while keeping the room feeling warm and welcoming. As a living sofa table, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Weathered Oak tones that pair easily with surrounding decor.
-Product Dimensions: 54"W X 20"D X 30"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Weathered Oak
-Weight: 83 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OAKWAY Sofa Table adds a Traditional touch while keeping the room feeling warm and welcoming. As a living sofa table, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Weathered Oak tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 54"W X 20"D X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Weathered Oak&lt;br&gt;
+Weight: 83 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -32589,12 +32589,12 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OLBIA Sofa Table adds a Industrial touch while keeping the room feeling warm and welcoming. This living sofa table is made to fit naturally into the room. Crafted from Steel, Paper Veneer, it is finished in Rustic Oak or Sand Black tones that pair easily with surrounding decor.
-Product Dimensions: 47 1/4"L X 15 3/4"W X 28"H
-Materials: Steel, Paper Veneer.
-Color: Rustic Oak or Sand Black
-Weight: 36.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OLBIA Sofa Table adds a Industrial touch while keeping the room feeling warm and welcoming. This living sofa table is made to fit naturally into the room. Crafted from Steel, Paper Veneer, it is finished in Rustic Oak or Sand Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 15 3/4"W X 28"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Paper Veneer.&lt;br&gt;
+Color: Rustic Oak or Sand Black&lt;br&gt;
+Weight: 36.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -32715,12 +32715,12 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ORLA II Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living sofa table, it pairs well with a wide range of interiors. The Stainless Steel, Tempered Glass, construction is complemented by Satin Plated or Black tones for a polished look.
-Product Dimensions: 48"L X 18"W X 29"H
-Materials: Stainless Steel, Tempered Glass.
-Color: Satin Plated or Black
-Weight: 62.48 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ORLA II Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living sofa table, it pairs well with a wide range of interiors. The Stainless Steel, Tempered Glass, construction is complemented by Satin Plated or Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 48"L X 18"W X 29"H&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Satin Plated or Black&lt;br&gt;
+Weight: 62.48 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -32837,12 +32837,12 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-RAYA Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. As a living sofa table, it is designed to complement your space. The Tempered Glass, Wood, construction is complemented by White tones for a polished look.
-Product Dimensions: 47"L X 15 3/4"W X 30"H
-Materials: Tempered Glass, Wood.
-Color: White
-Weight: 92.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+RAYA Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. As a living sofa table, it is designed to complement your space. The Tempered Glass, Wood, construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 47"L X 15 3/4"W X 30"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 92.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -32963,14 +32963,14 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ROSETTA Sofa Table and its Transitional character. Built as a living sofa table, it pairs well with a wide range of interiors. Finished in Dark Walnut tones, the Faux Marble, Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 48"L X 18 1/4"W X 29 1/2"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Faux Marble, Solid Wood, Wood Veneer.
-Color: Dark Walnut
-Weight: 86.68 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ROSETTA Sofa Table and its Transitional character. Built as a living sofa table, it pairs well with a wide range of interiors. Finished in Dark Walnut tones, the Faux Marble, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 48"L X 18 1/4"W X 29 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Faux Marble, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Walnut&lt;br&gt;
+Weight: 86.68 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -33091,12 +33091,12 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ROXO Sofa Table and its Contemporary character. Built as a living sofa table, it pairs well with a wide range of interiors. Finished in Satin Plated or Black tones, the Stainless Steel, Tempered Glass, build balances durability with visual appeal.
-Product Dimensions: 48"L X 18"W X 30 1/4"H
-Materials: Stainless Steel, Tempered Glass.
-Color: Satin Plated or Black
-Weight: 54.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ROXO Sofa Table and its Contemporary character. Built as a living sofa table, it pairs well with a wide range of interiors. Finished in Satin Plated or Black tones, the Stainless Steel, Tempered Glass, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 48"L X 18"W X 30 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Satin Plated or Black&lt;br&gt;
+Weight: 54.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -33213,12 +33213,12 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-RYLEE Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Metal, Tempered Glass, construction is complemented by Chrome tones for a polished look.
-Product Dimensions: 47-1/4"L x 17-3/4"W x 29"H
-Materials: Metal, Tempered Glass.
-Color: Chrome
-Weight: 62.92 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+RYLEE Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Metal, Tempered Glass, construction is complemented by Chrome tones for a polished look.&lt;br&gt;
+Product Dimensions: 47-1/4"L x 17-3/4"W x 29"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Tempered Glass.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 62.92 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -33339,12 +33339,12 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SLOANE Sofa Table and its Contemporary character. Built as a living sofa table, it pairs well with a wide range of interiors. Finished in White or Dark Gray or Chrome tones, the Glass, Stainless Steel build balances durability with visual appeal.
-Product Dimensions: 48"L X 18"W X 29 1/2"H
-Materials: Glass, Stainless Steel.
-Color: White or Dark Gray or Chrome
-Weight: 81.14 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SLOANE Sofa Table and its Contemporary character. Built as a living sofa table, it pairs well with a wide range of interiors. Finished in White or Dark Gray or Chrome tones, the Glass, Stainless Steel build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 48"L X 18"W X 29 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Stainless Steel.&lt;br&gt;
+Color: White or Dark Gray or Chrome&lt;br&gt;
+Weight: 81.14 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -33462,12 +33462,12 @@
       </c>
       <c r="G259" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with STATEN Sofa Table, styled in Contemporary and designed for everyday comfort. As a living sofa table, it is designed to complement your space. With Tempered Glass, Metal, Engineered Wood and Glossy Black or Chrome tones, it blends structure and softness in one clean profile.
-Product Dimensions: 48"L X 18"W X 29 3/4"H
-Materials: Tempered Glass, Metal, Engineered Wood.
-Color: Glossy Black or Chrome
-Weight: 57.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with STATEN Sofa Table, styled in Contemporary and designed for everyday comfort. As a living sofa table, it is designed to complement your space. With Tempered Glass, Metal, Engineered Wood and Glossy Black or Chrome tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 48"L X 18"W X 29 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Metal, Engineered Wood.&lt;br&gt;
+Color: Glossy Black or Chrome&lt;br&gt;
+Weight: 57.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H259" s="54" t="inlineStr">
@@ -33593,12 +33593,12 @@
       </c>
       <c r="G260" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-STATEN Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living sofa table is made to fit naturally into the room. Crafted from Tempered Glass, Metal, Engineered Wood, it is finished in Glossy White or Chrome tones that pair easily with surrounding decor.
-Product Dimensions: 48"L X 18"W X 29 3/4"H
-Materials: Tempered Glass, Metal, Engineered Wood.
-Color: Glossy White or Chrome
-Weight: 57.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+STATEN Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living sofa table is made to fit naturally into the room. Crafted from Tempered Glass, Metal, Engineered Wood, it is finished in Glossy White or Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48"L X 18"W X 29 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Metal, Engineered Wood.&lt;br&gt;
+Color: Glossy White or Chrome&lt;br&gt;
+Weight: 57.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H260" s="54" t="inlineStr">
@@ -33723,12 +33723,12 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SUNDANCE Sofa Table and its Contemporary character. As a living sofa table, it is designed to complement your space. Finished in Chrome tones, the Metal, Mirror, build balances durability with visual appeal.
-Product Dimensions: 48"L X 17"W X 30"H
-Materials: Metal, Mirror.
-Color: Chrome
-Weight: 68.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SUNDANCE Sofa Table and its Contemporary character. As a living sofa table, it is designed to complement your space. Finished in Chrome tones, the Metal, Mirror, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 48"L X 17"W X 30"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Mirror.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 68.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -33849,12 +33849,12 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with TITUS Sofa Table and its Contemporary character. As a living sofa table, it is designed to complement your space. Finished in White or Chrome tones, the Steel, Paper Veneer, build balances durability with visual appeal.
-Product Dimensions: 47 1/2"L X 15 3/4"W X 29 1/2"H
-Materials: Steel, Paper Veneer.
-Color: White or Chrome
-Weight: 49.06 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with TITUS Sofa Table and its Contemporary character. As a living sofa table, it is designed to complement your space. Finished in White or Chrome tones, the Steel, Paper Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 47 1/2"L X 15 3/4"W X 29 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Paper Veneer.&lt;br&gt;
+Color: White or Chrome&lt;br&gt;
+Weight: 49.06 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -33975,12 +33975,12 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VALO Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living sofa table is made to fit naturally into the room. Crafted from Stainless Steel, Tempered Glass, it is finished in Satin Plated or Black tones that pair easily with surrounding decor.
-Product Dimensions: 46"L X 16"W X 29 5/8"H
-Materials: Stainless Steel, Tempered Glass.
-Color: Satin Plated or Black
-Weight: 35.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VALO Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living sofa table is made to fit naturally into the room. Crafted from Stainless Steel, Tempered Glass, it is finished in Satin Plated or Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 46"L X 16"W X 29 5/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Tempered Glass.&lt;br&gt;
+Color: Satin Plated or Black&lt;br&gt;
+Weight: 35.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -34097,14 +34097,14 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VILLARSGLANE Sofa Table adds a Glam touch while keeping the room feeling warm and welcoming. This living sofa table is made to fit naturally into the room. Crafted from Stainless Steel, Faux Marble, it is finished in Chrome tones that pair easily with surrounding decor.
-Product Dimensions: 55"L X 16"W X 3"H
-Features
-- Glam design
-Materials: Stainless Steel, Faux Marble.
-Color: Chrome
-Weight: 112.36 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VILLARSGLANE Sofa Table adds a Glam touch while keeping the room feeling warm and welcoming. This living sofa table is made to fit naturally into the room. Crafted from Stainless Steel, Faux Marble, it is finished in Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 55"L X 16"W X 3"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Faux Marble.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 112.36 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -34221,15 +34221,15 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with WALWORTH Sofa Table, styled in Traditional and designed for everyday comfort. This living sofa table is made to fit naturally into the room. With Tempered Glass, Solid Wood and Dark Oak tones, it blends structure and softness in one clean profile.
-Product Dimensions: 48"L X 20"W X 30 1/2"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Tempered Glass, Solid Wood.
-Color: Dark Oak
-Weight: 70.84 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with WALWORTH Sofa Table, styled in Traditional and designed for everyday comfort. This living sofa table is made to fit naturally into the room. With Tempered Glass, Solid Wood and Dark Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 48"L X 20"W X 30 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood.&lt;br&gt;
+Color: Dark Oak&lt;br&gt;
+Weight: 70.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -34350,14 +34350,14 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WETTINGEN Sofa Table brings a Glam look to your home with a refined, comfortable feel. As a living sofa table, it is designed to complement your space. The Stainless Steel, Faux Marble construction is complemented by Chrome tones for a polished look.
-Product Dimensions: 55"L X 16"W X 3"H
-Features
-- Glam design
-Materials: Stainless Steel, Faux Marble.
-Color: Chrome
-Weight: 98.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WETTINGEN Sofa Table brings a Glam look to your home with a refined, comfortable feel. As a living sofa table, it is designed to complement your space. The Stainless Steel, Faux Marble construction is complemented by Chrome tones for a polished look.&lt;br&gt;
+Product Dimensions: 55"L X 16"W X 3"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;/p&gt;
+&lt;p&gt;Materials: Stainless Steel, Faux Marble.&lt;br&gt;
+Color: Chrome&lt;br&gt;
+Weight: 98.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -34475,14 +34475,14 @@
       </c>
       <c r="G267" s="48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with WETZIKON Sofa Table, styled in Glam and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Metal, Glass and Black or Silver tones, it blends structure and softness in one clean profile.
-Product Dimensions: 55"L X 16"W X 30"H
-Features
-- Glam design
-Materials: Metal, Glass.
-Color: Black or Silver
-Weight: 64.26 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with WETZIKON Sofa Table, styled in Glam and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Metal, Glass and Black or Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 55"L X 16"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Glass.&lt;br&gt;
+Color: Black or Silver&lt;br&gt;
+Weight: 64.26 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H267" s="48" t="inlineStr">
@@ -34608,14 +34608,14 @@
       </c>
       <c r="G268" s="48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WETZIKON Sofa Table adds a Glam touch while keeping the room feeling warm and welcoming. As a living sofa table, it is designed to complement your space. Crafted from Metal, Glass, it is finished in White or Silver tones that pair easily with surrounding decor.
-Product Dimensions: 55"L X 16"W X 30"H
-Features
-- Glam design
-Materials: Metal, Glass.
-Color: White or Silver
-Weight: 64.26 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WETZIKON Sofa Table adds a Glam touch while keeping the room feeling warm and welcoming. As a living sofa table, it is designed to complement your space. Crafted from Metal, Glass, it is finished in White or Silver tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 55"L X 16"W X 30"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Glass.&lt;br&gt;
+Color: White or Silver&lt;br&gt;
+Weight: 64.26 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H268" s="48" t="inlineStr">
@@ -34740,12 +34740,12 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-XANTHUS Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. As a living sofa table, it is designed to complement your space. The Steel, Glass, construction is complemented by Black tones for a polished look.
-Product Dimensions: 48"L X 18"W X 29"H
-Materials: Steel, Glass.
-Color: Black
-Weight: 51.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+XANTHUS Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. As a living sofa table, it is designed to complement your space. The Steel, Glass, construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 48"L X 18"W X 29"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Glass.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 51.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -34862,14 +34862,14 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTH Side Table adds a Mid-Century Modern touch while keeping the room feeling warm and welcoming. Built as a living chair, it pairs well with a wide range of interiors. Crafted from Solid Wood, Engineered Wood, Wood Veneer, it is finished in Walnut tones that pair easily with surrounding decor.
-Product Dimensions: 23.5"W X 23.5"D X 19.5"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Engineered Wood, Wood Veneer.
-Color: Walnut
-Weight: 15.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTH Side Table adds a Mid-Century Modern touch while keeping the room feeling warm and welcoming. Built as a living chair, it pairs well with a wide range of interiors. Crafted from Solid Wood, Engineered Wood, Wood Veneer, it is finished in Walnut tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 23.5"W X 23.5"D X 19.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood, Wood Veneer.&lt;br&gt;
+Color: Walnut&lt;br&gt;
+Weight: 15.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -34990,14 +34990,14 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SPIEZ Accent Chair brings a Mid-Century Modern look to your home with a refined, comfortable feel. As a living chair, it is designed to complement your space. The Fabric, Solid Wood, Engineered Wood, Wood Veneer construction is complemented by Walnut or Beige tones for a polished look.
-Product Dimensions: 24.5"W X 27"D X 28"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Fabric, Solid Wood, Engineered Wood, Wood Veneer.
-Color: Walnut or Beige
-Weight: 22 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SPIEZ Accent Chair brings a Mid-Century Modern look to your home with a refined, comfortable feel. As a living chair, it is designed to complement your space. The Fabric, Solid Wood, Engineered Wood, Wood Veneer construction is complemented by Walnut or Beige tones for a polished look.&lt;br&gt;
+Product Dimensions: 24.5"W X 27"D X 28"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Engineered Wood, Wood Veneer.&lt;br&gt;
+Color: Walnut or Beige&lt;br&gt;
+Weight: 22 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -35123,14 +35123,14 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BELP Accent Chair adds a Mid-Century Modern touch while keeping the room feeling warm and welcoming. As a living side table, it is designed to complement your space. Crafted from Fabric, Solid Wood, Engineered Wood, Wood Veneer, it is finished in Walnut or Beige tones that pair easily with surrounding decor.
-Product Dimensions: 23"W X 29"D X 29"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Fabric, Solid Wood, Engineered Wood, Wood Veneer.
-Color: Walnut or Beige
-Weight: 24.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BELP Accent Chair adds a Mid-Century Modern touch while keeping the room feeling warm and welcoming. As a living side table, it is designed to complement your space. Crafted from Fabric, Solid Wood, Engineered Wood, Wood Veneer, it is finished in Walnut or Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 23"W X 29"D X 29"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Engineered Wood, Wood Veneer.&lt;br&gt;
+Color: Walnut or Beige&lt;br&gt;
+Weight: 24.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -35256,12 +35256,12 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CHILOQUIN Side Table adds a Mid-century Modern touch while keeping the room feeling warm and welcoming. As a living side table, it is designed to complement your space. Crafted from Velvet, Stainless Steel, Engineered Wood, it is finished in Natural tones that pair easily with surrounding decor.
-Product Dimensions: 22"W X 16"D X 18"H
-Materials: Velvet, Stainless Steel, Engineered Wood.
-Color: Natural
-Weight: 35.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CHILOQUIN Side Table adds a Mid-century Modern touch while keeping the room feeling warm and welcoming. As a living side table, it is designed to complement your space. Crafted from Velvet, Stainless Steel, Engineered Wood, it is finished in Natural tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 22"W X 16"D X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Velvet, Stainless Steel, Engineered Wood.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 35.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -35382,12 +35382,12 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with GARIBALDI Side Table and its Rustic Farmhouse character. This living side table is made to fit naturally into the room. Finished in Brown or Gray tones, the Paper, Engineered Wood, Metal build balances durability with visual appeal.
-Product Dimensions: 16"W X 14"D X 23"H
-Materials: Paper, Engineered Wood, Metal.
-Color: Brown or Gray
-Weight: 25.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with GARIBALDI Side Table and its Rustic Farmhouse character. This living side table is made to fit naturally into the room. Finished in Brown or Gray tones, the Paper, Engineered Wood, Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 16"W X 14"D X 23"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Engineered Wood, Metal.&lt;br&gt;
+Color: Brown or Gray&lt;br&gt;
+Weight: 25.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -35508,12 +35508,12 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with NORTHWICH Side Table, styled in Contemporary and designed for everyday comfort. Built as a living side table, it pairs well with a wide range of interiors. With Sintered Stone, Stainless Steel and White or Matte Gold tones, it blends structure and softness in one clean profile.
-Product Dimensions: 22"W X 20"D X 22"H
-Materials: Sintered Stone, Stainless Steel.
-Color: White or Matte Gold
-Weight: 56 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with NORTHWICH Side Table, styled in Contemporary and designed for everyday comfort. Built as a living side table, it pairs well with a wide range of interiors. With Sintered Stone, Stainless Steel and White or Matte Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 22"W X 20"D X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Sintered Stone, Stainless Steel.&lt;br&gt;
+Color: White or Matte Gold&lt;br&gt;
+Weight: 56 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -35630,14 +35630,14 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with VARDO Side Table, styled in Mid-Century Modern and designed for everyday comfort. Built as a living side table, it pairs well with a wide range of interiors. With Solid Wood, Engineered Wood, Wood Veneer and Walnut tones, it blends structure and softness in one clean profile.
-Product Dimensions: 19.5"W X 19.5"D X 19.5"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Engineered Wood, Wood Veneer.
-Color: Walnut
-Weight: 11 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with VARDO Side Table, styled in Mid-Century Modern and designed for everyday comfort. Built as a living side table, it pairs well with a wide range of interiors. With Solid Wood, Engineered Wood, Wood Veneer and Walnut tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 19.5"W X 19.5"D X 19.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Engineered Wood, Wood Veneer.&lt;br&gt;
+Color: Walnut&lt;br&gt;
+Weight: 11 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -35759,11 +35759,11 @@
       </c>
       <c r="G277" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BORUP 3 Pc. Table Set adds a Rustic touch while keeping the room feeling warm and welcoming. This living table set is made to fit naturally into the room. Crafted from Paper, Metal, Engineered Wood, it is finished in Dark Brown or Black tones that pair easily with surrounding decor.
-Product Dimensions: COFFEE TABLE: 31.5"W X 30.5"D X 18"H, END TABLE: 15.5"W X 15"D X 23"H
-Materials: Paper, Metal, Engineered Wood.
-Color: Dark Brown or Black</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BORUP 3 Pc. Table Set adds a Rustic touch while keeping the room feeling warm and welcoming. This living table set is made to fit naturally into the room. Crafted from Paper, Metal, Engineered Wood, it is finished in Dark Brown or Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 31.5"W X 30.5"D X 18"H, END TABLE: 15.5"W X 15"D X 23"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
+Color: Dark Brown or Black&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H277" s="52" t="inlineStr">
@@ -35885,11 +35885,11 @@
       </c>
       <c r="G278" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with BORUP 3 Pc. Table Set and its Rustic character. Built as a living table set, it pairs well with a wide range of interiors. Finished in Natural or Black tones, the Paper, Metal, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: COFFEE TABLE: 31.5"W X 30.5"D X 18"H, END TABLE: 15.5"W X 15"D X 23"H
-Materials: Paper, Metal, Engineered Wood.
-Color: Natural or Black</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with BORUP 3 Pc. Table Set and its Rustic character. Built as a living table set, it pairs well with a wide range of interiors. Finished in Natural or Black tones, the Paper, Metal, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 31.5"W X 30.5"D X 18"H, END TABLE: 15.5"W X 15"D X 23"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
+Color: Natural or Black&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H278" s="52" t="inlineStr">
@@ -36011,14 +36011,14 @@
       </c>
       <c r="G279" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FINDLAY 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. As a living table set, it is designed to complement your space. The Paper, Rubberwood, Engineered Wood construction is complemented by Black tones for a polished look.
-Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Paper, Rubberwood, Engineered Wood.
-Color: Black
-Weight: 53 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FINDLAY 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. As a living table set, it is designed to complement your space. The Paper, Rubberwood, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 53 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H279" s="54" t="inlineStr">
@@ -36142,14 +36142,14 @@
       </c>
       <c r="G280" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with FINDLAY 3 Pc. Table Set, styled in Contemporary and designed for everyday comfort. This living table set is made to fit naturally into the room. With Paper, Rubberwood, Engineered Wood and Brown tones, it blends structure and softness in one clean profile.
-Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Paper, Rubberwood, Engineered Wood.
-Color: Brown
-Weight: 15 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with FINDLAY 3 Pc. Table Set, styled in Contemporary and designed for everyday comfort. This living table set is made to fit naturally into the room. With Paper, Rubberwood, Engineered Wood and Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 15 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H280" s="54" t="inlineStr">
@@ -36273,14 +36273,14 @@
       </c>
       <c r="G281" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FINDLAY 3 Pc. Table Set adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living table set, it pairs well with a wide range of interiors. Crafted from Paper, Rubberwood, Engineered Wood, it is finished in Black &amp; White tones that pair easily with surrounding decor.
-Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Paper, Rubberwood, Engineered Wood.
-Color: Black &amp; White
-Weight: 25 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FINDLAY 3 Pc. Table Set adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living table set, it pairs well with a wide range of interiors. Crafted from Paper, Rubberwood, Engineered Wood, it is finished in Black &amp;amp; White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Black &amp;amp; White&lt;br&gt;
+Weight: 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H281" s="54" t="inlineStr">
@@ -36404,14 +36404,14 @@
       </c>
       <c r="G282" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with FINDLAY 3 Pc. Table Set and its Contemporary character. As a living table set, it is designed to complement your space. Finished in Gray tones, the Paper, Rubberwood, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Paper, Rubberwood, Engineered Wood.
-Color: Gray
-Weight: 25 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with FINDLAY 3 Pc. Table Set and its Contemporary character. As a living table set, it is designed to complement your space. Finished in Gray tones, the Paper, Rubberwood, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H282" s="54" t="inlineStr">
@@ -36535,14 +36535,14 @@
       </c>
       <c r="G283" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FINDLAY 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. This living table set is made to fit naturally into the room. The Paper, Rubberwood, Engineered Wood construction is complemented by Light Gray tones for a polished look.
-Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Paper, Rubberwood, Engineered Wood.
-Color: Light Gray
-Weight: 25 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FINDLAY 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. This living table set is made to fit naturally into the room. The Paper, Rubberwood, Engineered Wood construction is complemented by Light Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Rubberwood, Engineered Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H283" s="54" t="inlineStr">
@@ -36666,14 +36666,14 @@
       </c>
       <c r="G284" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with FINDLAY 3 Pc. Table Set, styled in Contemporary and designed for everyday comfort. Built as a living table set, it pairs well with a wide range of interiors. With Paper, Rubberwood, Engineered Wood and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Paper, Rubberwood, Engineered Wood.
-Color: White
-Weight: 25 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with FINDLAY 3 Pc. Table Set, styled in Contemporary and designed for everyday comfort. Built as a living table set, it pairs well with a wide range of interiors. With Paper, Rubberwood, Engineered Wood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Rubberwood, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H284" s="54" t="inlineStr">
@@ -36797,12 +36797,12 @@
       </c>
       <c r="G285" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HOLEN 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. Built as a living table set, it pairs well with a wide range of interiors. The Paper Veneer, Engineered Wood construction is complemented by Gray tones for a polished look.
-Product Dimensions: COFFEE TABLE: 36"W X 36"D X 18"H, END TABLE: 24"W X 24"D X 24"H
-Materials: Paper Veneer, Engineered Wood.
-Color: Gray
-Weight: 99.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HOLEN 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. Built as a living table set, it pairs well with a wide range of interiors. The Paper Veneer, Engineered Wood construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 36"W X 36"D X 18"H, END TABLE: 24"W X 24"D X 24"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 99.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H285" s="56" t="inlineStr">
@@ -36926,12 +36926,12 @@
       </c>
       <c r="G286" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with HOLEN 3 Pc. Table Set, styled in Contemporary and designed for everyday comfort. As a living table set, it is designed to complement your space. With Paper Veneer, Engineered Wood and Natural tones, it blends structure and softness in one clean profile.
-Product Dimensions: COFFEE TABLE: 36"W X 36"D X 18"H, END TABLE: 24"W X 24"D X 24"H
-Materials: Paper Veneer, Engineered Wood.
-Color: Natural
-Weight: 99.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with HOLEN 3 Pc. Table Set, styled in Contemporary and designed for everyday comfort. As a living table set, it is designed to complement your space. With Paper Veneer, Engineered Wood and Natural tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 36"W X 36"D X 18"H, END TABLE: 24"W X 24"D X 24"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper Veneer, Engineered Wood.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 99.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H286" s="56" t="inlineStr">
@@ -37055,11 +37055,11 @@
       </c>
       <c r="G287" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with OPHIRA 3 Pc. Table Set, styled in Rustic and designed for everyday comfort. Built as a living table set, it pairs well with a wide range of interiors. With Paper, Metal, Engineered Wood and Dark Brown tones, it blends structure and softness in one clean profile.
-Product Dimensions: COFFEE TABLE: 24"W X 24"D X 18"H, END TABLE: 18.5"W X 18.5"D X 23"H
-Materials: Paper, Metal, Engineered Wood.
-Color: Dark Brown</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with OPHIRA 3 Pc. Table Set, styled in Rustic and designed for everyday comfort. Built as a living table set, it pairs well with a wide range of interiors. With Paper, Metal, Engineered Wood and Dark Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 24"W X 24"D X 18"H, END TABLE: 18.5"W X 18.5"D X 23"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
+Color: Dark Brown&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H287" s="28" t="inlineStr">
@@ -37181,11 +37181,11 @@
       </c>
       <c r="G288" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OPHIRA 3 Pc. Table Set adds a Rustic touch while keeping the room feeling warm and welcoming. As a living table set, it is designed to complement your space. Crafted from Paper, Metal, Engineered Wood, it is finished in Natural tones that pair easily with surrounding decor.
-Product Dimensions: COFFEE TABLE: 24"W X 24"D X 18"H, END TABLE: 18.5"W X 18.5"D X 23"H
-Materials: Paper, Metal, Engineered Wood.
-Color: Natural</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OPHIRA 3 Pc. Table Set adds a Rustic touch while keeping the room feeling warm and welcoming. As a living table set, it is designed to complement your space. Crafted from Paper, Metal, Engineered Wood, it is finished in Natural tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 24"W X 24"D X 18"H, END TABLE: 18.5"W X 18.5"D X 23"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
+Color: Natural&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H288" s="28" t="inlineStr">
@@ -37307,11 +37307,11 @@
       </c>
       <c r="G289" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PALLAS 3 Pc. Table Set brings a Rustic look to your home with a refined, comfortable feel. This living table set is made to fit naturally into the room. The Paper, Metal, Engineered Wood construction is complemented by Black tones for a polished look.
-Product Dimensions: COFFEE TABLE: 41.5"W X 19"D X 18.5"H, END TABLE: 15.5"W X 15.5"D X 23"H
-Materials: Paper, Metal, Engineered Wood.
-Color: Black</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PALLAS 3 Pc. Table Set brings a Rustic look to your home with a refined, comfortable feel. This living table set is made to fit naturally into the room. The Paper, Metal, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 41.5"W X 19"D X 18.5"H, END TABLE: 15.5"W X 15.5"D X 23"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
+Color: Black&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H289" s="52" t="inlineStr">
@@ -37433,11 +37433,11 @@
       </c>
       <c r="G290" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with PALLAS 3 Pc. Table Set, styled in Rustic and designed for everyday comfort. Built as a living table set, it pairs well with a wide range of interiors. With Paper, Metal, Engineered Wood and Natural tones, it blends structure and softness in one clean profile.
-Product Dimensions: COFFEE TABLE: 41.5"W X 19"D X 18.5"H, END TABLE: 15.5"W X 15.5"D X 23"H
-Materials: Paper, Metal, Engineered Wood.
-Color: Natural</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with PALLAS 3 Pc. Table Set, styled in Rustic and designed for everyday comfort. Built as a living table set, it pairs well with a wide range of interiors. With Paper, Metal, Engineered Wood and Natural tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 41.5"W X 19"D X 18.5"H, END TABLE: 15.5"W X 15.5"D X 23"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
+Color: Natural&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H290" s="52" t="inlineStr">
@@ -37559,11 +37559,11 @@
       </c>
       <c r="G291" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PALLAS 3 Pc. Table Set adds a Rustic touch while keeping the room feeling warm and welcoming. As a living table set, it is designed to complement your space. Crafted from Paper, Metal, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: COFFEE TABLE: 41.5"W X 19"D X 18.5"H, END TABLE: 15.5"W X 15.5"D X 23"H
-Materials: Paper, Metal, Engineered Wood.
-Color: White</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PALLAS 3 Pc. Table Set adds a Rustic touch while keeping the room feeling warm and welcoming. As a living table set, it is designed to complement your space. Crafted from Paper, Metal, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 41.5"W X 19"D X 18.5"H, END TABLE: 15.5"W X 15.5"D X 23"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
+Color: White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H291" s="52" t="inlineStr">
@@ -37685,11 +37685,11 @@
       </c>
       <c r="G292" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-RONDE 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. Built as a living table set, it pairs well with a wide range of interiors. The Paper, Metal, Engineered Wood construction is complemented by Natural tones for a polished look.
-Product Dimensions: COFFEE TABLE: 34"W X 34"D X 18"H, END TABLE: 18"W X 18"D X 23"H
-Materials: Paper, Metal, Engineered Wood.
-Color: Natural</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+RONDE 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. Built as a living table set, it pairs well with a wide range of interiors. The Paper, Metal, Engineered Wood construction is complemented by Natural tones for a polished look.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 34"W X 34"D X 18"H, END TABLE: 18"W X 18"D X 23"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
+Color: Natural&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H292" s="24" t="inlineStr">
@@ -37811,11 +37811,11 @@
       </c>
       <c r="G293" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with RONDE 3 Pc. Table Set, styled in Contemporary and designed for everyday comfort. As a living table set, it is designed to complement your space. With Paper, Metal, Engineered Wood and White tones, it blends structure and softness in one clean profile.
-Product Dimensions: COFFEE TABLE: 34"W X 34"D X 18"H, END TABLE: 18"W X 18"D X 23"H
-Materials: Paper, Metal, Engineered Wood.
-Color: White</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with RONDE 3 Pc. Table Set, styled in Contemporary and designed for everyday comfort. As a living table set, it is designed to complement your space. With Paper, Metal, Engineered Wood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 34"W X 34"D X 18"H, END TABLE: 18"W X 18"D X 23"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
+Color: White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H293" s="24" t="inlineStr">
@@ -37937,12 +37937,12 @@
       </c>
       <c r="G294" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with WHETSTONE 3 Pc. Table Set and its Contemporary character. This living table set is made to fit naturally into the room. Finished in Black tones, the Paper, Metal, Engineered Wood build balances durability with visual appeal.
-Product Dimensions: COFFEE TABLE: 31.5"W X 30.5"D X 17"H, END TABLE: 15.5"W X 15"D X 22.5"H
-Materials: Paper, Metal, Engineered Wood.
-Color: Black
-Weight: 25 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with WHETSTONE 3 Pc. Table Set and its Contemporary character. This living table set is made to fit naturally into the room. Finished in Black tones, the Paper, Metal, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 31.5"W X 30.5"D X 17"H, END TABLE: 15.5"W X 15"D X 22.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H294" s="56" t="inlineStr">
@@ -38066,12 +38066,12 @@
       </c>
       <c r="G295" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WHETSTONE 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. Built as a living table set, it pairs well with a wide range of interiors. The Paper, Metal, Engineered Wood construction is complemented by White tones for a polished look.
-Product Dimensions: COFFEE TABLE: 31.5"W X 30.5"D X 17"H, END TABLE: 15.5"W X 15"D X 22.5"H
-Materials: Paper, Metal, Engineered Wood.
-Color: White
-Weight: 25 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WHETSTONE 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. Built as a living table set, it pairs well with a wide range of interiors. The Paper, Metal, Engineered Wood construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 31.5"W X 30.5"D X 17"H, END TABLE: 15.5"W X 15"D X 22.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H295" s="56" t="inlineStr">
@@ -38194,14 +38194,14 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BRAMPTON 3 Pc. Table Set brings a Traditional look to your home with a refined, comfortable feel. This living occasional set is made to fit naturally into the room. The Faux Marble, Solid Wood, Wood Veneer, construction is complemented by Espresso or Black tones for a polished look.
-Product Dimensions: 48"L X 26"W X 19 3/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Faux Marble, Solid Wood, Wood Veneer.
-Color: Espresso or Black
-Weight: 99.22 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BRAMPTON 3 Pc. Table Set brings a Traditional look to your home with a refined, comfortable feel. This living occasional set is made to fit naturally into the room. The Faux Marble, Solid Wood, Wood Veneer, construction is complemented by Espresso or Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 48"L X 26"W X 19 3/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Faux Marble, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Espresso or Black&lt;br&gt;
+Weight: 99.22 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -38327,14 +38327,14 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BRYANNA 3 Pc. Set, styled in Rustic and designed for everyday comfort. As a living occasional set, it is designed to complement your space. With Solid Wood, Wood Veneer, and Antique Light Oak tones, it blends structure and softness in one clean profile.
-Product Dimensions: 22"L X 24"W X 23"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Antique Light Oak
-Weight: 102.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BRYANNA 3 Pc. Set, styled in Rustic and designed for everyday comfort. As a living occasional set, it is designed to complement your space. With Solid Wood, Wood Veneer, and Antique Light Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 22"L X 24"W X 23"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Antique Light Oak&lt;br&gt;
+Weight: 102.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -38460,14 +38460,14 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with BUNBURY 3 Pc. Coffee Table Set and its Traditional character. This living occasional set is made to fit naturally into the room. Finished in Cherry tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 48"L X 26"W X 19 1/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Cherry
-Weight: 112.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with BUNBURY 3 Pc. Coffee Table Set and its Traditional character. This living occasional set is made to fit naturally into the room. Finished in Cherry tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 48"L X 26"W X 19 1/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Cherry&lt;br&gt;
+Weight: 112.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -38588,15 +38588,15 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CHESHIRE 3 Pc. Table Set brings a Traditional look to your home with a refined, comfortable feel. This living occasional set is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Dark Cherry tones for a polished look.
-Product Dimensions: 47 3/4"L X 23 1/2"W X 18"H
-Features
-- Made with solid wood &amp; wood veneer
-- Elegant cabriole legs
-Materials: Solid Wood, Wood Veneer.
-Color: Dark Cherry
-Weight: 81.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CHESHIRE 3 Pc. Table Set brings a Traditional look to your home with a refined, comfortable feel. This living occasional set is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Dark Cherry tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 3/4"L X 23 1/2"W X 18"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;br&gt;
+- Elegant cabriole legs&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Cherry&lt;br&gt;
+Weight: 81.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -38722,14 +38722,14 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with LECHESTER 3 Pc. Coffee Table Set w/ Faux Marble, styled in Traditional and designed for everyday comfort. Built as a living occasional set, it pairs well with a wide range of interiors. With Faux Marble, Solid Wood, Wood Veneer, and Dark Oak or Ivory tones, it blends structure and softness in one clean profile.
-Product Dimensions: 48"L X 24"W X 18 1/4"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Faux Marble, Solid Wood, Wood Veneer.
-Color: Dark Oak or Ivory
-Weight: 99 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with LECHESTER 3 Pc. Coffee Table Set w/ Faux Marble, styled in Traditional and designed for everyday comfort. Built as a living occasional set, it pairs well with a wide range of interiors. With Faux Marble, Solid Wood, Wood Veneer, and Dark Oak or Ivory tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 48"L X 24"W X 18 1/4"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Faux Marble, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Dark Oak or Ivory&lt;br&gt;
+Weight: 99 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -38855,14 +38855,14 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with LODIVEA 3 Pc. Coffee Table Set w/ Faux Marble and its Transitional character. This living occasional set is made to fit naturally into the room. Finished in Black tones, the Solid Wood, Paper Veneer, build balances durability with visual appeal.
-Product Dimensions: COFFEE TABLE: 48"L X 24"W X 19"H, END TABLE: 22"L X 24"W X 24"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Paper Veneer.
-Color: Black
-Weight: 95 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with LODIVEA 3 Pc. Coffee Table Set w/ Faux Marble and its Transitional character. This living occasional set is made to fit naturally into the room. Finished in Black tones, the Solid Wood, Paper Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 48"L X 24"W X 19"H, END TABLE: 22"L X 24"W X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Paper Veneer.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 95 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -38983,14 +38983,14 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MONANGO 3 Pc. Table Set adds a Rustic touch while keeping the room feeling warm and welcoming. As a living occasional set, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Weathered Gray tones that pair easily with surrounding decor.
-Product Dimensions: COFFEE TABLE: 46 1/8"L X 23"W X 19 1/8"H, END TABLE: 20 7/8"L X 20 7/8"W X 23 7/8"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Solid Wood, Wood Veneer.
-Color: Weathered Gray
-Weight: 107 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MONANGO 3 Pc. Table Set adds a Rustic touch while keeping the room feeling warm and welcoming. As a living occasional set, it is designed to complement your space. Crafted from Solid Wood, Wood Veneer, it is finished in Weathered Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 46 1/8"L X 23"W X 19 1/8"H, END TABLE: 20 7/8"L X 20 7/8"W X 23 7/8"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Weathered Gray&lt;br&gt;
+Weight: 107 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -39111,12 +39111,12 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with OLBIA 3 Pc. Coffee Table Set, styled in Industrial and designed for everyday comfort. As a living occasional set, it is designed to complement your space. With Steel, Paper Veneer, and Rustic Oak or Sand Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: COFFEE TABLE: 47 1/4"L X 23 5/8"W X 18"H, END TABLE: 23 5/8"DIA X 22"H
-Materials: Steel, Paper Veneer.
-Color: Rustic Oak or Sand Black
-Weight: 91.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with OLBIA 3 Pc. Coffee Table Set, styled in Industrial and designed for everyday comfort. As a living occasional set, it is designed to complement your space. With Steel, Paper Veneer, and Rustic Oak or Sand Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: COFFEE TABLE: 47 1/4"L X 23 5/8"W X 18"H, END TABLE: 23 5/8"DIA X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Paper Veneer.&lt;br&gt;
+Color: Rustic Oak or Sand Black&lt;br&gt;
+Weight: 91.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -39242,14 +39242,14 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ORBE 3 Pc. Table Set and its Contemporary character. This living occasional set is made to fit naturally into the room. Finished in Espresso tones, the Tempered Glass, Solid Wood, Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 38"DIA X 19H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Tempered Glass, Solid Wood, Wood Veneer.
-Color: Espresso
-Weight: 154 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ORBE 3 Pc. Table Set and its Contemporary character. This living occasional set is made to fit naturally into the room. Finished in Espresso tones, the Tempered Glass, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 38"DIA X 19H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Tempered Glass, Solid Wood, Wood Veneer.&lt;br&gt;
+Color: Espresso&lt;br&gt;
+Weight: 154 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -39371,12 +39371,12 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GARIBALDI TV Stand brings a Rustic Farmhouse look to your home with a refined, comfortable feel. Built as a living tv stand, it pairs well with a wide range of interiors. The Paper, Engineered Wood, Metal construction is complemented by Brown or Gray tones for a polished look.
-Product Dimensions: 56"W X 16"D X 28"H Bonus storage &amp; convenience features (from matching set pieces): Sliding Drawer Doors
-Materials: Paper, Engineered Wood, Metal.
-Color: Brown or Gray
-Weight: 82.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GARIBALDI TV Stand brings a Rustic Farmhouse look to your home with a refined, comfortable feel. Built as a living tv stand, it pairs well with a wide range of interiors. The Paper, Engineered Wood, Metal construction is complemented by Brown or Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 56"W X 16"D X 28"H Bonus storage &amp;amp; convenience features (from matching set pieces): Sliding Drawer Doors&lt;/p&gt;
+&lt;p&gt;Materials: Paper, Engineered Wood, Metal.&lt;br&gt;
+Color: Brown or Gray&lt;br&gt;
+Weight: 82.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -39497,11 +39497,11 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HEPBURNE 70" TV Stand adds a LED Light on Pier touch while keeping the room feeling warm and welcoming. This living tv stand is made to fit naturally into the room. Crafted from Gold-Capped Legs, it is finished in Adjustable Shelves tones that pair easily with surrounding decor.
-Product Dimensions: 70"W X 18"D X 30"H
-Materials: Gold-Capped Legs.
-Color: Adjustable Shelves</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HEPBURNE 70" TV Stand adds a LED Light on Pier touch while keeping the room feeling warm and welcoming. This living tv stand is made to fit naturally into the room. Crafted from Gold-Capped Legs, it is finished in Adjustable Shelves tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 70"W X 18"D X 30"H&lt;/p&gt;
+&lt;p&gt;Materials: Gold-Capped Legs.&lt;br&gt;
+Color: Adjustable Shelves&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -39619,12 +39619,12 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-IDANHA TV Stand brings a Mid-century Modern look to your home with a refined, comfortable feel. Built as a living tv stand, it pairs well with a wide range of interiors. The Engineered Wood, Metal construction is complemented by Natural tones for a polished look.
-Product Dimensions: 56"W X 16"D X 32"H
-Materials: Engineered Wood, Metal.
-Color: Natural
-Weight: 81.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+IDANHA TV Stand brings a Mid-century Modern look to your home with a refined, comfortable feel. Built as a living tv stand, it pairs well with a wide range of interiors. The Engineered Wood, Metal construction is complemented by Natural tones for a polished look.&lt;br&gt;
+Product Dimensions: 56"W X 16"D X 32"H&lt;/p&gt;
+&lt;p&gt;Materials: Engineered Wood, Metal.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 81.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -39745,11 +39745,11 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WESTERHAM 70" TV Stand brings a Modern look to your home with a refined, comfortable feel. This living tv stand is made to fit naturally into the room. The Solid Rubberwood, Cherry Veneer, Poplar Burl Veneer construction is complemented by Dark Cherry tones for a polished look.
-Product Dimensions: 70"W X 18"D X 30"H Bonus storage &amp; convenience features (from matching set pieces): Felt-Lined Drawer and LED on End Table
-Materials: Solid Rubberwood, Cherry Veneer, Poplar Burl Veneer.
-Color: Dark Cherry</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WESTERHAM 70" TV Stand brings a Modern look to your home with a refined, comfortable feel. This living tv stand is made to fit naturally into the room. The Solid Rubberwood, Cherry Veneer, Poplar Burl Veneer construction is complemented by Dark Cherry tones for a polished look.&lt;br&gt;
+Product Dimensions: 70"W X 18"D X 30"H Bonus storage &amp;amp; convenience features (from matching set pieces): Felt-Lined Drawer and LED on End Table&lt;/p&gt;
+&lt;p&gt;Materials: Solid Rubberwood, Cherry Veneer, Poplar Burl Veneer.&lt;br&gt;
+Color: Dark Cherry&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -39867,14 +39867,14 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ORKDAL Coffee Table adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a living table, it pairs well with a wide range of interiors. Crafted from Wood Veneer, it is finished in Walnut tones that pair easily with surrounding decor.
-Product Dimensions: 49"W X 32"D X 18"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Wood Veneer.
-Color: Walnut
-Weight: 55 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ORKDAL Coffee Table adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a living table, it pairs well with a wide range of interiors. Crafted from Wood Veneer, it is finished in Walnut tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 49"W X 32"D X 18"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Wood Veneer.&lt;br&gt;
+Color: Walnut&lt;br&gt;
+Weight: 55 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -39995,14 +39995,14 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ORKDAL End Table and its Transitional character. As a living table, it is designed to complement your space. Finished in Walnut tones, the Wood Veneer, build balances durability with visual appeal.
-Product Dimensions: 31"W X 27"D X 24"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Wood Veneer.
-Color: Walnut
-Weight: 31.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ORKDAL End Table and its Transitional character. As a living table, it is designed to complement your space. Finished in Walnut tones, the Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 31"W X 27"D X 24"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Wood Veneer.&lt;br&gt;
+Color: Walnut&lt;br&gt;
+Weight: 31.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -40123,14 +40123,14 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ORKDAL Sofa Table brings a Transitional look to your home with a refined, comfortable feel. This living table is made to fit naturally into the room. The Wood Veneer, construction is complemented by Walnut tones for a polished look.
-Product Dimensions: 49"W X 23.5"D X 31"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Wood Veneer.
-Color: Walnut
-Weight: 44 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ORKDAL Sofa Table brings a Transitional look to your home with a refined, comfortable feel. This living table is made to fit naturally into the room. The Wood Veneer, construction is complemented by Walnut tones for a polished look.&lt;br&gt;
+Product Dimensions: 49"W X 23.5"D X 31"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Wood Veneer.&lt;br&gt;
+Color: Walnut&lt;br&gt;
+Weight: 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">

--- a/FOA Singles/Living-Single.xlsx
+++ b/FOA Singles/Living-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD311"/>
+  <dimension ref="A1:AG311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,6 +780,21 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Variable tags</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Product Category</t>
         </is>
       </c>
     </row>
@@ -907,7 +922,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Living, TV Console, ALMA</t>
+          <t>Living, TV Console, ALMA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1065,22 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Living, TV Console, ALMA</t>
+          <t>Living, TV Console, ALMA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1206,22 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Living, TV Console, BLAIR</t>
+          <t>Living, TV Console, BLAIR, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1352,22 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Living, TV Console, BORREGO</t>
+          <t>Living, TV Console, BORREGO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1498,22 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Living, TV Console, BORREGO</t>
+          <t>Living, TV Console, BORREGO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1641,22 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Living, TV Console, BROMOAK</t>
+          <t>Living, TV Console, BROMOAK, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1784,22 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Living, TV Console, BROMOAK</t>
+          <t>Living, TV Console, BROMOAK, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1927,22 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Living, TV Console, BROMOAK</t>
+          <t>Living, TV Console, BROMOAK, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -1935,7 +2070,22 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Living, TV Console, BROMOAK</t>
+          <t>Living, TV Console, BROMOAK, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2213,22 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Living, TV Console, BROMOAK</t>
+          <t>Living, TV Console, BROMOAK, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2357,22 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Living, TV Console, CERRO</t>
+          <t>Living, TV Console, CERRO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2501,22 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Living, TV Console, CERRO</t>
+          <t>Living, TV Console, CERRO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2642,22 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Living, TV Console, DIETRICH</t>
+          <t>Living, TV Console, DIETRICH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2783,22 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Living, TV Console, EGALEO</t>
+          <t>Living, TV Console, EGALEO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2927,22 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Living, TV Console, ERNST</t>
+          <t>Living, TV Console, ERNST, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -2831,7 +3071,22 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Living, TV Console, ERNST</t>
+          <t>Living, TV Console, ERNST, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -2957,7 +3212,22 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Living, TV Console, EVOS</t>
+          <t>Living, TV Console, EVOS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3355,22 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Living, TV Console, GEORGIA</t>
+          <t>Living, TV Console, GEORGIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3498,22 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Living, TV Console, GEORGIA</t>
+          <t>Living, TV Console, GEORGIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3635,22 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Living, TV Console, KEBBYLL</t>
+          <t>Living, TV Console, KEBBYLL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3776,22 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Living, TV Console, KEBBYLL</t>
+          <t>Living, TV Console, KEBBYLL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3917,22 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Living, TV Console, KEBBYLL</t>
+          <t>Living, TV Console, KEBBYLL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -3709,7 +4054,22 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Living, TV Console, NEAPOLI</t>
+          <t>Living, TV Console, NEAPOLI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -3835,7 +4195,22 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Living, TV Console, NINOVE</t>
+          <t>Living, TV Console, NINOVE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -3963,7 +4338,22 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Living, TV Console, PRESHO</t>
+          <t>Living, TV Console, PRESHO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4479,22 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Living, TV Console, SABUGAL</t>
+          <t>Living, TV Console, SABUGAL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4620,22 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Living, TV Console, SABUGAL</t>
+          <t>Living, TV Console, SABUGAL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4761,22 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Living, TV Console, SILVER CREEK</t>
+          <t>Living, TV Console, SILVER CREEK, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4902,22 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Living, TV Console, SILVER CREEK</t>
+          <t>Living, TV Console, SILVER CREEK, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -4589,7 +5039,22 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, ALVISE</t>
+          <t>Living, Coffee Table, ALVISE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -4717,7 +5182,22 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, ARLINGTON</t>
+          <t>Living, Coffee Table, ARLINGTON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -4841,7 +5321,22 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, ATWOOD II</t>
+          <t>Living, Coffee Table, ATWOOD II, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -4969,7 +5464,22 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, AUGSBURG</t>
+          <t>Living, Coffee Table, AUGSBURG, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5609,22 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, BACERRA</t>
+          <t>Living, Coffee Table, BACERRA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5746,22 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, BATAM II</t>
+          <t>Living, Coffee Table, BATAM II, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5883,22 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, BIMA II</t>
+          <t>Living, Coffee Table, BIMA II, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -5465,7 +6020,22 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, BISHOP</t>
+          <t>Living, Coffee Table, BISHOP, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -5593,7 +6163,22 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, CALANDRA</t>
+          <t>Living, Coffee Table, CALANDRA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -5721,7 +6306,22 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, CARRIE</t>
+          <t>Living, Coffee Table, CARRIE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -5852,7 +6452,22 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, CONISBROUGH</t>
+          <t>Living, Coffee Table, CONISBROUGH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -5983,7 +6598,22 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, CONISBROUGH</t>
+          <t>Living, Coffee Table, CONISBROUGH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6742,22 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, COOKSHIRE</t>
+          <t>Living, Coffee Table, COOKSHIRE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6885,22 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, CORINNE</t>
+          <t>Living, Coffee Table, CORINNE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -6368,7 +7028,22 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, CRYSTAL COVE II</t>
+          <t>Living, Coffee Table, CRYSTAL COVE II, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -6496,7 +7171,22 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, CRYSTAL FALLS</t>
+          <t>Living, Coffee Table, CRYSTAL FALLS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -6625,7 +7315,22 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, DUBENDORF</t>
+          <t>Living, Coffee Table, DUBENDORF, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -6754,7 +7459,22 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, DUBENDORF</t>
+          <t>Living, Coffee Table, DUBENDORF, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -6880,7 +7600,22 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, EIMEAR</t>
+          <t>Living, Coffee Table, EIMEAR, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7743,22 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, FINLEY</t>
+          <t>Living, Coffee Table, FINLEY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7891,22 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, GIORDANI</t>
+          <t>Living, Coffee Table, GIORDANI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -7269,7 +8034,22 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, GRANVIA</t>
+          <t>Living, Coffee Table, GRANVIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -7396,7 +8176,22 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, GRASTEN</t>
+          <t>Living, Coffee Table, GRASTEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -7531,7 +8326,22 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, GUIS</t>
+          <t>Living, Coffee Table, GUIS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -7666,7 +8476,22 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, GUIS</t>
+          <t>Living, Coffee Table, GUIS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -7795,7 +8620,22 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, HALCASTER</t>
+          <t>Living, Coffee Table, HALCASTER, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -7926,7 +8766,22 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, HALEWOOD</t>
+          <t>Living, Coffee Table, HALEWOOD, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -8053,7 +8908,22 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, HALEWOOD</t>
+          <t>Living, Coffee Table, HALEWOOD, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -8175,7 +9045,22 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, IZAR</t>
+          <t>Living, Coffee Table, IZAR, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -8303,7 +9188,22 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, JOLIET</t>
+          <t>Living, Coffee Table, JOLIET, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -8431,7 +9331,22 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, JOLIET</t>
+          <t>Living, Coffee Table, JOLIET, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -8562,7 +9477,22 @@
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, KOBLENZ</t>
+          <t>Living, Coffee Table, KOBLENZ, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -8693,7 +9623,22 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, KOBLENZ</t>
+          <t>Living, Coffee Table, KOBLENZ, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -8815,7 +9760,22 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, LAILA</t>
+          <t>Living, Coffee Table, LAILA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -8946,7 +9906,22 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, LOBB</t>
+          <t>Living, Coffee Table, LOBB, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -9068,7 +10043,22 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, LODIA</t>
+          <t>Living, Coffee Table, LODIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -9195,7 +10185,22 @@
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, LODIA III</t>
+          <t>Living, Coffee Table, LODIA III, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -9322,7 +10327,22 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, LODIA III</t>
+          <t>Living, Coffee Table, LODIA III, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -9448,7 +10468,22 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, LUDVIG</t>
+          <t>Living, Coffee Table, LUDVIG, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -9576,7 +10611,22 @@
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MAJKEN</t>
+          <t>Living, Coffee Table, MAJKEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -9700,7 +10750,22 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MANHATTAN IV</t>
+          <t>Living, Coffee Table, MANHATTAN IV, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -9824,7 +10889,22 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MANHATTAN IV</t>
+          <t>Living, Coffee Table, MANHATTAN IV, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -9948,7 +11028,22 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MANHATTAN IV</t>
+          <t>Living, Coffee Table, MANHATTAN IV, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -10077,7 +11172,22 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MANNEDORF</t>
+          <t>Living, Coffee Table, MANNEDORF, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -10206,7 +11316,22 @@
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MANNEDORF</t>
+          <t>Living, Coffee Table, MANNEDORF, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -10338,7 +11463,22 @@
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MARSTON</t>
+          <t>Living, Coffee Table, MARSTON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -10470,7 +11610,22 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MARSTON</t>
+          <t>Living, Coffee Table, MARSTON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -10596,7 +11751,22 @@
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MAY</t>
+          <t>Living, Coffee Table, MAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -10722,7 +11892,22 @@
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MAY</t>
+          <t>Living, Coffee Table, MAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -10850,7 +12035,22 @@
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MEADOW</t>
+          <t>Living, Coffee Table, MEADOW, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -10978,7 +12178,22 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MEADOW</t>
+          <t>Living, Coffee Table, MEADOW, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -11105,7 +12320,22 @@
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MEDA</t>
+          <t>Living, Coffee Table, MEDA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -11236,7 +12466,22 @@
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MIKA</t>
+          <t>Living, Coffee Table, MIKA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -11367,7 +12612,22 @@
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MIKA</t>
+          <t>Living, Coffee Table, MIKA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -11495,7 +12755,22 @@
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, MOA</t>
+          <t>Living, Coffee Table, MOA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -11622,7 +12897,22 @@
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, NAHARA</t>
+          <t>Living, Coffee Table, NAHARA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -11749,7 +13039,22 @@
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, NAHARA</t>
+          <t>Living, Coffee Table, NAHARA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -11876,7 +13181,22 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, NAHARA</t>
+          <t>Living, Coffee Table, NAHARA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -12005,7 +13325,22 @@
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, NINOVE</t>
+          <t>Living, Coffee Table, NINOVE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -12134,7 +13469,22 @@
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, NINOVE</t>
+          <t>Living, Coffee Table, NINOVE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -12261,7 +13611,22 @@
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, NORTHWICH</t>
+          <t>Living, Coffee Table, NORTHWICH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -12388,7 +13753,22 @@
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, NORTHWICH</t>
+          <t>Living, Coffee Table, NORTHWICH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -12510,7 +13890,22 @@
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, NORTHWICH</t>
+          <t>Living, Coffee Table, NORTHWICH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -12632,7 +14027,22 @@
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, NOVA</t>
+          <t>Living, Coffee Table, NOVA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -12760,7 +14170,22 @@
       </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, OAKWAY</t>
+          <t>Living, Coffee Table, OAKWAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -12882,7 +14307,22 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, ORLA II</t>
+          <t>Living, Coffee Table, ORLA II, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -13013,7 +14453,22 @@
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, ORRIN</t>
+          <t>Living, Coffee Table, ORRIN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -13139,7 +14594,22 @@
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, POLTIMORE</t>
+          <t>Living, Coffee Table, POLTIMORE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -13265,7 +14735,22 @@
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, RAYA</t>
+          <t>Living, Coffee Table, RAYA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -13401,7 +14886,22 @@
       </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, ROCHESTER</t>
+          <t>Living, Coffee Table, ROCHESTER, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -13533,7 +15033,22 @@
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, ROCHESTER</t>
+          <t>Living, Coffee Table, ROCHESTER, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -13661,7 +15176,22 @@
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, ROSETTA</t>
+          <t>Living, Coffee Table, ROSETTA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -13783,7 +15313,22 @@
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, ROXO</t>
+          <t>Living, Coffee Table, ROXO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -13909,7 +15454,22 @@
       </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, RYLEE</t>
+          <t>Living, Coffee Table, RYLEE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -14031,7 +15591,22 @@
       </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, SINDAL</t>
+          <t>Living, Coffee Table, SINDAL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -14153,7 +15728,22 @@
       </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, SINDAL</t>
+          <t>Living, Coffee Table, SINDAL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -14275,7 +15865,22 @@
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, SLOANE</t>
+          <t>Living, Coffee Table, SLOANE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -14406,7 +16011,22 @@
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, STATEN</t>
+          <t>Living, Coffee Table, STATEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -14537,7 +16157,22 @@
       </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, STATEN</t>
+          <t>Living, Coffee Table, STATEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -14663,7 +16298,22 @@
       </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, SUNDANCE</t>
+          <t>Living, Coffee Table, SUNDANCE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -14785,7 +16435,22 @@
       </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, SURDAL</t>
+          <t>Living, Coffee Table, SURDAL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -14907,7 +16572,22 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, SURDAL</t>
+          <t>Living, Coffee Table, SURDAL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -15036,7 +16716,22 @@
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, TADCASTER</t>
+          <t>Living, Coffee Table, TADCASTER, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -15158,7 +16853,22 @@
       </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, TANIKA</t>
+          <t>Living, Coffee Table, TANIKA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -15286,7 +16996,22 @@
       </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, THISTED</t>
+          <t>Living, Coffee Table, THISTED, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -15414,7 +17139,22 @@
       </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, THISTED</t>
+          <t>Living, Coffee Table, THISTED, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -15540,7 +17280,22 @@
       </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, TITUS</t>
+          <t>Living, Coffee Table, TITUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -15666,7 +17421,22 @@
       </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, TORKEL</t>
+          <t>Living, Coffee Table, TORKEL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -15788,7 +17558,22 @@
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, VALO</t>
+          <t>Living, Coffee Table, VALO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -15912,7 +17697,22 @@
       </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, VILLARSGLANE</t>
+          <t>Living, Coffee Table, VILLARSGLANE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -16038,7 +17838,22 @@
       </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, VIRDEN</t>
+          <t>Living, Coffee Table, VIRDEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -16164,7 +17979,22 @@
       </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, VIRDEN</t>
+          <t>Living, Coffee Table, VIRDEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -16290,7 +18120,22 @@
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, VIRDEN</t>
+          <t>Living, Coffee Table, VIRDEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -16416,7 +18261,22 @@
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, VIRDEN</t>
+          <t>Living, Coffee Table, VIRDEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -16545,7 +18405,22 @@
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, WALWORTH</t>
+          <t>Living, Coffee Table, WALWORTH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -16667,7 +18542,22 @@
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, WESTERHAM</t>
+          <t>Living, Coffee Table, WESTERHAM, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -16791,7 +18681,22 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, WETTINGEN</t>
+          <t>Living, Coffee Table, WETTINGEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -16924,7 +18829,22 @@
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, WETZIKON</t>
+          <t>Living, Coffee Table, WETZIKON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -17057,7 +18977,22 @@
       </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, WETZIKON</t>
+          <t>Living, Coffee Table, WETZIKON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -17179,7 +19114,22 @@
       </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, XANTHUS</t>
+          <t>Living, Coffee Table, XANTHUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -17305,7 +19255,22 @@
       </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>Living, Coffee Table, ZOLA</t>
+          <t>Living, Coffee Table, ZOLA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -17427,7 +19392,22 @@
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>Living, End Table, ALVISE</t>
+          <t>Living, End Table, ALVISE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -17555,7 +19535,22 @@
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>Living, End Table, ARLINGTON</t>
+          <t>Living, End Table, ARLINGTON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -17679,7 +19674,22 @@
       </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>Living, End Table, ATWOOD II</t>
+          <t>Living, End Table, ATWOOD II, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -17807,7 +19817,22 @@
       </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>Living, End Table, AUGSBURG</t>
+          <t>Living, End Table, AUGSBURG, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -17935,7 +19960,22 @@
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>Living, End Table, BACERRA</t>
+          <t>Living, End Table, BACERRA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -18057,7 +20097,22 @@
       </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>Living, End Table, BATAM II</t>
+          <t>Living, End Table, BATAM II, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -18183,7 +20238,22 @@
       </c>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>Living, End Table, BIMA II</t>
+          <t>Living, End Table, BIMA II, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -18305,7 +20375,22 @@
       </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>Living, End Table, BISHOP</t>
+          <t>Living, End Table, BISHOP, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -18433,7 +20518,22 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>Living, End Table, CALANDRA</t>
+          <t>Living, End Table, CALANDRA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -18561,7 +20661,22 @@
       </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>Living, End Table, CARRIE</t>
+          <t>Living, End Table, CARRIE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -18692,7 +20807,22 @@
       </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>Living, End Table, CONISBROUGH</t>
+          <t>Living, End Table, CONISBROUGH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -18821,7 +20951,22 @@
       </c>
       <c r="AD143" t="inlineStr">
         <is>
-          <t>Living, End Table, COOKSHIRE</t>
+          <t>Living, End Table, COOKSHIRE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -18949,7 +21094,22 @@
       </c>
       <c r="AD144" t="inlineStr">
         <is>
-          <t>Living, End Table, CORINNE</t>
+          <t>Living, End Table, CORINNE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -19077,7 +21237,22 @@
       </c>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>Living, End Table, CRYSTAL FALLS</t>
+          <t>Living, End Table, CRYSTAL FALLS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -19206,7 +21381,22 @@
       </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>Living, End Table, DUBENDORF</t>
+          <t>Living, End Table, DUBENDORF, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -19335,7 +21525,22 @@
       </c>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>Living, End Table, DUBENDORF</t>
+          <t>Living, End Table, DUBENDORF, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -19461,7 +21666,22 @@
       </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>Living, End Table, EIMEAR</t>
+          <t>Living, End Table, EIMEAR, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -19589,7 +21809,22 @@
       </c>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>Living, End Table, FINLEY</t>
+          <t>Living, End Table, FINLEY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -19722,7 +21957,22 @@
       </c>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>Living, End Table, GIORDANI</t>
+          <t>Living, End Table, GIORDANI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -19850,7 +22100,22 @@
       </c>
       <c r="AD151" t="inlineStr">
         <is>
-          <t>Living, End Table, GRANVIA</t>
+          <t>Living, End Table, GRANVIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -19981,7 +22246,22 @@
       </c>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>Living, End Table, GRASTEN</t>
+          <t>Living, End Table, GRASTEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -20110,7 +22390,22 @@
       </c>
       <c r="AD153" t="inlineStr">
         <is>
-          <t>Living, End Table, HALCASTER</t>
+          <t>Living, End Table, HALCASTER, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -20241,7 +22536,22 @@
       </c>
       <c r="AD154" t="inlineStr">
         <is>
-          <t>Living, End Table, HALEWOOD</t>
+          <t>Living, End Table, HALEWOOD, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -20368,7 +22678,22 @@
       </c>
       <c r="AD155" t="inlineStr">
         <is>
-          <t>Living, End Table, HALEWOOD</t>
+          <t>Living, End Table, HALEWOOD, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -20490,7 +22815,22 @@
       </c>
       <c r="AD156" t="inlineStr">
         <is>
-          <t>Living, End Table, IZAR</t>
+          <t>Living, End Table, IZAR, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -20618,7 +22958,22 @@
       </c>
       <c r="AD157" t="inlineStr">
         <is>
-          <t>Living, End Table, JOLIET</t>
+          <t>Living, End Table, JOLIET, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -20749,7 +23104,22 @@
       </c>
       <c r="AD158" t="inlineStr">
         <is>
-          <t>Living, End Table, KOBLENZ</t>
+          <t>Living, End Table, KOBLENZ, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -20880,7 +23250,22 @@
       </c>
       <c r="AD159" t="inlineStr">
         <is>
-          <t>Living, End Table, KOBLENZ</t>
+          <t>Living, End Table, KOBLENZ, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -21002,7 +23387,22 @@
       </c>
       <c r="AD160" t="inlineStr">
         <is>
-          <t>Living, End Table, LAILA</t>
+          <t>Living, End Table, LAILA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -21133,7 +23533,22 @@
       </c>
       <c r="AD161" t="inlineStr">
         <is>
-          <t>Living, End Table, LOBB</t>
+          <t>Living, End Table, LOBB, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -21255,7 +23670,22 @@
       </c>
       <c r="AD162" t="inlineStr">
         <is>
-          <t>Living, End Table, LODIA</t>
+          <t>Living, End Table, LODIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -21382,7 +23812,22 @@
       </c>
       <c r="AD163" t="inlineStr">
         <is>
-          <t>Living, End Table, LODIA III</t>
+          <t>Living, End Table, LODIA III, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -21509,7 +23954,22 @@
       </c>
       <c r="AD164" t="inlineStr">
         <is>
-          <t>Living, End Table, LODIA III</t>
+          <t>Living, End Table, LODIA III, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -21635,7 +24095,22 @@
       </c>
       <c r="AD165" t="inlineStr">
         <is>
-          <t>Living, End Table, LUDVIG</t>
+          <t>Living, End Table, LUDVIG, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -21763,7 +24238,22 @@
       </c>
       <c r="AD166" t="inlineStr">
         <is>
-          <t>Living, End Table, MAJKEN</t>
+          <t>Living, End Table, MAJKEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -21892,7 +24382,22 @@
       </c>
       <c r="AD167" t="inlineStr">
         <is>
-          <t>Living, End Table, MANNEDORF</t>
+          <t>Living, End Table, MANNEDORF, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -22021,7 +24526,22 @@
       </c>
       <c r="AD168" t="inlineStr">
         <is>
-          <t>Living, End Table, MANNEDORF</t>
+          <t>Living, End Table, MANNEDORF, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -22153,7 +24673,22 @@
       </c>
       <c r="AD169" t="inlineStr">
         <is>
-          <t>Living, End Table, MARSTON</t>
+          <t>Living, End Table, MARSTON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -22285,7 +24820,22 @@
       </c>
       <c r="AD170" t="inlineStr">
         <is>
-          <t>Living, End Table, MARSTON</t>
+          <t>Living, End Table, MARSTON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -22411,7 +24961,22 @@
       </c>
       <c r="AD171" t="inlineStr">
         <is>
-          <t>Living, End Table, MAY</t>
+          <t>Living, End Table, MAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -22538,7 +25103,22 @@
       </c>
       <c r="AD172" t="inlineStr">
         <is>
-          <t>Living, End Table, MEDA</t>
+          <t>Living, End Table, MEDA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -22666,7 +25246,22 @@
       </c>
       <c r="AD173" t="inlineStr">
         <is>
-          <t>Living, End Table, MOA</t>
+          <t>Living, End Table, MOA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -22793,7 +25388,22 @@
       </c>
       <c r="AD174" t="inlineStr">
         <is>
-          <t>Living, End Table, NAHARA</t>
+          <t>Living, End Table, NAHARA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -22920,7 +25530,22 @@
       </c>
       <c r="AD175" t="inlineStr">
         <is>
-          <t>Living, End Table, NAHARA</t>
+          <t>Living, End Table, NAHARA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -23047,7 +25672,22 @@
       </c>
       <c r="AD176" t="inlineStr">
         <is>
-          <t>Living, End Table, NAHARA</t>
+          <t>Living, End Table, NAHARA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -23176,7 +25816,22 @@
       </c>
       <c r="AD177" t="inlineStr">
         <is>
-          <t>Living, End Table, NINOVE</t>
+          <t>Living, End Table, NINOVE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -23305,7 +25960,22 @@
       </c>
       <c r="AD178" t="inlineStr">
         <is>
-          <t>Living, End Table, NINOVE</t>
+          <t>Living, End Table, NINOVE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -23427,7 +26097,22 @@
       </c>
       <c r="AD179" t="inlineStr">
         <is>
-          <t>Living, End Table, NORTHWICH</t>
+          <t>Living, End Table, NORTHWICH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -23549,7 +26234,22 @@
       </c>
       <c r="AD180" t="inlineStr">
         <is>
-          <t>Living, End Table, NOVA</t>
+          <t>Living, End Table, NOVA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -23677,7 +26377,22 @@
       </c>
       <c r="AD181" t="inlineStr">
         <is>
-          <t>Living, End Table, OAKWAY</t>
+          <t>Living, End Table, OAKWAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -23799,7 +26514,22 @@
       </c>
       <c r="AD182" t="inlineStr">
         <is>
-          <t>Living, End Table, ORLA II</t>
+          <t>Living, End Table, ORLA II, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -23930,7 +26660,22 @@
       </c>
       <c r="AD183" t="inlineStr">
         <is>
-          <t>Living, End Table, ORRIN</t>
+          <t>Living, End Table, ORRIN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -24056,7 +26801,22 @@
       </c>
       <c r="AD184" t="inlineStr">
         <is>
-          <t>Living, End Table, POLTIMORE</t>
+          <t>Living, End Table, POLTIMORE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -24182,7 +26942,22 @@
       </c>
       <c r="AD185" t="inlineStr">
         <is>
-          <t>Living, End Table, RAYA</t>
+          <t>Living, End Table, RAYA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -24318,7 +27093,22 @@
       </c>
       <c r="AD186" t="inlineStr">
         <is>
-          <t>Living, End Table, ROCHESTER</t>
+          <t>Living, End Table, ROCHESTER, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -24450,7 +27240,22 @@
       </c>
       <c r="AD187" t="inlineStr">
         <is>
-          <t>Living, End Table, ROCHESTER</t>
+          <t>Living, End Table, ROCHESTER, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -24578,7 +27383,22 @@
       </c>
       <c r="AD188" t="inlineStr">
         <is>
-          <t>Living, End Table, ROSETTA</t>
+          <t>Living, End Table, ROSETTA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -24700,7 +27520,22 @@
       </c>
       <c r="AD189" t="inlineStr">
         <is>
-          <t>Living, End Table, ROXO</t>
+          <t>Living, End Table, ROXO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -24826,7 +27661,22 @@
       </c>
       <c r="AD190" t="inlineStr">
         <is>
-          <t>Living, End Table, RYLEE</t>
+          <t>Living, End Table, RYLEE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -24948,7 +27798,22 @@
       </c>
       <c r="AD191" t="inlineStr">
         <is>
-          <t>Living, End Table, SINDAL</t>
+          <t>Living, End Table, SINDAL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -25070,7 +27935,22 @@
       </c>
       <c r="AD192" t="inlineStr">
         <is>
-          <t>Living, End Table, SINDAL</t>
+          <t>Living, End Table, SINDAL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -25192,7 +28072,22 @@
       </c>
       <c r="AD193" t="inlineStr">
         <is>
-          <t>Living, End Table, SLOANE</t>
+          <t>Living, End Table, SLOANE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -25323,7 +28218,22 @@
       </c>
       <c r="AD194" t="inlineStr">
         <is>
-          <t>Living, End Table, STATEN</t>
+          <t>Living, End Table, STATEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -25454,7 +28364,22 @@
       </c>
       <c r="AD195" t="inlineStr">
         <is>
-          <t>Living, End Table, STATEN</t>
+          <t>Living, End Table, STATEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -25580,7 +28505,22 @@
       </c>
       <c r="AD196" t="inlineStr">
         <is>
-          <t>Living, End Table, SUNDANCE</t>
+          <t>Living, End Table, SUNDANCE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -25702,7 +28642,22 @@
       </c>
       <c r="AD197" t="inlineStr">
         <is>
-          <t>Living, End Table, SURDAL</t>
+          <t>Living, End Table, SURDAL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -25831,7 +28786,22 @@
       </c>
       <c r="AD198" t="inlineStr">
         <is>
-          <t>Living, End Table, TADCASTER</t>
+          <t>Living, End Table, TADCASTER, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -25953,7 +28923,22 @@
       </c>
       <c r="AD199" t="inlineStr">
         <is>
-          <t>Living, End Table, TANIKA</t>
+          <t>Living, End Table, TANIKA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -26081,7 +29066,22 @@
       </c>
       <c r="AD200" t="inlineStr">
         <is>
-          <t>Living, End Table, THISTED</t>
+          <t>Living, End Table, THISTED, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -26207,7 +29207,22 @@
       </c>
       <c r="AD201" t="inlineStr">
         <is>
-          <t>Living, End Table, TITUS</t>
+          <t>Living, End Table, TITUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -26333,7 +29348,22 @@
       </c>
       <c r="AD202" t="inlineStr">
         <is>
-          <t>Living, End Table, TORKEL</t>
+          <t>Living, End Table, TORKEL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -26455,7 +29485,22 @@
       </c>
       <c r="AD203" t="inlineStr">
         <is>
-          <t>Living, End Table, VALO</t>
+          <t>Living, End Table, VALO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -26579,7 +29624,22 @@
       </c>
       <c r="AD204" t="inlineStr">
         <is>
-          <t>Living, End Table, VILLARSGLANE</t>
+          <t>Living, End Table, VILLARSGLANE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -26705,7 +29765,22 @@
       </c>
       <c r="AD205" t="inlineStr">
         <is>
-          <t>Living, End Table, VIRDEN</t>
+          <t>Living, End Table, VIRDEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -26831,7 +29906,22 @@
       </c>
       <c r="AD206" t="inlineStr">
         <is>
-          <t>Living, End Table, VIRDEN</t>
+          <t>Living, End Table, VIRDEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -26960,7 +30050,22 @@
       </c>
       <c r="AD207" t="inlineStr">
         <is>
-          <t>Living, End Table, WALWORTH</t>
+          <t>Living, End Table, WALWORTH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -27082,7 +30187,22 @@
       </c>
       <c r="AD208" t="inlineStr">
         <is>
-          <t>Living, End Table, WESTERHAM</t>
+          <t>Living, End Table, WESTERHAM, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -27206,7 +30326,22 @@
       </c>
       <c r="AD209" t="inlineStr">
         <is>
-          <t>Living, End Table, WETTINGEN</t>
+          <t>Living, End Table, WETTINGEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -27339,7 +30474,22 @@
       </c>
       <c r="AD210" t="inlineStr">
         <is>
-          <t>Living, End Table, WETZIKON</t>
+          <t>Living, End Table, WETZIKON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -27472,7 +30622,22 @@
       </c>
       <c r="AD211" t="inlineStr">
         <is>
-          <t>Living, End Table, WETZIKON</t>
+          <t>Living, End Table, WETZIKON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -27594,7 +30759,22 @@
       </c>
       <c r="AD212" t="inlineStr">
         <is>
-          <t>Living, End Table, XANTHUS</t>
+          <t>Living, End Table, XANTHUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -27720,7 +30900,22 @@
       </c>
       <c r="AD213" t="inlineStr">
         <is>
-          <t>Living, End Table, ZOLA</t>
+          <t>Living, End Table, ZOLA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -27848,7 +31043,22 @@
       </c>
       <c r="AD214" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, ARLINGTON</t>
+          <t>Living, Sofa Table, ARLINGTON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -27972,7 +31182,22 @@
       </c>
       <c r="AD215" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, ATWOOD II</t>
+          <t>Living, Sofa Table, ATWOOD II, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -28100,7 +31325,22 @@
       </c>
       <c r="AD216" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, AUGSBURG</t>
+          <t>Living, Sofa Table, AUGSBURG, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -28228,7 +31468,22 @@
       </c>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, AUGSBURG</t>
+          <t>Living, Sofa Table, AUGSBURG, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -28357,7 +31612,22 @@
       </c>
       <c r="AD218" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, BACERRA</t>
+          <t>Living, Sofa Table, BACERRA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -28479,7 +31749,22 @@
       </c>
       <c r="AD219" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, BATAM II</t>
+          <t>Living, Sofa Table, BATAM II, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -28601,7 +31886,22 @@
       </c>
       <c r="AD220" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, BIMA II</t>
+          <t>Living, Sofa Table, BIMA II, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -28729,7 +32029,22 @@
       </c>
       <c r="AD221" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, BRAMPTON</t>
+          <t>Living, Sofa Table, BRAMPTON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -28857,7 +32172,22 @@
       </c>
       <c r="AD222" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, BRYANNA</t>
+          <t>Living, Sofa Table, BRYANNA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -28985,7 +32315,22 @@
       </c>
       <c r="AD223" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, BUNBURY</t>
+          <t>Living, Sofa Table, BUNBURY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -29113,7 +32458,22 @@
       </c>
       <c r="AD224" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, CALANDRA</t>
+          <t>Living, Sofa Table, CALANDRA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -29242,7 +32602,22 @@
       </c>
       <c r="AD225" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, CHESHIRE</t>
+          <t>Living, Sofa Table, CHESHIRE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -29370,7 +32745,22 @@
       </c>
       <c r="AD226" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, CRYSTAL FALLS</t>
+          <t>Living, Sofa Table, CRYSTAL FALLS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -29499,7 +32889,22 @@
       </c>
       <c r="AD227" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, DUBENDORF</t>
+          <t>Living, Sofa Table, DUBENDORF, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -29628,7 +33033,22 @@
       </c>
       <c r="AD228" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, DUBENDORF</t>
+          <t>Living, Sofa Table, DUBENDORF, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -29754,7 +33174,22 @@
       </c>
       <c r="AD229" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, EIMEAR</t>
+          <t>Living, Sofa Table, EIMEAR, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -29887,7 +33322,22 @@
       </c>
       <c r="AD230" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, GIORDANI</t>
+          <t>Living, Sofa Table, GIORDANI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -30015,7 +33465,22 @@
       </c>
       <c r="AD231" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, GRANVIA</t>
+          <t>Living, Sofa Table, GRANVIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -30137,7 +33602,22 @@
       </c>
       <c r="AD232" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, IZAR</t>
+          <t>Living, Sofa Table, IZAR, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -30268,7 +33748,22 @@
       </c>
       <c r="AD233" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, KOBLENZ</t>
+          <t>Living, Sofa Table, KOBLENZ, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -30399,7 +33894,22 @@
       </c>
       <c r="AD234" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, KOBLENZ</t>
+          <t>Living, Sofa Table, KOBLENZ, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -30521,7 +34031,22 @@
       </c>
       <c r="AD235" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, LAILA</t>
+          <t>Living, Sofa Table, LAILA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -30652,7 +34177,22 @@
       </c>
       <c r="AD236" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, LOBB</t>
+          <t>Living, Sofa Table, LOBB, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -30779,7 +34319,22 @@
       </c>
       <c r="AD237" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, LODIA III</t>
+          <t>Living, Sofa Table, LODIA III, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -30906,7 +34461,22 @@
       </c>
       <c r="AD238" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, LODIA III</t>
+          <t>Living, Sofa Table, LODIA III, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -31028,7 +34598,22 @@
       </c>
       <c r="AD239" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, LODIA</t>
+          <t>Living, Sofa Table, LODIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -31154,7 +34739,22 @@
       </c>
       <c r="AD240" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, LUDVIG</t>
+          <t>Living, Sofa Table, LUDVIG, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG240" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -31282,7 +34882,22 @@
       </c>
       <c r="AD241" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, MAJKEN</t>
+          <t>Living, Sofa Table, MAJKEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -31415,7 +35030,22 @@
       </c>
       <c r="AD242" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, MANNEDORF</t>
+          <t>Living, Sofa Table, MANNEDORF, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -31544,7 +35174,22 @@
       </c>
       <c r="AD243" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, MANNEDORF</t>
+          <t>Living, Sofa Table, MANNEDORF, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -31670,7 +35315,22 @@
       </c>
       <c r="AD244" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, MAY</t>
+          <t>Living, Sofa Table, MAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -31798,7 +35458,22 @@
       </c>
       <c r="AD245" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, MEADOW</t>
+          <t>Living, Sofa Table, MEADOW, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -31926,7 +35601,22 @@
       </c>
       <c r="AD246" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, MOA</t>
+          <t>Living, Sofa Table, MOA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -32053,7 +35743,22 @@
       </c>
       <c r="AD247" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, NAHARA</t>
+          <t>Living, Sofa Table, NAHARA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -32180,7 +35885,22 @@
       </c>
       <c r="AD248" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, NAHARA</t>
+          <t>Living, Sofa Table, NAHARA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -32307,7 +36027,22 @@
       </c>
       <c r="AD249" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, NAHARA</t>
+          <t>Living, Sofa Table, NAHARA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -32429,7 +36164,22 @@
       </c>
       <c r="AD250" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, NOVA</t>
+          <t>Living, Sofa Table, NOVA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -32557,7 +36307,22 @@
       </c>
       <c r="AD251" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, OAKWAY</t>
+          <t>Living, Sofa Table, OAKWAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -32683,7 +36448,22 @@
       </c>
       <c r="AD252" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, OLBIA</t>
+          <t>Living, Sofa Table, OLBIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -32805,7 +36585,22 @@
       </c>
       <c r="AD253" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, ORLA II</t>
+          <t>Living, Sofa Table, ORLA II, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -32931,7 +36726,22 @@
       </c>
       <c r="AD254" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, RAYA</t>
+          <t>Living, Sofa Table, RAYA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -33059,7 +36869,22 @@
       </c>
       <c r="AD255" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, ROSETTA</t>
+          <t>Living, Sofa Table, ROSETTA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -33181,7 +37006,22 @@
       </c>
       <c r="AD256" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, ROXO</t>
+          <t>Living, Sofa Table, ROXO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -33307,7 +37147,22 @@
       </c>
       <c r="AD257" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, RYLEE</t>
+          <t>Living, Sofa Table, RYLEE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -33429,7 +37284,22 @@
       </c>
       <c r="AD258" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, SLOANE</t>
+          <t>Living, Sofa Table, SLOANE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -33560,7 +37430,22 @@
       </c>
       <c r="AD259" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, STATEN</t>
+          <t>Living, Sofa Table, STATEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF259" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -33691,7 +37576,22 @@
       </c>
       <c r="AD260" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, STATEN</t>
+          <t>Living, Sofa Table, STATEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF260" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -33817,7 +37717,22 @@
       </c>
       <c r="AD261" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, SUNDANCE</t>
+          <t>Living, Sofa Table, SUNDANCE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -33943,7 +37858,22 @@
       </c>
       <c r="AD262" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, TITUS</t>
+          <t>Living, Sofa Table, TITUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -34065,7 +37995,22 @@
       </c>
       <c r="AD263" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, VALO</t>
+          <t>Living, Sofa Table, VALO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -34189,7 +38134,22 @@
       </c>
       <c r="AD264" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, VILLARSGLANE</t>
+          <t>Living, Sofa Table, VILLARSGLANE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -34318,7 +38278,22 @@
       </c>
       <c r="AD265" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, WALWORTH</t>
+          <t>Living, Sofa Table, WALWORTH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -34442,7 +38417,22 @@
       </c>
       <c r="AD266" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, WETTINGEN</t>
+          <t>Living, Sofa Table, WETTINGEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -34575,7 +38565,22 @@
       </c>
       <c r="AD267" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, WETZIKON</t>
+          <t>Living, Sofa Table, WETZIKON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -34708,7 +38713,22 @@
       </c>
       <c r="AD268" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, WETZIKON</t>
+          <t>Living, Sofa Table, WETZIKON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF268" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -34830,7 +38850,22 @@
       </c>
       <c r="AD269" t="inlineStr">
         <is>
-          <t>Living, Sofa Table, XANTHUS</t>
+          <t>Living, Sofa Table, XANTHUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Sofa Tables</t>
         </is>
       </c>
     </row>
@@ -34958,7 +38993,22 @@
       </c>
       <c r="AD270" t="inlineStr">
         <is>
-          <t>Living, Chair, ARTH</t>
+          <t>Living, Chair, ARTH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -35091,7 +39141,22 @@
       </c>
       <c r="AD271" t="inlineStr">
         <is>
-          <t>Living, Chair, SPIEZ</t>
+          <t>Living, Chair, SPIEZ, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -35224,7 +39289,22 @@
       </c>
       <c r="AD272" t="inlineStr">
         <is>
-          <t>Living, Side Table, BELP</t>
+          <t>Living, Side Table, BELP, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -35350,7 +39430,22 @@
       </c>
       <c r="AD273" t="inlineStr">
         <is>
-          <t>Living, Side Table, CHILOQUIN</t>
+          <t>Living, Side Table, CHILOQUIN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -35476,7 +39571,22 @@
       </c>
       <c r="AD274" t="inlineStr">
         <is>
-          <t>Living, Side Table, GARIBALDI</t>
+          <t>Living, Side Table, GARIBALDI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -35598,7 +39708,22 @@
       </c>
       <c r="AD275" t="inlineStr">
         <is>
-          <t>Living, Side Table, NORTHWICH</t>
+          <t>Living, Side Table, NORTHWICH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -35726,7 +39851,22 @@
       </c>
       <c r="AD276" t="inlineStr">
         <is>
-          <t>Living, Side Table, VARDO</t>
+          <t>Living, Side Table, VARDO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; End Tables</t>
         </is>
       </c>
     </row>
@@ -35852,7 +39992,22 @@
       </c>
       <c r="AD277" t="inlineStr">
         <is>
-          <t>Living, Table Set, BORUP</t>
+          <t>Living, Table Set, BORUP, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -35978,7 +40133,22 @@
       </c>
       <c r="AD278" t="inlineStr">
         <is>
-          <t>Living, Table Set, BORUP</t>
+          <t>Living, Table Set, BORUP, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE278" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF278" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG278" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -36109,7 +40279,22 @@
       </c>
       <c r="AD279" t="inlineStr">
         <is>
-          <t>Living, Table Set, FINDLAY</t>
+          <t>Living, Table Set, FINDLAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -36240,7 +40425,22 @@
       </c>
       <c r="AD280" t="inlineStr">
         <is>
-          <t>Living, Table Set, FINDLAY</t>
+          <t>Living, Table Set, FINDLAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -36371,7 +40571,22 @@
       </c>
       <c r="AD281" t="inlineStr">
         <is>
-          <t>Living, Table Set, FINDLAY</t>
+          <t>Living, Table Set, FINDLAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -36502,7 +40717,22 @@
       </c>
       <c r="AD282" t="inlineStr">
         <is>
-          <t>Living, Table Set, FINDLAY</t>
+          <t>Living, Table Set, FINDLAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF282" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -36633,7 +40863,22 @@
       </c>
       <c r="AD283" t="inlineStr">
         <is>
-          <t>Living, Table Set, FINDLAY</t>
+          <t>Living, Table Set, FINDLAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -36764,7 +41009,22 @@
       </c>
       <c r="AD284" t="inlineStr">
         <is>
-          <t>Living, Table Set, FINDLAY</t>
+          <t>Living, Table Set, FINDLAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF284" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -36893,7 +41153,22 @@
       </c>
       <c r="AD285" t="inlineStr">
         <is>
-          <t>Living, Table Set, HOLEN</t>
+          <t>Living, Table Set, HOLEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF285" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG285" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37022,7 +41297,22 @@
       </c>
       <c r="AD286" t="inlineStr">
         <is>
-          <t>Living, Table Set, HOLEN</t>
+          <t>Living, Table Set, HOLEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF286" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37148,7 +41438,22 @@
       </c>
       <c r="AD287" t="inlineStr">
         <is>
-          <t>Living, Table Set, OPHIRA</t>
+          <t>Living, Table Set, OPHIRA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF287" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG287" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37274,7 +41579,22 @@
       </c>
       <c r="AD288" t="inlineStr">
         <is>
-          <t>Living, Table Set, OPHIRA</t>
+          <t>Living, Table Set, OPHIRA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37400,7 +41720,22 @@
       </c>
       <c r="AD289" t="inlineStr">
         <is>
-          <t>Living, Table Set, PALLAS</t>
+          <t>Living, Table Set, PALLAS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE289" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF289" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG289" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37526,7 +41861,22 @@
       </c>
       <c r="AD290" t="inlineStr">
         <is>
-          <t>Living, Table Set, PALLAS</t>
+          <t>Living, Table Set, PALLAS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF290" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG290" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37652,7 +42002,22 @@
       </c>
       <c r="AD291" t="inlineStr">
         <is>
-          <t>Living, Table Set, PALLAS</t>
+          <t>Living, Table Set, PALLAS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF291" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG291" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37778,7 +42143,22 @@
       </c>
       <c r="AD292" t="inlineStr">
         <is>
-          <t>Living, Table Set, RONDE</t>
+          <t>Living, Table Set, RONDE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE292" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF292" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG292" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -37904,7 +42284,22 @@
       </c>
       <c r="AD293" t="inlineStr">
         <is>
-          <t>Living, Table Set, RONDE</t>
+          <t>Living, Table Set, RONDE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE293" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF293" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG293" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38033,7 +42428,22 @@
       </c>
       <c r="AD294" t="inlineStr">
         <is>
-          <t>Living, Table Set, WHETSTONE</t>
+          <t>Living, Table Set, WHETSTONE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE294" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF294" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG294" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38162,7 +42572,22 @@
       </c>
       <c r="AD295" t="inlineStr">
         <is>
-          <t>Living, Table Set, WHETSTONE</t>
+          <t>Living, Table Set, WHETSTONE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE295" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF295" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG295" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38295,7 +42720,22 @@
       </c>
       <c r="AD296" t="inlineStr">
         <is>
-          <t>Living, Occasional Set, BRAMPTON</t>
+          <t>Living, Occasional Set, BRAMPTON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE296" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF296" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG296" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38428,7 +42868,22 @@
       </c>
       <c r="AD297" t="inlineStr">
         <is>
-          <t>Living, Occasional Set, BRYANNA</t>
+          <t>Living, Occasional Set, BRYANNA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE297" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF297" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG297" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38556,7 +43011,22 @@
       </c>
       <c r="AD298" t="inlineStr">
         <is>
-          <t>Living, Occasional Set, BUNBURY</t>
+          <t>Living, Occasional Set, BUNBURY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE298" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF298" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG298" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38690,7 +43160,22 @@
       </c>
       <c r="AD299" t="inlineStr">
         <is>
-          <t>Living, Occasional Set, CHESHIRE</t>
+          <t>Living, Occasional Set, CHESHIRE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE299" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF299" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG299" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38823,7 +43308,22 @@
       </c>
       <c r="AD300" t="inlineStr">
         <is>
-          <t>Living, Occasional Set, LECHESTER</t>
+          <t>Living, Occasional Set, LECHESTER, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF300" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -38951,7 +43451,22 @@
       </c>
       <c r="AD301" t="inlineStr">
         <is>
-          <t>Living, Occasional Set, LODIVEA</t>
+          <t>Living, Occasional Set, LODIVEA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE301" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF301" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG301" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -39079,7 +43594,22 @@
       </c>
       <c r="AD302" t="inlineStr">
         <is>
-          <t>Living, Occasional Set, MONANGO</t>
+          <t>Living, Occasional Set, MONANGO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE302" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF302" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG302" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -39210,7 +43740,22 @@
       </c>
       <c r="AD303" t="inlineStr">
         <is>
-          <t>Living, Occasional Set, OLBIA</t>
+          <t>Living, Occasional Set, OLBIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE303" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF303" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG303" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -39339,7 +43884,22 @@
       </c>
       <c r="AD304" t="inlineStr">
         <is>
-          <t>Living, Occasional Set, ORBE</t>
+          <t>Living, Occasional Set, ORBE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE304" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF304" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG304" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -39465,7 +44025,22 @@
       </c>
       <c r="AD305" t="inlineStr">
         <is>
-          <t>Living, TV Stand, GARIBALDI</t>
+          <t>Living, TV Stand, GARIBALDI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE305" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF305" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG305" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -39587,7 +44162,22 @@
       </c>
       <c r="AD306" t="inlineStr">
         <is>
-          <t>Living, TV Stand, HEPBURNE</t>
+          <t>Living, TV Stand, HEPBURNE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE306" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF306" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG306" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -39713,7 +44303,22 @@
       </c>
       <c r="AD307" t="inlineStr">
         <is>
-          <t>Living, TV Stand, IDANHA</t>
+          <t>Living, TV Stand, IDANHA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE307" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF307" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG307" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -39835,7 +44440,22 @@
       </c>
       <c r="AD308" t="inlineStr">
         <is>
-          <t>Living, TV Stand, WESTERHAM</t>
+          <t>Living, TV Stand, WESTERHAM, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE308" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF308" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG308" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Entertainment Centers &amp; TV Stands</t>
         </is>
       </c>
     </row>
@@ -39963,7 +44583,22 @@
       </c>
       <c r="AD309" t="inlineStr">
         <is>
-          <t>Living, Table, ORKDAL</t>
+          <t>Living, Table, ORKDAL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE309" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF309" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG309" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -40091,7 +44726,22 @@
       </c>
       <c r="AD310" t="inlineStr">
         <is>
-          <t>Living, Table, ORKDAL</t>
+          <t>Living, Table, ORKDAL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE310" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF310" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG310" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -40219,7 +44869,22 @@
       </c>
       <c r="AD311" t="inlineStr">
         <is>
-          <t>Living, Table, ORKDAL</t>
+          <t>Living, Table, ORKDAL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE311" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF311" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG311" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>

--- a/FOA Singles/Living-Single.xlsx
+++ b/FOA Singles/Living-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1259,8 +1259,8 @@
 Product Dimensions: 72"W X 20"D X 29 7/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Metal, Solid Wood.&lt;br&gt;
-Color: Dark Oak&lt;br&gt;
+&lt;p&gt;Materials: Metal, Solid Wood, Others.&lt;br&gt;
+Color: Dark Oak or Antique White&lt;br&gt;
 Weight: 169.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1401,12 +1401,12 @@
       <c r="G6" s="28" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with BORREGO TV Stand, styled in Rustic and designed for everyday comfort. As a living tv console, it is designed to complement your space. With Metal, Solid Wood, and Antique White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+BORREGO TV Stand brings a Rustic look to your home with a refined, comfortable feel. Built as a living tv console, it pairs well with a wide range of interiors. The Metal, Solid Wood, construction is complemented by Dark Oak tones for a polished look.&lt;br&gt;
 Product Dimensions: 72"W X 20"D X 29 7/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Metal, Solid Wood.&lt;br&gt;
-Color: Antique White&lt;br&gt;
+&lt;p&gt;Materials: Metal, Solid Wood, Others.&lt;br&gt;
+Color: Dark Oak or Antique White&lt;br&gt;
 Weight: 169.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -2264,8 +2264,8 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with CERRO 59" TV Console and its Contemporary character. Built as a living tv console, it pairs well with a wide range of interiors. Finished in Black tones, the Lacquer, Metal, Wood, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 59"W X 15 3/8"D X 15 3/4"H&lt;/p&gt;
-&lt;p&gt;Materials: Lacquer, Metal, Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Wood, Others.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 120 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -2406,10 +2406,10 @@
       <c r="G13" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CERRO 59" TV Console brings a Contemporary look to your home with a refined, comfortable feel. As a living tv console, it is designed to complement your space. The Lacquer, Metal, Wood, construction is complemented by White tones for a polished look.&lt;br&gt;
+Make the room feel complete with CERRO 59" TV Console and its Contemporary character. Built as a living tv console, it pairs well with a wide range of interiors. Finished in Black tones, the Lacquer, Metal, Wood, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 59"W X 15 3/8"D X 15 3/4"H&lt;/p&gt;
-&lt;p&gt;Materials: Lacquer, Metal, Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Wood, Others.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 120 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2834,8 +2834,8 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ERNST 60" TV Stand adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living tv console, it is designed to complement your space. Crafted from Acrylic, Glass, Replicated Wood, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 60"L X 18"W X 21 3/4"H&lt;/p&gt;
-&lt;p&gt;Materials: Acrylic, Glass, Replicated Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
+&lt;p&gt;Materials: Acrylic, Glass, Replicated Wood, Others.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 103.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -2976,10 +2976,10 @@
       <c r="G17" s="33" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with ERNST 60" TV Stand and its Contemporary character. This living tv console is made to fit naturally into the room. Finished in White tones, the Acrylic, Glass, Replicated Wood, build balances durability with visual appeal.&lt;br&gt;
+ERNST 60" TV Stand adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living tv console, it is designed to complement your space. Crafted from Acrylic, Glass, Replicated Wood, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 60"L X 18"W X 21 3/4"H&lt;/p&gt;
-&lt;p&gt;Materials: Acrylic, Glass, Replicated Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Acrylic, Glass, Replicated Wood, Others.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 103.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
@@ -7222,8 +7222,8 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 DUBENDORF Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Glass, construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 23 5/8"W X 15"H&lt;/p&gt;
-&lt;p&gt;Materials: Glass.&lt;br&gt;
-Color: Black&lt;br&gt;
+&lt;p&gt;Materials: Glass, Others.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 74.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -7364,10 +7364,10 @@
       <c r="G48" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with DUBENDORF Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Glass, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+DUBENDORF Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Glass, construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 23 5/8"W X 15"H&lt;/p&gt;
-&lt;p&gt;Materials: Glass.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Glass, Others.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 74.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -8230,7 +8230,7 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Linen-like, Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
-Color: Natural Tone or Beige&lt;br&gt;
+Color: Natural Tone or Beige or Natural Tone or Dark Gray&lt;br&gt;
 Weight: 74.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
@@ -8375,12 +8375,12 @@
       <c r="G55" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with GUIS Round Coffee Table and its Transitional character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in Natural Tone or Dark Gray tones, the Linen-like, Solid Wood, Wood Veneer, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+GUIS Round Coffee Table adds a Transitional touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Linen-like, Solid Wood, Wood Veneer, Engineered Wood, it is finished in Natural Tone or Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 40 3/4"DIA X 20 1/4"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Linen-like, Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
-Color: Natural Tone or Dark Gray&lt;br&gt;
+Color: Natural Tone or Beige or Natural Tone or Dark Gray&lt;br&gt;
 Weight: 74.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
@@ -8672,8 +8672,8 @@
 HALEWOOD Cocktail Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Rubberwood, Oak Veneer, Engineered Wood, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 29"DIA X 17"H&lt;/p&gt;
 &lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 41.34 lbs&lt;/p&gt;</t>
+Color: Black or Oak&lt;br&gt;
+Weight: 41.34 or 44.13 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H57" s="39" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -8815,11 +8815,11 @@
       <c r="G58" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with HALEWOOD Cocktail Table and its Contemporary character. As a living coffee table, it is designed to complement your space. Finished in Oak tones, the Rubberwood, Oak Veneer, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+HALEWOOD Cocktail Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Rubberwood, Oak Veneer, Engineered Wood, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 29"DIA X 17"H&lt;/p&gt;
 &lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
-Color: Oak&lt;br&gt;
-Weight: 44.13 lbs&lt;/p&gt;</t>
+Color: Black or Oak&lt;br&gt;
+Weight: 41.34 or 44.13 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H58" s="39" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -9384,9 +9384,9 @@
 Product Dimensions: 48"L X 24"W X 18"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawer&lt;/p&gt;
-&lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Light Teal&lt;br&gt;
-Weight: 80 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Metal, Others.&lt;br&gt;
+Color: Light Teal or Dark Walnut&lt;br&gt;
+Weight: 80 or 79 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H62" s="41" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
@@ -9526,13 +9526,13 @@
       <c r="G63" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-KOBLENZ Coffee Table adds a Glam touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Metal, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with KOBLENZ Coffee Table, styled in Glam and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Metal, and Light Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 48"L X 24"W X 18"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawer&lt;/p&gt;
-&lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
-Weight: 79 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Metal, Others.&lt;br&gt;
+Color: Light Teal or Dark Walnut&lt;br&gt;
+Weight: 80 or 79 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H63" s="41" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
@@ -10095,7 +10095,7 @@
 LODIA III Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Tempered Glass, Paper Veneer, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 23 5/8"W X 17 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 69.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -10234,10 +10234,10 @@
       <c r="G68" s="28" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with LODIA III Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Tempered Glass, Paper Veneer, Engineered Wood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+LODIA III Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Tempered Glass, Paper Veneer, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 23 5/8"W X 17 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 69.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
@@ -11079,9 +11079,9 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Elevate your space with MANNEDORF Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Tempered Glass,Paper Veneer, and Black or Dark Walnut tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 23 5/8"W X 18 7/8"H&lt;/p&gt;
-&lt;p&gt;Materials: Tempered Glass,Paper Veneer.&lt;br&gt;
-Color: Black or Dark Walnut&lt;br&gt;
-Weight: 102 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Tempered Glass,Paper Veneer,Others.&lt;br&gt;
+Color: Black or Dark Walnut or Black or White&lt;br&gt;
+Weight: 102 or 83.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H74" s="35" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
@@ -11221,11 +11221,11 @@
       <c r="G75" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MANNEDORF Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Tempered Glass,Paper Veneer, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with MANNEDORF Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Tempered Glass,Paper Veneer, and Black or Dark Walnut tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 23 5/8"W X 18 7/8"H&lt;/p&gt;
-&lt;p&gt;Materials: Tempered Glass,Paper Veneer.&lt;br&gt;
-Color: Black or White&lt;br&gt;
-Weight: 83.6 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Tempered Glass,Paper Veneer,Others.&lt;br&gt;
+Color: Black or Dark Walnut or Black or White&lt;br&gt;
+Weight: 102 or 83.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H75" s="35" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
@@ -11370,9 +11370,9 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Elegant cabriole legs&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
-Weight: 91.3 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or Champagne&lt;br&gt;
+Weight: 91.3 or 60.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H76" s="33" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr">
@@ -11512,14 +11512,14 @@
       <c r="G77" s="33" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with MARSTON Coffee Table, styled in Traditional and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Champagne tones, it blends structure and softness in one clean profile.&lt;br&gt;
+MARSTON Coffee Table brings a Traditional look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Solid Wood, Wood Veneer, construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
 Product Dimensions: 48"W X 28"D X 19"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Elegant cabriole legs&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Champagne&lt;br&gt;
-Weight: 60.5 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or Champagne&lt;br&gt;
+Weight: 91.3 or 60.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H77" s="33" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr">
@@ -12370,11 +12370,11 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MIKA Coffee Table w/ Cushion Top adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Fabric, Solid Wood, Wood Veneer, it is finished in Antique Oak tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 48 1/2"DIA X 18"H&lt;/p&gt;
+Product Dimensions: 48 1/2"DIA X 18"H / 48"DIA X 20"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Oak&lt;br&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Oak or Antique Gray&lt;br&gt;
 Weight: 102.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
@@ -12515,12 +12515,12 @@
       <c r="G84" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with MIKA Coffee Table w/ Cushion Top and its Rustic character. As a living coffee table, it is designed to complement your space. Finished in Antique Gray tones, the Fabric, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 48"DIA X 20"H&lt;/p&gt;
+MIKA Coffee Table w/ Cushion Top adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Fabric, Solid Wood, Wood Veneer, it is finished in Antique Oak tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 48 1/2"DIA X 18"H / 48"DIA X 20"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Gray&lt;br&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Oak or Antique Gray&lt;br&gt;
 Weight: 102.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr">
@@ -12806,8 +12806,8 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Elevate your space with NAHARA Coffee Table, styled in Contemporary and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Glass, and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 23 5/8"W X 18"H&lt;/p&gt;
-&lt;p&gt;Materials: Glass.&lt;br&gt;
-Color: Black&lt;br&gt;
+&lt;p&gt;Materials: Glass, Others.&lt;br&gt;
+Color: Black or Gray or White&lt;br&gt;
 Weight: 67.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr">
@@ -12946,10 +12946,10 @@
       <c r="G87" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NAHARA Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living coffee table is made to fit naturally into the room. Crafted from Glass, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with NAHARA Coffee Table, styled in Contemporary and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Glass, and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 23 5/8"W X 18"H&lt;/p&gt;
-&lt;p&gt;Materials: Glass.&lt;br&gt;
-Color: Gray&lt;br&gt;
+&lt;p&gt;Materials: Glass, Others.&lt;br&gt;
+Color: Black or Gray or White&lt;br&gt;
 Weight: 67.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
@@ -13088,10 +13088,10 @@
       <c r="G88" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with NAHARA Coffee Table and its Contemporary character. Built as a living coffee table, it pairs well with a wide range of interiors. Finished in White tones, the Glass, build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with NAHARA Coffee Table, styled in Contemporary and designed for everyday comfort. As a living coffee table, it is designed to complement your space. With Glass, and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 23 5/8"W X 18"H&lt;/p&gt;
-&lt;p&gt;Materials: Glass.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Glass, Others.&lt;br&gt;
+Color: Black or Gray or White&lt;br&gt;
 Weight: 67.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
@@ -13231,9 +13231,9 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 NINOVE Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. This living coffee table is made to fit naturally into the room. The Lacquer, Metal, Wood, construction is complemented by Black or Chrome tones for a polished look.&lt;br&gt;
-Product Dimensions: 47 1/4"L X 23 5/8"W X 16"H&lt;/p&gt;
-&lt;p&gt;Materials: Lacquer, Metal, Wood.&lt;br&gt;
-Color: Black or Chrome&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 16"H / 47 1/4"L X 23 1/2"W X 16"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Wood, Others.&lt;br&gt;
+Color: Black or Chrome or White or Chrome&lt;br&gt;
 Weight: 73.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
@@ -13374,10 +13374,10 @@
       <c r="G90" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with NINOVE Coffee Table, styled in Contemporary and designed for everyday comfort. Built as a living coffee table, it pairs well with a wide range of interiors. With Lacquer, Metal, Wood, and White or Chrome tones, it blends structure and softness in one clean profile.&lt;br&gt;
-Product Dimensions: 47 1/4"L X 23 1/2"W X 16"H&lt;/p&gt;
-&lt;p&gt;Materials: Lacquer, Metal, Wood.&lt;br&gt;
-Color: White or Chrome&lt;br&gt;
+NINOVE Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. This living coffee table is made to fit naturally into the room. The Lacquer, Metal, Wood, construction is complemented by Black or Chrome tones for a polished look.&lt;br&gt;
+Product Dimensions: 47 1/4"L X 23 5/8"W X 16"H / 47 1/4"L X 23 1/2"W X 16"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Wood, Others.&lt;br&gt;
+Color: Black or Chrome or White or Chrome&lt;br&gt;
 Weight: 73.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr">
@@ -13521,8 +13521,8 @@
 NORTHWICH Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Sintered Stone, Stainless Steel construction is complemented by White or Matte Gold tones for a polished look.&lt;br&gt;
 Product Dimensions: 51"W X 27.5"D X 17.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Sintered Stone, Stainless Steel.&lt;br&gt;
-Color: White or Matte Gold&lt;br&gt;
-Weight: 124 lbs&lt;/p&gt;</t>
+Color: White or Matte Gold or Black or Gray or Matte Gold&lt;br&gt;
+Weight: 124 or 127 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H91" s="44" t="inlineStr">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr">
@@ -13660,11 +13660,11 @@
       <c r="G92" s="44" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with NORTHWICH Coffee Table, styled in Contemporary and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Sintered Stone, Stainless Steel and Black or Gray or Matte Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
+NORTHWICH Coffee Table brings a Contemporary look to your home with a refined, comfortable feel. As a living coffee table, it is designed to complement your space. The Sintered Stone, Stainless Steel construction is complemented by White or Matte Gold tones for a polished look.&lt;br&gt;
 Product Dimensions: 51"W X 27.5"D X 17.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Sintered Stone, Stainless Steel.&lt;br&gt;
-Color: Black or Gray or Matte Gold&lt;br&gt;
-Weight: 127 lbs&lt;/p&gt;</t>
+Color: White or Matte Gold or Black or Gray or Matte Gold&lt;br&gt;
+Weight: 124 or 127 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H92" s="44" t="inlineStr">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD92" t="inlineStr">
@@ -13885,7 +13885,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD94" t="inlineStr">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr">
@@ -14589,7 +14589,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
@@ -14730,7 +14730,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr">
@@ -14789,9 +14789,9 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Elegant cabriole legs&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Champagne&lt;br&gt;
-Weight: 83.6 lbs&lt;/p&gt;</t>
+Weight: 83.6 or 73.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H100" s="30" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr">
@@ -14935,14 +14935,14 @@
       <c r="G101" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ROCHESTER Coffee Table adds a Traditional touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Champagne tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with ROCHESTER Coffee Table, styled in Traditional and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Champagne tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 53"W X 30.5"D X 20.5"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Elegant cabriole legs&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Champagne&lt;br&gt;
-Weight: 73.5 lbs&lt;/p&gt;</t>
+Weight: 83.6 or 73.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H101" s="30" t="inlineStr">
@@ -15028,7 +15028,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -15917,7 +15917,7 @@
 Elevate your space with STATEN Coffee Table, styled in Contemporary and designed for everyday comfort. Built as a living coffee table, it pairs well with a wide range of interiors. With Tempered Glass, Metal, Engineered Wood and Glossy Black or Chrome tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 23 5/8"W X 17 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Tempered Glass, Metal, Engineered Wood.&lt;br&gt;
-Color: Glossy Black or Chrome&lt;br&gt;
+Color: Glossy Black or Chrome or Glossy White or Chrome&lt;br&gt;
 Weight: 60.06 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
@@ -16060,10 +16060,10 @@
       <c r="G109" s="46" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-STATEN Coffee Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living coffee table, it is designed to complement your space. Crafted from Tempered Glass, Metal, Engineered Wood, it is finished in Glossy White or Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with STATEN Coffee Table, styled in Contemporary and designed for everyday comfort. Built as a living coffee table, it pairs well with a wide range of interiors. With Tempered Glass, Metal, Engineered Wood and Glossy Black or Chrome tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 23 5/8"W X 17 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Tempered Glass, Metal, Engineered Wood.&lt;br&gt;
-Color: Glossy White or Chrome&lt;br&gt;
+Color: Glossy Black or Chrome or Glossy White or Chrome&lt;br&gt;
 Weight: 60.06 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16152,7 +16152,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr">
@@ -16430,7 +16430,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr">
@@ -16711,7 +16711,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
@@ -17275,7 +17275,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
@@ -17692,7 +17692,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
@@ -18256,7 +18256,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
@@ -18676,7 +18676,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr">
@@ -18735,7 +18735,7 @@
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Glass.&lt;br&gt;
-Color: Black or Silver&lt;br&gt;
+Color: Black or Silver or White or Silver&lt;br&gt;
 Weight: 78.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
@@ -18878,12 +18878,12 @@
       <c r="G129" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-WETZIKON Coffee Table adds a Glam touch while keeping the room feeling warm and welcoming. Built as a living coffee table, it pairs well with a wide range of interiors. Crafted from Metal, Glass, it is finished in White or Silver tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with WETZIKON Coffee Table, styled in Glam and designed for everyday comfort. This living coffee table is made to fit naturally into the room. With Metal, Glass and Black or Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 51"L X 27 1/2"W X 18"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Glass.&lt;br&gt;
-Color: White or Silver&lt;br&gt;
+Color: Black or Silver or White or Silver&lt;br&gt;
 Weight: 78.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -18972,7 +18972,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
@@ -19109,7 +19109,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
@@ -19530,7 +19530,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr">
@@ -19812,7 +19812,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -19955,7 +19955,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr">
@@ -20092,7 +20092,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -20233,7 +20233,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD138" t="inlineStr">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -20513,7 +20513,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD140" t="inlineStr">
@@ -20656,7 +20656,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
@@ -20802,7 +20802,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD142" t="inlineStr">
@@ -20946,7 +20946,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD144" t="inlineStr">
@@ -21232,7 +21232,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
@@ -21288,8 +21288,8 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 DUBENDORF End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Glass, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 22"L X 22"W X 23 5/8"H&lt;/p&gt;
-&lt;p&gt;Materials: Glass.&lt;br&gt;
-Color: Black&lt;br&gt;
+&lt;p&gt;Materials: Glass, Others.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -21376,7 +21376,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr">
@@ -21430,10 +21430,10 @@
       <c r="G147" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with DUBENDORF End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in White tones, the Glass, build balances durability with visual appeal.&lt;br&gt;
+DUBENDORF End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Glass, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 22"L X 22"W X 23 5/8"H&lt;/p&gt;
-&lt;p&gt;Materials: Glass.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Glass, Others.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -21520,7 +21520,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
@@ -21661,7 +21661,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
@@ -21804,7 +21804,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
@@ -21952,7 +21952,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr">
@@ -22095,7 +22095,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -22241,7 +22241,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr">
@@ -22385,7 +22385,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr">
@@ -22442,8 +22442,8 @@
 HALEWOOD End Table brings a Contemporary look to your home with a refined, comfortable feel. This living end table is made to fit naturally into the room. The Rubberwood, Oak Veneer, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 20"DIA X 21"H&lt;/p&gt;
 &lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 28.6 lbs&lt;/p&gt;</t>
+Color: Black or Oak&lt;br&gt;
+Weight: 28.6 or 26.66 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H154" s="48" t="inlineStr">
@@ -22531,7 +22531,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD154" t="inlineStr">
@@ -22585,11 +22585,11 @@
       <c r="G155" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with HALEWOOD End Table, styled in Contemporary and designed for everyday comfort. Built as a living end table, it pairs well with a wide range of interiors. With Rubberwood, Oak Veneer, Engineered Wood and Oak tones, it blends structure and softness in one clean profile.&lt;br&gt;
+HALEWOOD End Table brings a Contemporary look to your home with a refined, comfortable feel. This living end table is made to fit naturally into the room. The Rubberwood, Oak Veneer, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 20"DIA X 21"H&lt;/p&gt;
 &lt;p&gt;Materials: Rubberwood, Oak Veneer, Engineered Wood.&lt;br&gt;
-Color: Oak&lt;br&gt;
-Weight: 26.66 lbs&lt;/p&gt;</t>
+Color: Black or Oak&lt;br&gt;
+Weight: 28.6 or 26.66 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H155" s="48" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD155" t="inlineStr">
@@ -22810,7 +22810,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD156" t="inlineStr">
@@ -22953,7 +22953,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr">
@@ -23011,9 +23011,9 @@
 Product Dimensions: 23"DIA X 24"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawer&lt;/p&gt;
-&lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Light Teal&lt;br&gt;
-Weight: 41.14 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Metal, Others.&lt;br&gt;
+Color: Light Teal or Dark Walnut&lt;br&gt;
+Weight: 41.14 or 41.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H158" s="50" t="inlineStr">
@@ -23099,7 +23099,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD158" t="inlineStr">
@@ -23153,13 +23153,13 @@
       <c r="G159" s="50" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-KOBLENZ End Table brings a Glam look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Metal, construction is complemented by Dark Walnut tones for a polished look.&lt;br&gt;
+Make the room feel complete with KOBLENZ End Table and its Glam character. Built as a living end table, it pairs well with a wide range of interiors. Finished in Light Teal tones, the Metal, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 23"DIA X 24"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawer&lt;/p&gt;
-&lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
-Weight: 41.2 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Metal, Others.&lt;br&gt;
+Color: Light Teal or Dark Walnut&lt;br&gt;
+Weight: 41.14 or 41.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H159" s="50" t="inlineStr">
@@ -23245,7 +23245,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD159" t="inlineStr">
@@ -23382,7 +23382,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD160" t="inlineStr">
@@ -23528,7 +23528,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD161" t="inlineStr">
@@ -23665,7 +23665,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD162" t="inlineStr">
@@ -23722,7 +23722,7 @@
 LODIA III End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Tempered Glass, Paper Veneer, Engineered Wood, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 23 5/8"DIA X 22"H&lt;/p&gt;
 &lt;p&gt;Materials: Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 47.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -23807,7 +23807,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD163" t="inlineStr">
@@ -23861,10 +23861,10 @@
       <c r="G164" s="52" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with LODIA III End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in White tones, the Tempered Glass, Paper Veneer, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+LODIA III End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Tempered Glass, Paper Veneer, Engineered Wood, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 23 5/8"DIA X 22"H&lt;/p&gt;
 &lt;p&gt;Materials: Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 47.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -23949,7 +23949,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD164" t="inlineStr">
@@ -24090,7 +24090,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD165" t="inlineStr">
@@ -24233,7 +24233,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD166" t="inlineStr">
@@ -24289,9 +24289,9 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with MANNEDORF End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in Black or Dark Walnut tones, the Tempered Glass,Paper Veneer, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 22"L X 22"W X 24 3/8"H&lt;/p&gt;
-&lt;p&gt;Materials: Tempered Glass,Paper Veneer.&lt;br&gt;
-Color: Black or Dark Walnut&lt;br&gt;
-Weight: 57 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Tempered Glass,Paper Veneer,Others.&lt;br&gt;
+Color: Black or Dark Walnut or Black or White&lt;br&gt;
+Weight: 57 or 47.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H167" s="24" t="inlineStr">
@@ -24377,7 +24377,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD167" t="inlineStr">
@@ -24431,11 +24431,11 @@
       <c r="G168" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MANNEDORF End Table brings a Contemporary look to your home with a refined, comfortable feel. This living end table is made to fit naturally into the room. The Tempered Glass,Paper Veneer, construction is complemented by Black or White tones for a polished look.&lt;br&gt;
+Make the room feel complete with MANNEDORF End Table and its Contemporary character. As a living end table, it is designed to complement your space. Finished in Black or Dark Walnut tones, the Tempered Glass,Paper Veneer, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 22"L X 22"W X 24 3/8"H&lt;/p&gt;
-&lt;p&gt;Materials: Tempered Glass,Paper Veneer.&lt;br&gt;
-Color: Black or White&lt;br&gt;
-Weight: 47.3 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Tempered Glass,Paper Veneer,Others.&lt;br&gt;
+Color: Black or Dark Walnut or Black or White&lt;br&gt;
+Weight: 57 or 47.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H168" s="24" t="inlineStr">
@@ -24521,7 +24521,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD168" t="inlineStr">
@@ -24580,9 +24580,9 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Elegant cabriole legs&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
-Weight: 67.1 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or Champagne&lt;br&gt;
+Weight: 67.1 or 48.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H169" s="54" t="inlineStr">
@@ -24668,7 +24668,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD169" t="inlineStr">
@@ -24722,14 +24722,14 @@
       <c r="G170" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with MARSTON End Table and its Traditional character. As a living end table, it is designed to complement your space. Finished in Champagne tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+MARSTON End Table adds a Traditional touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 27.5"W X 26"D X 23.5"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Elegant cabriole legs&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Champagne&lt;br&gt;
-Weight: 48.4 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Dark Walnut or Champagne&lt;br&gt;
+Weight: 67.1 or 48.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H170" s="54" t="inlineStr">
@@ -24815,7 +24815,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD170" t="inlineStr">
@@ -24956,7 +24956,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD171" t="inlineStr">
@@ -25098,7 +25098,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD172" t="inlineStr">
@@ -25241,7 +25241,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr">
@@ -25297,8 +25297,8 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 NAHARA End Table brings a Contemporary look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Glass, construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 22"DIA X 23 3/8"H&lt;/p&gt;
-&lt;p&gt;Materials: Glass.&lt;br&gt;
-Color: Black&lt;br&gt;
+&lt;p&gt;Materials: Glass, Others.&lt;br&gt;
+Color: Black or Gray or White&lt;br&gt;
 Weight: 53.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25383,7 +25383,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr">
@@ -25437,10 +25437,10 @@
       <c r="G175" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with NAHARA End Table, styled in Contemporary and designed for everyday comfort. This living end table is made to fit naturally into the room. With Glass, and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+NAHARA End Table brings a Contemporary look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Glass, construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 22"DIA X 23 3/8"H&lt;/p&gt;
-&lt;p&gt;Materials: Glass.&lt;br&gt;
-Color: Gray&lt;br&gt;
+&lt;p&gt;Materials: Glass, Others.&lt;br&gt;
+Color: Black or Gray or White&lt;br&gt;
 Weight: 53.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25525,7 +25525,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr">
@@ -25579,10 +25579,10 @@
       <c r="G176" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NAHARA End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living end table, it pairs well with a wide range of interiors. Crafted from Glass, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+NAHARA End Table brings a Contemporary look to your home with a refined, comfortable feel. As a living end table, it is designed to complement your space. The Glass, construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 22"DIA X 23 3/8"H&lt;/p&gt;
-&lt;p&gt;Materials: Glass.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Glass, Others.&lt;br&gt;
+Color: Black or Gray or White&lt;br&gt;
 Weight: 53.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25667,7 +25667,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD176" t="inlineStr">
@@ -25722,9 +25722,9 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 NINOVE End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living end table, it is designed to complement your space. Crafted from Lacquer, Metal, Wood, it is finished in Black or Chrome tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H&lt;/p&gt;
-&lt;p&gt;Materials: Lacquer, Metal, Wood.&lt;br&gt;
-Color: Black or Chrome&lt;br&gt;
+Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H / 23 1/2"L X 23 1/2"W X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Wood, Others.&lt;br&gt;
+Color: Black or Chrome or White or Chrome&lt;br&gt;
 Weight: 53.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25811,7 +25811,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD177" t="inlineStr">
@@ -25865,10 +25865,10 @@
       <c r="G178" s="50" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with NINOVE End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in White or Chrome tones, the Lacquer, Metal, Wood, build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 23 1/2"L X 23 1/2"W X 22"H&lt;/p&gt;
-&lt;p&gt;Materials: Lacquer, Metal, Wood.&lt;br&gt;
-Color: White or Chrome&lt;br&gt;
+NINOVE End Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living end table, it is designed to complement your space. Crafted from Lacquer, Metal, Wood, it is finished in Black or Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H / 23 1/2"L X 23 1/2"W X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Lacquer, Metal, Wood, Others.&lt;br&gt;
+Color: Black or Chrome or White or Chrome&lt;br&gt;
 Weight: 53.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25955,7 +25955,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD178" t="inlineStr">
@@ -26092,7 +26092,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD179" t="inlineStr">
@@ -26229,7 +26229,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD180" t="inlineStr">
@@ -26372,7 +26372,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD181" t="inlineStr">
@@ -26509,7 +26509,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD182" t="inlineStr">
@@ -26655,7 +26655,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD183" t="inlineStr">
@@ -26796,7 +26796,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD184" t="inlineStr">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD185" t="inlineStr">
@@ -26996,9 +26996,9 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Elegant cabriole legs&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Champagne&lt;br&gt;
-Weight: 61.6 lbs&lt;/p&gt;</t>
+Weight: 61.6 or 50 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H186" s="35" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD186" t="inlineStr">
@@ -27142,14 +27142,14 @@
       <c r="G187" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ROCHESTER End Table brings a Traditional look to your home with a refined, comfortable feel. This living end table is made to fit naturally into the room. The Solid Wood, Wood Veneer, construction is complemented by Champagne tones for a polished look.&lt;br&gt;
+Make the room feel complete with ROCHESTER End Table and its Traditional character. As a living end table, it is designed to complement your space. Finished in Champagne tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 26.5"W X 28.5"D X 24.5"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;br&gt;
 - Elegant cabriole legs&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
 Color: Champagne&lt;br&gt;
-Weight: 50 lbs&lt;/p&gt;</t>
+Weight: 61.6 or 50 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H187" s="35" t="inlineStr">
@@ -27235,7 +27235,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr">
@@ -27378,7 +27378,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD188" t="inlineStr">
@@ -27515,7 +27515,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr">
@@ -27656,7 +27656,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD190" t="inlineStr">
@@ -27793,7 +27793,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr">
@@ -27930,7 +27930,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD192" t="inlineStr">
@@ -28067,7 +28067,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD193" t="inlineStr">
@@ -28124,7 +28124,7 @@
 Make the room feel complete with STATEN End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in Glossy Black or Chrome tones, the Tempered Glass, Metal, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H&lt;/p&gt;
 &lt;p&gt;Materials: Tempered Glass, Metal, Engineered Wood.&lt;br&gt;
-Color: Glossy Black or Chrome&lt;br&gt;
+Color: Glossy Black or Chrome or Glossy White or Chrome&lt;br&gt;
 Weight: 43.56 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -28213,7 +28213,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr">
@@ -28267,10 +28267,10 @@
       <c r="G195" s="33" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-STATEN End Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a living end table, it pairs well with a wide range of interiors. The Tempered Glass, Metal, Engineered Wood construction is complemented by Glossy White or Chrome tones for a polished look.&lt;br&gt;
+Make the room feel complete with STATEN End Table and its Contemporary character. This living end table is made to fit naturally into the room. Finished in Glossy Black or Chrome tones, the Tempered Glass, Metal, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 23 5/8"L X 23 5/8"W X 22"H&lt;/p&gt;
 &lt;p&gt;Materials: Tempered Glass, Metal, Engineered Wood.&lt;br&gt;
-Color: Glossy White or Chrome&lt;br&gt;
+Color: Glossy Black or Chrome or Glossy White or Chrome&lt;br&gt;
 Weight: 43.56 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -28359,7 +28359,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD195" t="inlineStr">
@@ -28500,7 +28500,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD196" t="inlineStr">
@@ -28637,7 +28637,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD197" t="inlineStr">
@@ -28781,7 +28781,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD198" t="inlineStr">
@@ -28918,7 +28918,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr">
@@ -29061,7 +29061,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr">
@@ -29202,7 +29202,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr">
@@ -29343,7 +29343,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD202" t="inlineStr">
@@ -29480,7 +29480,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD203" t="inlineStr">
@@ -29619,7 +29619,7 @@
       </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD204" t="inlineStr">
@@ -29760,7 +29760,7 @@
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD205" t="inlineStr">
@@ -29901,7 +29901,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD206" t="inlineStr">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr">
@@ -30182,7 +30182,7 @@
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD208" t="inlineStr">
@@ -30321,7 +30321,7 @@
       </c>
       <c r="AC209" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD209" t="inlineStr">
@@ -30380,7 +30380,7 @@
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Glass.&lt;br&gt;
-Color: Black or Silver&lt;br&gt;
+Color: Black or Silver or White or Silver&lt;br&gt;
 Weight: 53.95 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -30469,7 +30469,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
@@ -30523,12 +30523,12 @@
       <c r="G211" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-WETZIKON End Table brings a Glam look to your home with a refined, comfortable feel. This living end table is made to fit naturally into the room. The Metal, Glass construction is complemented by White or Silver tones for a polished look.&lt;br&gt;
+Make the room feel complete with WETZIKON End Table and its Glam character. As a living end table, it is designed to complement your space. Finished in Black or Silver tones, the Metal, Glass build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 23 1/2"L X 23 1/2"W X 23"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Glass.&lt;br&gt;
-Color: White or Silver&lt;br&gt;
+Color: Black or Silver or White or Silver&lt;br&gt;
 Weight: 53.95 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -30617,7 +30617,7 @@
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD211" t="inlineStr">
@@ -30754,7 +30754,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -30895,7 +30895,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD213" t="inlineStr">
@@ -31038,7 +31038,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD214" t="inlineStr">
@@ -31177,7 +31177,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr">
@@ -31320,7 +31320,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
@@ -31463,7 +31463,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr">
@@ -31607,7 +31607,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
@@ -31744,7 +31744,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr">
@@ -31881,7 +31881,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">
@@ -32024,7 +32024,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD221" t="inlineStr">
@@ -32167,7 +32167,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr">
@@ -32310,7 +32310,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr">
@@ -32453,7 +32453,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr">
@@ -32597,7 +32597,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD225" t="inlineStr">
@@ -32740,7 +32740,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr">
@@ -32796,8 +32796,8 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 DUBENDORF Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Glass, construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 17 7/8"W X 29 7/8"H&lt;/p&gt;
-&lt;p&gt;Materials: Glass.&lt;br&gt;
-Color: Black&lt;br&gt;
+&lt;p&gt;Materials: Glass, Others.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 88 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32884,7 +32884,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr">
@@ -32938,10 +32938,10 @@
       <c r="G228" s="46" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with DUBENDORF Sofa Table, styled in Contemporary and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Glass, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+DUBENDORF Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Glass, construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 17 7/8"W X 29 7/8"H&lt;/p&gt;
-&lt;p&gt;Materials: Glass.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Glass, Others.&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 88 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr">
@@ -33169,7 +33169,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr">
@@ -33317,7 +33317,7 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD230" t="inlineStr">
@@ -33460,7 +33460,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr">
@@ -33597,7 +33597,7 @@
       </c>
       <c r="AC232" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD232" t="inlineStr">
@@ -33655,9 +33655,9 @@
 Product Dimensions: 48"L X 16"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawer&lt;/p&gt;
-&lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Light Teal&lt;br&gt;
-Weight: 64.1 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Metal, Others.&lt;br&gt;
+Color: Light Teal or Dark Walnut&lt;br&gt;
+Weight: 64.1 or 65.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H233" s="44" t="inlineStr">
@@ -33743,7 +33743,7 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD233" t="inlineStr">
@@ -33797,13 +33797,13 @@
       <c r="G234" s="44" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-KOBLENZ Sofa Table adds a Glam touch while keeping the room feeling warm and welcoming. Built as a living sofa table, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Dark Walnut tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with KOBLENZ Sofa Table, styled in Glam and designed for everyday comfort. This living sofa table is made to fit naturally into the room. With Metal, and Light Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 48"L X 16"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design Bonus storage &amp;amp; convenience features (from matching set pieces): Concealed Drawer&lt;/p&gt;
-&lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Dark Walnut&lt;br&gt;
-Weight: 65.3 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Metal, Others.&lt;br&gt;
+Color: Light Teal or Dark Walnut&lt;br&gt;
+Weight: 64.1 or 65.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H234" s="44" t="inlineStr">
@@ -33889,7 +33889,7 @@
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr">
@@ -34026,7 +34026,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr">
@@ -34172,7 +34172,7 @@
       </c>
       <c r="AC236" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD236" t="inlineStr">
@@ -34229,7 +34229,7 @@
 LODIA III Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Tempered Glass, Paper Veneer, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 18"W X 29 7/8"H&lt;/p&gt;
 &lt;p&gt;Materials: Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 65.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -34314,7 +34314,7 @@
       </c>
       <c r="AC237" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD237" t="inlineStr">
@@ -34368,10 +34368,10 @@
       <c r="G238" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with LODIA III Sofa Table, styled in Contemporary and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Tempered Glass, Paper Veneer, Engineered Wood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+LODIA III Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Tempered Glass, Paper Veneer, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 18"W X 29 7/8"H&lt;/p&gt;
 &lt;p&gt;Materials: Tempered Glass, Paper Veneer, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 65.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -34456,7 +34456,7 @@
       </c>
       <c r="AC238" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD238" t="inlineStr">
@@ -34593,7 +34593,7 @@
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD239" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD240" t="inlineStr">
@@ -34877,7 +34877,7 @@
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD241" t="inlineStr">
@@ -34933,9 +34933,9 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Elevate your space with MANNEDORF Sofa Table, styled in Contemporary and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Tempered Glass,Paper Veneer, and Black or Dark Walnut tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 15 5/8"W X 3"H&lt;/p&gt;
-&lt;p&gt;Materials: Tempered Glass,Paper Veneer.&lt;br&gt;
-Color: Black or Dark Walnut&lt;br&gt;
-Weight: 85 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Tempered Glass,Paper Veneer,Others.&lt;br&gt;
+Color: Black or Dark Walnut or Black or White&lt;br&gt;
+Weight: 85 or 72.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H242" s="46" t="inlineStr">
@@ -35025,7 +35025,7 @@
       </c>
       <c r="AC242" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD242" t="inlineStr">
@@ -35079,11 +35079,11 @@
       <c r="G243" s="46" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MANNEDORF Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a living sofa table, it is designed to complement your space. Crafted from Tempered Glass,Paper Veneer, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with MANNEDORF Sofa Table, styled in Contemporary and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Tempered Glass,Paper Veneer, and Black or Dark Walnut tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 15 5/8"W X 3"H&lt;/p&gt;
-&lt;p&gt;Materials: Tempered Glass,Paper Veneer.&lt;br&gt;
-Color: Black or White&lt;br&gt;
-Weight: 72.6 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Tempered Glass,Paper Veneer,Others.&lt;br&gt;
+Color: Black or Dark Walnut or Black or White&lt;br&gt;
+Weight: 85 or 72.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H243" s="46" t="inlineStr">
@@ -35169,7 +35169,7 @@
       </c>
       <c r="AC243" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD243" t="inlineStr">
@@ -35310,7 +35310,7 @@
       </c>
       <c r="AC244" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD244" t="inlineStr">
@@ -35453,7 +35453,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -35596,7 +35596,7 @@
       </c>
       <c r="AC246" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD246" t="inlineStr">
@@ -35652,8 +35652,8 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with NAHARA Sofa Table and its Contemporary character. As a living sofa table, it is designed to complement your space. Finished in Black tones, the Glass, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 18"W X 29 3/4"H&lt;/p&gt;
-&lt;p&gt;Materials: Glass.&lt;br&gt;
-Color: Black&lt;br&gt;
+&lt;p&gt;Materials: Glass, Others.&lt;br&gt;
+Color: Black or Gray or White&lt;br&gt;
 Weight: 83.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -35738,7 +35738,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr">
@@ -35792,10 +35792,10 @@
       <c r="G248" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NAHARA Sofa Table brings a Contemporary look to your home with a refined, comfortable feel. This living sofa table is made to fit naturally into the room. The Glass, construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Make the room feel complete with NAHARA Sofa Table and its Contemporary character. As a living sofa table, it is designed to complement your space. Finished in Black tones, the Glass, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 18"W X 29 3/4"H&lt;/p&gt;
-&lt;p&gt;Materials: Glass.&lt;br&gt;
-Color: Gray&lt;br&gt;
+&lt;p&gt;Materials: Glass, Others.&lt;br&gt;
+Color: Black or Gray or White&lt;br&gt;
 Weight: 83.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -35880,7 +35880,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD248" t="inlineStr">
@@ -35934,10 +35934,10 @@
       <c r="G249" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with NAHARA Sofa Table, styled in Contemporary and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Glass, and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with NAHARA Sofa Table and its Contemporary character. As a living sofa table, it is designed to complement your space. Finished in Black tones, the Glass, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 18"W X 29 3/4"H&lt;/p&gt;
-&lt;p&gt;Materials: Glass.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Glass, Others.&lt;br&gt;
+Color: Black or Gray or White&lt;br&gt;
 Weight: 83.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -36022,7 +36022,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr">
@@ -36159,7 +36159,7 @@
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD250" t="inlineStr">
@@ -36302,7 +36302,7 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr">
@@ -36443,7 +36443,7 @@
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD252" t="inlineStr">
@@ -36580,7 +36580,7 @@
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD253" t="inlineStr">
@@ -36721,7 +36721,7 @@
       </c>
       <c r="AC254" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD254" t="inlineStr">
@@ -36864,7 +36864,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="AC256" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD256" t="inlineStr">
@@ -37142,7 +37142,7 @@
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD257" t="inlineStr">
@@ -37279,7 +37279,7 @@
       </c>
       <c r="AC258" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD258" t="inlineStr">
@@ -37336,7 +37336,7 @@
 Elevate your space with STATEN Sofa Table, styled in Contemporary and designed for everyday comfort. As a living sofa table, it is designed to complement your space. With Tempered Glass, Metal, Engineered Wood and Glossy Black or Chrome tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 48"L X 18"W X 29 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Tempered Glass, Metal, Engineered Wood.&lt;br&gt;
-Color: Glossy Black or Chrome&lt;br&gt;
+Color: Glossy Black or Chrome or Glossy White or Chrome&lt;br&gt;
 Weight: 57.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -37425,7 +37425,7 @@
       </c>
       <c r="AC259" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD259" t="inlineStr">
@@ -37479,10 +37479,10 @@
       <c r="G260" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-STATEN Sofa Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This living sofa table is made to fit naturally into the room. Crafted from Tempered Glass, Metal, Engineered Wood, it is finished in Glossy White or Chrome tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with STATEN Sofa Table, styled in Contemporary and designed for everyday comfort. As a living sofa table, it is designed to complement your space. With Tempered Glass, Metal, Engineered Wood and Glossy Black or Chrome tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 48"L X 18"W X 29 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Tempered Glass, Metal, Engineered Wood.&lt;br&gt;
-Color: Glossy White or Chrome&lt;br&gt;
+Color: Glossy Black or Chrome or Glossy White or Chrome&lt;br&gt;
 Weight: 57.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -37571,7 +37571,7 @@
       </c>
       <c r="AC260" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD260" t="inlineStr">
@@ -37712,7 +37712,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr">
@@ -37853,7 +37853,7 @@
       </c>
       <c r="AC262" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD262" t="inlineStr">
@@ -37990,7 +37990,7 @@
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD263" t="inlineStr">
@@ -38129,7 +38129,7 @@
       </c>
       <c r="AC264" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD264" t="inlineStr">
@@ -38273,7 +38273,7 @@
       </c>
       <c r="AC265" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD265" t="inlineStr">
@@ -38412,7 +38412,7 @@
       </c>
       <c r="AC266" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD266" t="inlineStr">
@@ -38471,7 +38471,7 @@
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Glass.&lt;br&gt;
-Color: Black or Silver&lt;br&gt;
+Color: Black or Silver or White or Silver&lt;br&gt;
 Weight: 64.26 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -38560,7 +38560,7 @@
       </c>
       <c r="AC267" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD267" t="inlineStr">
@@ -38614,12 +38614,12 @@
       <c r="G268" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-WETZIKON Sofa Table adds a Glam touch while keeping the room feeling warm and welcoming. As a living sofa table, it is designed to complement your space. Crafted from Metal, Glass, it is finished in White or Silver tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with WETZIKON Sofa Table, styled in Glam and designed for everyday comfort. Built as a living sofa table, it pairs well with a wide range of interiors. With Metal, Glass and Black or Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 55"L X 16"W X 30"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Glass.&lt;br&gt;
-Color: White or Silver&lt;br&gt;
+Color: Black or Silver or White or Silver&lt;br&gt;
 Weight: 64.26 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -38708,7 +38708,7 @@
       </c>
       <c r="AC268" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD268" t="inlineStr">
@@ -38845,7 +38845,7 @@
       </c>
       <c r="AC269" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD269" t="inlineStr">
@@ -38988,7 +38988,7 @@
       </c>
       <c r="AC270" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD270" t="inlineStr">
@@ -39136,7 +39136,7 @@
       </c>
       <c r="AC271" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD271" t="inlineStr">
@@ -39284,7 +39284,7 @@
       </c>
       <c r="AC272" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD272" t="inlineStr">
@@ -39425,7 +39425,7 @@
       </c>
       <c r="AC273" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD273" t="inlineStr">
@@ -39566,7 +39566,7 @@
       </c>
       <c r="AC274" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD274" t="inlineStr">
@@ -39703,7 +39703,7 @@
       </c>
       <c r="AC275" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD275" t="inlineStr">
@@ -39846,7 +39846,7 @@
       </c>
       <c r="AC276" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD276" t="inlineStr">
@@ -39903,7 +39903,7 @@
 BORUP 3 Pc. Table Set adds a Rustic touch while keeping the room feeling warm and welcoming. This living table set is made to fit naturally into the room. Crafted from Paper, Metal, Engineered Wood, it is finished in Dark Brown or Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 31.5"W X 30.5"D X 18"H, END TABLE: 15.5"W X 15"D X 23"H&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
-Color: Dark Brown or Black&lt;/p&gt;</t>
+Color: Dark Brown or Black or Natural or Black&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H277" s="52" t="inlineStr">
@@ -39987,7 +39987,7 @@
       </c>
       <c r="AC277" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD277" t="inlineStr">
@@ -40041,10 +40041,10 @@
       <c r="G278" s="52" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with BORUP 3 Pc. Table Set and its Rustic character. Built as a living table set, it pairs well with a wide range of interiors. Finished in Natural or Black tones, the Paper, Metal, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+BORUP 3 Pc. Table Set adds a Rustic touch while keeping the room feeling warm and welcoming. This living table set is made to fit naturally into the room. Crafted from Paper, Metal, Engineered Wood, it is finished in Dark Brown or Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 31.5"W X 30.5"D X 18"H, END TABLE: 15.5"W X 15"D X 23"H&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
-Color: Natural or Black&lt;/p&gt;</t>
+Color: Dark Brown or Black or Natural or Black&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H278" s="52" t="inlineStr">
@@ -40128,7 +40128,7 @@
       </c>
       <c r="AC278" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD278" t="inlineStr">
@@ -40187,8 +40187,8 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Rubberwood, Engineered Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 53 lbs&lt;/p&gt;</t>
+Color: Black or Brown or Black &amp; White or Gray or Light Gray or White&lt;br&gt;
+Weight: 53 or 15 or 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H279" s="54" t="inlineStr">
@@ -40274,7 +40274,7 @@
       </c>
       <c r="AC279" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD279" t="inlineStr">
@@ -40328,13 +40328,13 @@
       <c r="G280" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with FINDLAY 3 Pc. Table Set, styled in Contemporary and designed for everyday comfort. This living table set is made to fit naturally into the room. With Paper, Rubberwood, Engineered Wood and Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
+FINDLAY 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. As a living table set, it is designed to complement your space. The Paper, Rubberwood, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Rubberwood, Engineered Wood.&lt;br&gt;
-Color: Brown&lt;br&gt;
-Weight: 15 lbs&lt;/p&gt;</t>
+Color: Black or Brown or Black &amp; White or Gray or Light Gray or White&lt;br&gt;
+Weight: 53 or 15 or 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H280" s="54" t="inlineStr">
@@ -40420,7 +40420,7 @@
       </c>
       <c r="AC280" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD280" t="inlineStr">
@@ -40474,13 +40474,13 @@
       <c r="G281" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FINDLAY 3 Pc. Table Set adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a living table set, it pairs well with a wide range of interiors. Crafted from Paper, Rubberwood, Engineered Wood, it is finished in Black &amp;amp; White tones that pair easily with surrounding decor.&lt;br&gt;
+FINDLAY 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. As a living table set, it is designed to complement your space. The Paper, Rubberwood, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Rubberwood, Engineered Wood.&lt;br&gt;
-Color: Black &amp;amp; White&lt;br&gt;
-Weight: 25 lbs&lt;/p&gt;</t>
+Color: Black or Brown or Black &amp; White or Gray or Light Gray or White&lt;br&gt;
+Weight: 53 or 15 or 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H281" s="54" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD281" t="inlineStr">
@@ -40620,13 +40620,13 @@
       <c r="G282" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with FINDLAY 3 Pc. Table Set and its Contemporary character. As a living table set, it is designed to complement your space. Finished in Gray tones, the Paper, Rubberwood, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+FINDLAY 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. As a living table set, it is designed to complement your space. The Paper, Rubberwood, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Rubberwood, Engineered Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 25 lbs&lt;/p&gt;</t>
+Color: Black or Brown or Black &amp; White or Gray or Light Gray or White&lt;br&gt;
+Weight: 53 or 15 or 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H282" s="54" t="inlineStr">
@@ -40712,7 +40712,7 @@
       </c>
       <c r="AC282" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD282" t="inlineStr">
@@ -40766,13 +40766,13 @@
       <c r="G283" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FINDLAY 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. This living table set is made to fit naturally into the room. The Paper, Rubberwood, Engineered Wood construction is complemented by Light Gray tones for a polished look.&lt;br&gt;
+FINDLAY 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. As a living table set, it is designed to complement your space. The Paper, Rubberwood, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Rubberwood, Engineered Wood.&lt;br&gt;
-Color: Light Gray&lt;br&gt;
-Weight: 25 lbs&lt;/p&gt;</t>
+Color: Black or Brown or Black &amp; White or Gray or Light Gray or White&lt;br&gt;
+Weight: 53 or 15 or 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H283" s="54" t="inlineStr">
@@ -40858,7 +40858,7 @@
       </c>
       <c r="AC283" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD283" t="inlineStr">
@@ -40912,13 +40912,13 @@
       <c r="G284" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with FINDLAY 3 Pc. Table Set, styled in Contemporary and designed for everyday comfort. Built as a living table set, it pairs well with a wide range of interiors. With Paper, Rubberwood, Engineered Wood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+FINDLAY 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. As a living table set, it is designed to complement your space. The Paper, Rubberwood, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 47.5"W X 24"D X 16"H, END TABLE: 18.5"W X 21"D X 19"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Rubberwood, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 25 lbs&lt;/p&gt;</t>
+Color: Black or Brown or Black &amp; White or Gray or Light Gray or White&lt;br&gt;
+Weight: 53 or 15 or 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H284" s="54" t="inlineStr">
@@ -41004,7 +41004,7 @@
       </c>
       <c r="AC284" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD284" t="inlineStr">
@@ -41061,7 +41061,7 @@
 HOLEN 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. Built as a living table set, it pairs well with a wide range of interiors. The Paper Veneer, Engineered Wood construction is complemented by Gray tones for a polished look.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 36"W X 36"D X 18"H, END TABLE: 24"W X 24"D X 24"H&lt;/p&gt;
 &lt;p&gt;Materials: Paper Veneer, Engineered Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Gray or Natural&lt;br&gt;
 Weight: 99.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -41148,7 +41148,7 @@
       </c>
       <c r="AC285" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD285" t="inlineStr">
@@ -41202,10 +41202,10 @@
       <c r="G286" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with HOLEN 3 Pc. Table Set, styled in Contemporary and designed for everyday comfort. As a living table set, it is designed to complement your space. With Paper Veneer, Engineered Wood and Natural tones, it blends structure and softness in one clean profile.&lt;br&gt;
+HOLEN 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. Built as a living table set, it pairs well with a wide range of interiors. The Paper Veneer, Engineered Wood construction is complemented by Gray tones for a polished look.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 36"W X 36"D X 18"H, END TABLE: 24"W X 24"D X 24"H&lt;/p&gt;
 &lt;p&gt;Materials: Paper Veneer, Engineered Wood.&lt;br&gt;
-Color: Natural&lt;br&gt;
+Color: Gray or Natural&lt;br&gt;
 Weight: 99.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -41292,7 +41292,7 @@
       </c>
       <c r="AC286" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD286" t="inlineStr">
@@ -41349,7 +41349,7 @@
 Elevate your space with OPHIRA 3 Pc. Table Set, styled in Rustic and designed for everyday comfort. Built as a living table set, it pairs well with a wide range of interiors. With Paper, Metal, Engineered Wood and Dark Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 24"W X 24"D X 18"H, END TABLE: 18.5"W X 18.5"D X 23"H&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
-Color: Dark Brown&lt;/p&gt;</t>
+Color: Dark Brown or Natural&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H287" s="28" t="inlineStr">
@@ -41433,7 +41433,7 @@
       </c>
       <c r="AC287" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD287" t="inlineStr">
@@ -41487,10 +41487,10 @@
       <c r="G288" s="28" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-OPHIRA 3 Pc. Table Set adds a Rustic touch while keeping the room feeling warm and welcoming. As a living table set, it is designed to complement your space. Crafted from Paper, Metal, Engineered Wood, it is finished in Natural tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with OPHIRA 3 Pc. Table Set, styled in Rustic and designed for everyday comfort. Built as a living table set, it pairs well with a wide range of interiors. With Paper, Metal, Engineered Wood and Dark Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 24"W X 24"D X 18"H, END TABLE: 18.5"W X 18.5"D X 23"H&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
-Color: Natural&lt;/p&gt;</t>
+Color: Dark Brown or Natural&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H288" s="28" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="AC288" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD288" t="inlineStr">
@@ -41631,7 +41631,7 @@
 PALLAS 3 Pc. Table Set brings a Rustic look to your home with a refined, comfortable feel. This living table set is made to fit naturally into the room. The Paper, Metal, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 41.5"W X 19"D X 18.5"H, END TABLE: 15.5"W X 15.5"D X 23"H&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
-Color: Black&lt;/p&gt;</t>
+Color: Black or Natural or White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H289" s="52" t="inlineStr">
@@ -41715,7 +41715,7 @@
       </c>
       <c r="AC289" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD289" t="inlineStr">
@@ -41769,10 +41769,10 @@
       <c r="G290" s="52" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with PALLAS 3 Pc. Table Set, styled in Rustic and designed for everyday comfort. Built as a living table set, it pairs well with a wide range of interiors. With Paper, Metal, Engineered Wood and Natural tones, it blends structure and softness in one clean profile.&lt;br&gt;
+PALLAS 3 Pc. Table Set brings a Rustic look to your home with a refined, comfortable feel. This living table set is made to fit naturally into the room. The Paper, Metal, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 41.5"W X 19"D X 18.5"H, END TABLE: 15.5"W X 15.5"D X 23"H&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
-Color: Natural&lt;/p&gt;</t>
+Color: Black or Natural or White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H290" s="52" t="inlineStr">
@@ -41856,7 +41856,7 @@
       </c>
       <c r="AC290" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD290" t="inlineStr">
@@ -41910,10 +41910,10 @@
       <c r="G291" s="52" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PALLAS 3 Pc. Table Set adds a Rustic touch while keeping the room feeling warm and welcoming. As a living table set, it is designed to complement your space. Crafted from Paper, Metal, Engineered Wood, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+PALLAS 3 Pc. Table Set brings a Rustic look to your home with a refined, comfortable feel. This living table set is made to fit naturally into the room. The Paper, Metal, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 41.5"W X 19"D X 18.5"H, END TABLE: 15.5"W X 15.5"D X 23"H&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
-Color: White&lt;/p&gt;</t>
+Color: Black or Natural or White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H291" s="52" t="inlineStr">
@@ -41997,7 +41997,7 @@
       </c>
       <c r="AC291" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD291" t="inlineStr">
@@ -42054,7 +42054,7 @@
 RONDE 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. Built as a living table set, it pairs well with a wide range of interiors. The Paper, Metal, Engineered Wood construction is complemented by Natural tones for a polished look.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 34"W X 34"D X 18"H, END TABLE: 18"W X 18"D X 23"H&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
-Color: Natural&lt;/p&gt;</t>
+Color: Natural or White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H292" s="24" t="inlineStr">
@@ -42138,7 +42138,7 @@
       </c>
       <c r="AC292" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD292" t="inlineStr">
@@ -42192,10 +42192,10 @@
       <c r="G293" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with RONDE 3 Pc. Table Set, styled in Contemporary and designed for everyday comfort. As a living table set, it is designed to complement your space. With Paper, Metal, Engineered Wood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+RONDE 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. Built as a living table set, it pairs well with a wide range of interiors. The Paper, Metal, Engineered Wood construction is complemented by Natural tones for a polished look.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 34"W X 34"D X 18"H, END TABLE: 18"W X 18"D X 23"H&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
-Color: White&lt;/p&gt;</t>
+Color: Natural or White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H293" s="24" t="inlineStr">
@@ -42279,7 +42279,7 @@
       </c>
       <c r="AC293" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD293" t="inlineStr">
@@ -42336,7 +42336,7 @@
 Make the room feel complete with WHETSTONE 3 Pc. Table Set and its Contemporary character. This living table set is made to fit naturally into the room. Finished in Black tones, the Paper, Metal, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 31.5"W X 30.5"D X 17"H, END TABLE: 15.5"W X 15"D X 22.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -42423,7 +42423,7 @@
       </c>
       <c r="AC294" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD294" t="inlineStr">
@@ -42477,10 +42477,10 @@
       <c r="G295" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-WHETSTONE 3 Pc. Table Set brings a Contemporary look to your home with a refined, comfortable feel. Built as a living table set, it pairs well with a wide range of interiors. The Paper, Metal, Engineered Wood construction is complemented by White tones for a polished look.&lt;br&gt;
+Make the room feel complete with WHETSTONE 3 Pc. Table Set and its Contemporary character. This living table set is made to fit naturally into the room. Finished in Black tones, the Paper, Metal, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: COFFEE TABLE: 31.5"W X 30.5"D X 17"H, END TABLE: 15.5"W X 15"D X 22.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Paper, Metal, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -42567,7 +42567,7 @@
       </c>
       <c r="AC295" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD295" t="inlineStr">
@@ -42715,7 +42715,7 @@
       </c>
       <c r="AC296" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD296" t="inlineStr">
@@ -42863,7 +42863,7 @@
       </c>
       <c r="AC297" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD297" t="inlineStr">
@@ -43006,7 +43006,7 @@
       </c>
       <c r="AC298" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD298" t="inlineStr">
@@ -43155,7 +43155,7 @@
       </c>
       <c r="AC299" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD299" t="inlineStr">
@@ -43303,7 +43303,7 @@
       </c>
       <c r="AC300" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD300" t="inlineStr">
@@ -43446,7 +43446,7 @@
       </c>
       <c r="AC301" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD301" t="inlineStr">
@@ -43589,7 +43589,7 @@
       </c>
       <c r="AC302" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD302" t="inlineStr">
@@ -43735,7 +43735,7 @@
       </c>
       <c r="AC303" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD303" t="inlineStr">
@@ -43879,7 +43879,7 @@
       </c>
       <c r="AC304" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD304" t="inlineStr">
@@ -44020,7 +44020,7 @@
       </c>
       <c r="AC305" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD305" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="AC306" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD306" t="inlineStr">
@@ -44298,7 +44298,7 @@
       </c>
       <c r="AC307" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD307" t="inlineStr">
@@ -44435,7 +44435,7 @@
       </c>
       <c r="AC308" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD308" t="inlineStr">
@@ -44578,7 +44578,7 @@
       </c>
       <c r="AC309" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD309" t="inlineStr">
@@ -44721,7 +44721,7 @@
       </c>
       <c r="AC310" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD310" t="inlineStr">
@@ -44864,7 +44864,7 @@
       </c>
       <c r="AC311" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD311" t="inlineStr">

--- a/FOA Singles/Living-Single.xlsx
+++ b/FOA Singles/Living-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -838,12 +838,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ALMA 60" TV Stand in Gray | GOODDEGG</t>
+          <t>ALMA 60" TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The ALMA TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALMA 60" TV Stand TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ALMA 72" TV Stand in Gray | GOODDEGG</t>
+          <t>ALMA 72" TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The ALMA TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALMA 72" TV Stand TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BLAIR 70" TV Console in White Champagne Gray | GOODDEGG</t>
+          <t>BLAIR 70" TV Console | GOODDEGG</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The BLAIR TV Console brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BLAIR 70" TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="H5" s="28" t="inlineStr">
         <is>
-          <t>Borrego TV Stand in Dark Oak | GOODDEGG</t>
+          <t>BORREGO TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I5" s="28" t="inlineStr">
         <is>
-          <t>The BORREGO TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BORREGO TV Stand TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J5" s="28" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="H6" s="28" t="inlineStr">
         <is>
-          <t>Borrego TV Stand in Antique White | GOODDEGG</t>
+          <t>BORREGO TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I6" s="28" t="inlineStr">
         <is>
-          <t>The BORREGO TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BORREGO TV Stand TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J6" s="28" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BROMOAK Console Base in Weathered Oak | GOODDEGG</t>
+          <t>BROMOAK Console Base | GOODDEGG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The BROMOAK Console Base brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BROMOAK Console Base TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BROMOAK Left Facing Unit Base in Weathered Oak | GOODDEGG</t>
+          <t>BROMOAK Left Facing Unit Base | GOODDEGG</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>The BROMOAK Left Facing Unit Base brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BROMOAK Left Facing Unit Base TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BROMOAK Left Facing Unit Top in Weathered Oak | GOODDEGG</t>
+          <t>BROMOAK Left Facing Unit Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>The BROMOAK Left Facing Unit Top brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BROMOAK Left Facing Unit Top TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BROMOAK Right Facing Unit Base in Weathered Oak | GOODDEGG</t>
+          <t>BROMOAK Right Facing Unit Base | GOODDEGG</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>The BROMOAK Right Facing Unit Base brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BROMOAK Right Facing Unit Base TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BROMOAK Right Facing Unit Top in Weathered Oak | GOODDEGG</t>
+          <t>BROMOAK Right Facing Unit Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>The BROMOAK Right Facing Unit Top brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BROMOAK Right Facing Unit Top TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2271,12 +2271,12 @@
       </c>
       <c r="H12" s="30" t="inlineStr">
         <is>
-          <t>CERRO 59" TV Console in Black | GOODDEGG</t>
+          <t>CERRO 59" TV Console | GOODDEGG</t>
         </is>
       </c>
       <c r="I12" s="30" t="inlineStr">
         <is>
-          <t>The CERRO TV Console brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CERRO 59" TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J12" s="30" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="H13" s="30" t="inlineStr">
         <is>
-          <t>CERRO 59" TV Console in White | GOODDEGG</t>
+          <t>CERRO 59" TV Console | GOODDEGG</t>
         </is>
       </c>
       <c r="I13" s="30" t="inlineStr">
         <is>
-          <t>The CERRO TV Console brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CERRO 59" TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J13" s="30" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DIETRICH 60" TV Console in Black | GOODDEGG</t>
+          <t>DIETRICH 60" TV Console | GOODDEGG</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>The DIETRICH TV Console brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DIETRICH 60" TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>EGALEO 55" TV Console in Black White | GOODDEGG</t>
+          <t>EGALEO 55" TV Console | GOODDEGG</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>The EGALEO TV Console brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EGALEO 55" TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="H16" s="33" t="inlineStr">
         <is>
-          <t>ERNST 60" TV Stand in Black | GOODDEGG</t>
+          <t>ERNST 60" TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I16" s="33" t="inlineStr">
         <is>
-          <t>The ERNST TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ERNST 60" TV Stand TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J16" s="33" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="H17" s="33" t="inlineStr">
         <is>
-          <t>ERNST 60" TV Stand in White | GOODDEGG</t>
+          <t>ERNST 60" TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I17" s="33" t="inlineStr">
         <is>
-          <t>The ERNST TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ERNST 60" TV Stand TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J17" s="33" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>EVOS 63" TV Console in Black White | GOODDEGG</t>
+          <t>EVOS 63" TV Console | GOODDEGG</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>The EVOS TV Console brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EVOS 63" TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Georgia 60" TV Stand in Antique White | GOODDEGG</t>
+          <t>GEORGIA 60" TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>The GEORGIA TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GEORGIA 60" TV Stand TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Georgia 72" TV Stand in Antique White | GOODDEGG</t>
+          <t>GEORGIA 72" TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>The GEORGIA TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GEORGIA 72" TV Stand TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kebbyll 60" TV Stand in Antique Black Natural Tone | GOODDEGG</t>
+          <t>KEBBYLL 60" TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>The KEBBYLL TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KEBBYLL 60" TV Stand TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KEBBYLL Bridge in Antique Black Natural Tone | GOODDEGG</t>
+          <t>KEBBYLL Bridge | GOODDEGG</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>The KEBBYLL Bridge brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KEBBYLL Bridge TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>KEBBYLL Pier Cabinet in Antique Black Natural Tone | GOODDEGG</t>
+          <t>KEBBYLL Pier Cabinet | GOODDEGG</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>The KEBBYLL Pier Cabinet brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KEBBYLL Pier Cabinet TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>NEAPOLI 63" TV Console in Black White | GOODDEGG</t>
+          <t>NEAPOLI 63" TV Console | GOODDEGG</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>The NEAPOLI TV Console brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEAPOLI 63" TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NINOVE 55" TV Console in White | GOODDEGG</t>
+          <t>NINOVE 55" TV Console | GOODDEGG</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>The NINOVE TV Console brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NINOVE 55" TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PRESHO 72" TV Stand in Dark Oak | GOODDEGG</t>
+          <t>PRESHO 72" TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>The PRESHO TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PRESHO 72" TV Stand TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sabugal 60" TV Stand in White | GOODDEGG</t>
+          <t>SABUGAL 60" TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>The SABUGAL TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SABUGAL 60" TV Stand TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sabugal 70" TV Stand in White | GOODDEGG</t>
+          <t>SABUGAL 70" TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>The SABUGAL TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SABUGAL 70" TV Stand TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SILVER CREEK 2 Pc. Pier Shelves (1 Pair) in Brown Silver | GOODDE</t>
+          <t>SILVER CREEK 2 Pc. Pier Shelves (1 Pair) | GOODDEGG</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>The CREEK Pier Shelves ( Pair) brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TV Console SILVER CREEK 2 Pc. Pier Shelves (1 supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4818,12 +4818,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SILVER CREEK 52" TV Console in Brown Silver | GOODDEGG</t>
+          <t>SILVER CREEK 52" TV Console | GOODDEGG</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>The CREEK TV Console brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SILVER CREEK 52" TV Console supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ALVISE Coffee Table in Champagne | GOODDEGG</t>
+          <t>ALVISE Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>The ALVISE Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALVISE Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ARLINGTON Coffee Table in Antique White | GOODDEGG</t>
+          <t>ARLINGTON Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>The ARLINGTON Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARLINGTON Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5241,12 +5241,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ATWOOD II Coffee Table in Dark Walnut | GOODDEGG</t>
+          <t>ATWOOD II Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>The ATWOOD II Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ATWOOD II Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>AUGSBURG Coffee Table in Walnut Gold | GOODDEGG</t>
+          <t>AUGSBURG Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>The AUGSBURG Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AUGSBURG Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>BACERRA Coffee Table in Antique White Gold | GOODDEGG</t>
+          <t>BACERRA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>The BACERRA Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BACERRA Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>BATAM II Coffee Table in White Natural Tone | GOODDEGG</t>
+          <t>BATAM II Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>The BATAM II Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BATAM II Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>BIMA II Coffee Table in White Natural Tone | GOODDEGG</t>
+          <t>BIMA II Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>The BIMA II Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BIMA II Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>BISHOP Coffee Table in Black Gray | GOODDEGG</t>
+          <t>BISHOP Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>The BISHOP Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BISHOP Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CALANDRA Coffee Table in Antique Black | GOODDEGG</t>
+          <t>CALANDRA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>The CALANDRA Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CALANDRA Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CARRIE Coffee Table in Antique Black | GOODDEGG</t>
+          <t>CARRIE Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>The CARRIE Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CARRIE Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CONISBROUGH Cocktail Table in Modern | GOODDEGG</t>
+          <t>CONISBROUGH Cocktail Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>The CONISBROUGH Cocktail Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CONISBROUGH Cocktail Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CONISBROUGH Oval Cocktail Table in Modern | GOODDEGG</t>
+          <t>CONISBROUGH Oval Cocktail Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>The CONISBROUGH Oval Cocktail Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CONISBROUGH Oval Cocktail Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>COOKSHIRE Coffee Table in Rich Tobacco | GOODDEGG</t>
+          <t>COOKSHIRE Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>The COOKSHIRE Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>COOKSHIRE Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CORINNE Coffee Table in White Distressed Dark Oak | GOODDEGG</t>
+          <t>CORINNE Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>The CORINNE Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CORINNE Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CRYSTAL COVE II Round Coffee Table w/ Stools creates a welcoming place for meals and. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRYSTAL COVE II Round Coffee Table w/ 4 Stools supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -7087,12 +7087,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CRYSTAL FALLS Coffee Table in Dark Cherry | GOODDEGG</t>
+          <t>CRYSTAL FALLS Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>The CRYSTAL FALLS Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRYSTAL FALLS Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H47" s="35" t="inlineStr">
         <is>
-          <t>DUBENDORF Coffee Table in Black | GOODDEGG</t>
+          <t>DUBENDORF Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I47" s="35" t="inlineStr">
         <is>
-          <t>The DUBENDORF Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DUBENDORF Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J47" s="35" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="H48" s="35" t="inlineStr">
         <is>
-          <t>DUBENDORF Coffee Table in White | GOODDEGG</t>
+          <t>DUBENDORF Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I48" s="35" t="inlineStr">
         <is>
-          <t>The DUBENDORF Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DUBENDORF Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J48" s="35" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>EIMEAR Coffee Table in White Black | GOODDEGG</t>
+          <t>EIMEAR Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>The EIMEAR Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EIMEAR Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FINLEY Coffee Table in Espresso | GOODDEGG</t>
+          <t>FINLEY Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>The FINLEY Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FINLEY Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>GIORDANI Coffee Table in Weathered Oak | GOODDEGG</t>
+          <t>GIORDANI Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>The GIORDANI Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GIORDANI Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>GRANVIA Coffee Table in Dark Cherry | GOODDEGG</t>
+          <t>GRANVIA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>The GRANVIA Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRANVIA Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>GRASTEN Square Coffee Table in Ash Gray | GOODDEGG</t>
+          <t>GRASTEN Square Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>The GRASTEN Square Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRASTEN Square Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -8236,12 +8236,12 @@
       </c>
       <c r="H54" s="37" t="inlineStr">
         <is>
-          <t>GUIS Round Coffee Table in Natural Tone Beige | GOODDEGG</t>
+          <t>GUIS Round Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I54" s="37" t="inlineStr">
         <is>
-          <t>The GUIS Round Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GUIS Round Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J54" s="37" t="inlineStr">
@@ -8386,12 +8386,12 @@
       </c>
       <c r="H55" s="37" t="inlineStr">
         <is>
-          <t>GUIS Round Coffee Table in Natural Tone Dark Gray | GOODDEGG</t>
+          <t>GUIS Round Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I55" s="37" t="inlineStr">
         <is>
-          <t>The GUIS Round Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GUIS Round Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J55" s="37" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>HALCASTER Coffee Table in Java | GOODDEGG</t>
+          <t>HALCASTER Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>The HALCASTER Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALCASTER Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="H57" s="39" t="inlineStr">
         <is>
-          <t>HALEWOOD Cocktail Table in Black | GOODDEGG</t>
+          <t>HALEWOOD Cocktail Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I57" s="39" t="inlineStr">
         <is>
-          <t>The HALEWOOD Cocktail Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALEWOOD Cocktail Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J57" s="39" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H58" s="39" t="inlineStr">
         <is>
-          <t>HALEWOOD Cocktail Table in Oak | GOODDEGG</t>
+          <t>HALEWOOD Cocktail Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I58" s="39" t="inlineStr">
         <is>
-          <t>The HALEWOOD Cocktail Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALEWOOD Cocktail Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J58" s="39" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>IZAR Coffee Table in White Gun Metal | GOODDEGG</t>
+          <t>IZAR Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>The IZAR Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>IZAR Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -9104,12 +9104,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>JOLIET Coffee Table in Antique White | GOODDEGG</t>
+          <t>JOLIET Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>The JOLIET Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JOLIET Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>JOLIET Sofa Table in Antique White | GOODDEGG</t>
+          <t>JOLIET Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>The JOLIET Sofa Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JOLIET Sofa Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H62" s="41" t="inlineStr">
         <is>
-          <t>KOBLENZ Coffee Table in Light Teal | GOODDEGG</t>
+          <t>KOBLENZ Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I62" s="41" t="inlineStr">
         <is>
-          <t>The KOBLENZ Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KOBLENZ Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J62" s="41" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H63" s="41" t="inlineStr">
         <is>
-          <t>KOBLENZ Coffee Table in Dark Walnut | GOODDEGG</t>
+          <t>KOBLENZ Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I63" s="41" t="inlineStr">
         <is>
-          <t>The KOBLENZ Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KOBLENZ Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J63" s="41" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>LAILA Coffee Table in Chrome | GOODDEGG</t>
+          <t>LAILA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>The LAILA Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LAILA Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -9817,12 +9817,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>LOBB Coffee Table in Natural Tone Black | GOODDEGG</t>
+          <t>LOBB Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>The LOBB Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LOBB Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>LODIA Coffee Table in Gray | GOODDEGG</t>
+          <t>LODIA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>The LODIA Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LODIA Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -10101,12 +10101,12 @@
       </c>
       <c r="H67" s="28" t="inlineStr">
         <is>
-          <t>LODIA III Coffee Table in Black | GOODDEGG</t>
+          <t>LODIA III Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I67" s="28" t="inlineStr">
         <is>
-          <t>The LODIA III Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LODIA III Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J67" s="28" t="inlineStr">
@@ -10243,12 +10243,12 @@
       </c>
       <c r="H68" s="28" t="inlineStr">
         <is>
-          <t>LODIA III Coffee Table in White | GOODDEGG</t>
+          <t>LODIA III Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I68" s="28" t="inlineStr">
         <is>
-          <t>The LODIA III Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LODIA III Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J68" s="28" t="inlineStr">
@@ -10384,12 +10384,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>LUDVIG Coffee Table in Chrome Clear | GOODDEGG</t>
+          <t>LUDVIG Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>The LUDVIG Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LUDVIG Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -10527,12 +10527,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>MAJKEN Coffee Table in White Natural Tone | GOODDEGG</t>
+          <t>MAJKEN Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>The MAJKEN Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MAJKEN Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>MANHATTAN IV Coffee Table in Brown Cherry | GOODDEGG</t>
+          <t>MANHATTAN IV Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>The MANHATTAN IV Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MANHATTAN IV Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>MANHATTAN IV End Table in Brown Cherry | GOODDEGG</t>
+          <t>MANHATTAN IV End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>The MANHATTAN IV End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MANHATTAN IV End Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -10948,12 +10948,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>MANHATTAN IV Sofa Table in Brown Cherry | GOODDEGG</t>
+          <t>MANHATTAN IV Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>The MANHATTAN IV Sofa Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MANHATTAN IV Sofa Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -11086,12 +11086,12 @@
       </c>
       <c r="H74" s="35" t="inlineStr">
         <is>
-          <t>MANNEDORF Coffee Table in Black Dark Walnut | GOODDEGG</t>
+          <t>MANNEDORF Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I74" s="35" t="inlineStr">
         <is>
-          <t>The MANNEDORF Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MANNEDORF Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J74" s="35" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H75" s="35" t="inlineStr">
         <is>
-          <t>MANNEDORF Coffee Table in Black White | GOODDEGG</t>
+          <t>MANNEDORF Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I75" s="35" t="inlineStr">
         <is>
-          <t>The MANNEDORF Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MANNEDORF Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J75" s="35" t="inlineStr">
@@ -11377,12 +11377,12 @@
       </c>
       <c r="H76" s="33" t="inlineStr">
         <is>
-          <t>MARSTON Coffee Table in Dark Walnut | GOODDEGG</t>
+          <t>MARSTON Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I76" s="33" t="inlineStr">
         <is>
-          <t>The MARSTON Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARSTON Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J76" s="33" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="H77" s="33" t="inlineStr">
         <is>
-          <t>MARSTON Coffee Table in Champagne | GOODDEGG</t>
+          <t>MARSTON Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I77" s="33" t="inlineStr">
         <is>
-          <t>The MARSTON Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARSTON Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J77" s="33" t="inlineStr">
@@ -11667,12 +11667,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>MAY Coffee Table in Brown Cherry | GOODDEGG</t>
+          <t>MAY Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>The MAY Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MAY Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>MAY Side Table in Brown Cherry | GOODDEGG</t>
+          <t>MAY Side Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>The MAY Side Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MAY Side Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>MEADOW Coffee Table in Antique Black | GOODDEGG</t>
+          <t>MEADOW Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>The MEADOW Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MEADOW Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -12094,12 +12094,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>MEADOW Side Table in Antique Black | GOODDEGG</t>
+          <t>MEADOW Side Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>The MEADOW Side Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MEADOW Side Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -12235,12 +12235,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>MEDA Coffee Table in White Chrome | GOODDEGG</t>
+          <t>MEDA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>The MEDA Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MEDA Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -12380,12 +12380,12 @@
       </c>
       <c r="H83" s="37" t="inlineStr">
         <is>
-          <t>MIKA Coffee Table w/ Cushion Top in Antique Oak | GOODDEGG</t>
+          <t>MIKA Coffee Table w/ Cushion Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I83" s="37" t="inlineStr">
         <is>
-          <t>The MIKA Coffee Table w/ Cushion Top creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MIKA Coffee Table w/ Cushion Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J83" s="37" t="inlineStr">
@@ -12526,12 +12526,12 @@
       </c>
       <c r="H84" s="37" t="inlineStr">
         <is>
-          <t>MIKA Coffee Table w/ Cushion Top in Antique Gray | GOODDEGG</t>
+          <t>MIKA Coffee Table w/ Cushion Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I84" s="37" t="inlineStr">
         <is>
-          <t>The MIKA Coffee Table w/ Cushion Top creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MIKA Coffee Table w/ Cushion Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J84" s="37" t="inlineStr">
@@ -12671,12 +12671,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>MOA Coffee Table in White Natural Tone | GOODDEGG</t>
+          <t>MOA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>The MOA Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MOA Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -12813,12 +12813,12 @@
       </c>
       <c r="H86" s="39" t="inlineStr">
         <is>
-          <t>NAHARA Coffee Table in Black | GOODDEGG</t>
+          <t>NAHARA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I86" s="39" t="inlineStr">
         <is>
-          <t>The NAHARA Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NAHARA Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J86" s="39" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="H87" s="39" t="inlineStr">
         <is>
-          <t>NAHARA Coffee Table in Gray | GOODDEGG</t>
+          <t>NAHARA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I87" s="39" t="inlineStr">
         <is>
-          <t>The NAHARA Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NAHARA Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J87" s="39" t="inlineStr">
@@ -13097,12 +13097,12 @@
       </c>
       <c r="H88" s="39" t="inlineStr">
         <is>
-          <t>NAHARA Coffee Table in White | GOODDEGG</t>
+          <t>NAHARA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I88" s="39" t="inlineStr">
         <is>
-          <t>The NAHARA Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NAHARA Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J88" s="39" t="inlineStr">
@@ -13239,12 +13239,12 @@
       </c>
       <c r="H89" s="41" t="inlineStr">
         <is>
-          <t>NINOVE Coffee Table in Black Chrome | GOODDEGG</t>
+          <t>NINOVE Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I89" s="41" t="inlineStr">
         <is>
-          <t>The NINOVE Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NINOVE Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J89" s="41" t="inlineStr">
@@ -13383,12 +13383,12 @@
       </c>
       <c r="H90" s="41" t="inlineStr">
         <is>
-          <t>NINOVE Coffee Table in White Chrome | GOODDEGG</t>
+          <t>NINOVE Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I90" s="41" t="inlineStr">
         <is>
-          <t>The NINOVE Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NINOVE Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J90" s="41" t="inlineStr">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="H91" s="44" t="inlineStr">
         <is>
-          <t>NORTHWICH Coffee Table in White Matte Gold | GOODDEGG</t>
+          <t>NORTHWICH Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I91" s="44" t="inlineStr">
         <is>
-          <t>The NORTHWICH Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NORTHWICH Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J91" s="44" t="inlineStr">
@@ -13669,12 +13669,12 @@
       </c>
       <c r="H92" s="44" t="inlineStr">
         <is>
-          <t>NORTHWICH Coffee Table in Black Gray Matte Gold | GOODDEGG</t>
+          <t>NORTHWICH Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I92" s="44" t="inlineStr">
         <is>
-          <t>The NORTHWICH Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NORTHWICH Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J92" s="44" t="inlineStr">
@@ -13810,12 +13810,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>NORTHWICH Oval Coffee Table in Black Gray Matte Gold | GOODD</t>
+          <t>NORTHWICH Oval Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>The NORTHWICH Oval Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NORTHWICH Oval Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>NOVA Coffee Table in Satin Plated Black | GOODDEGG</t>
+          <t>NOVA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>The NOVA Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NOVA Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -14086,12 +14086,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>OAKWAY Coffee Table in Weathered Oak | GOODDEGG</t>
+          <t>OAKWAY Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>The OAKWAY Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OAKWAY Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>ORLA II Coffee Table in Satin Plated Black | GOODDEGG</t>
+          <t>ORLA II Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>The ORLA II Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ORLA II Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -14364,12 +14364,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>ORRIN Coffee Table in Gray Walnut | GOODDEGG</t>
+          <t>ORRIN Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>The ORRIN Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ORRIN Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -14510,12 +14510,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>POLTIMORE Round Cocktail Table in Oak | GOODDEGG</t>
+          <t>POLTIMORE Round Cocktail Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>The POLTIMORE Round Cocktail Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>POLTIMORE Round Cocktail Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -14651,12 +14651,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>RAYA Coffee Table in White | GOODDEGG</t>
+          <t>RAYA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>The RAYA Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RAYA Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="H100" s="30" t="inlineStr">
         <is>
-          <t>ROCHESTER Coffee Table in Champagne | GOODDEGG</t>
+          <t>ROCHESTER Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I100" s="30" t="inlineStr">
         <is>
-          <t>The ROCHESTER Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ROCHESTER Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J100" s="30" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="H101" s="30" t="inlineStr">
         <is>
-          <t>ROCHESTER Coffee Table in Champagne | GOODDEGG</t>
+          <t>ROCHESTER Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I101" s="30" t="inlineStr">
         <is>
-          <t>The ROCHESTER Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ROCHESTER Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J101" s="30" t="inlineStr">
@@ -15092,12 +15092,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ROSETTA Coffee Table in Dark Walnut | GOODDEGG</t>
+          <t>ROSETTA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>The ROSETTA Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ROSETTA Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -15233,12 +15233,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>ROXO Coffee Table in Satin Plated Black | GOODDEGG</t>
+          <t>ROXO Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>The ROXO Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ROXO Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -15370,12 +15370,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>RYLEE Coffee Table in Chrome | GOODDEGG</t>
+          <t>RYLEE Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>The RYLEE Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RYLEE Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -15511,12 +15511,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>SINDAL Coffee Table in Black | GOODDEGG</t>
+          <t>SINDAL Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>The SINDAL Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINDAL Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -15648,12 +15648,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>SINDAL Round Cocktail Table in Black | GOODDEGG</t>
+          <t>SINDAL Round Cocktail Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>The SINDAL Round Cocktail Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINDAL Round Cocktail Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -15785,12 +15785,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>SLOANE Coffee Table in White Dark Gray Chrome | GOODDEGG</t>
+          <t>SLOANE Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>The SLOANE Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SLOANE Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -15923,12 +15923,12 @@
       </c>
       <c r="H108" s="46" t="inlineStr">
         <is>
-          <t>STATEN Coffee Table in Glossy Black Chrome | GOODDEGG</t>
+          <t>STATEN Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I108" s="46" t="inlineStr">
         <is>
-          <t>The STATEN Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STATEN Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J108" s="46" t="inlineStr">
@@ -16069,12 +16069,12 @@
       </c>
       <c r="H109" s="46" t="inlineStr">
         <is>
-          <t>STATEN Coffee Table in Glossy White Chrome | GOODDEGG</t>
+          <t>STATEN Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I109" s="46" t="inlineStr">
         <is>
-          <t>The STATEN Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STATEN Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J109" s="46" t="inlineStr">
@@ -16214,12 +16214,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>SUNDANCE Coffee Table in Chrome | GOODDEGG</t>
+          <t>SUNDANCE Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>The SUNDANCE Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SUNDANCE Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -16355,12 +16355,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>SURDAL Oval Coffee Table in Black | GOODDEGG</t>
+          <t>SURDAL Oval Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>The SURDAL Oval Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SURDAL Oval Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -16492,12 +16492,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>SURDAL Round Coffee Table in Black | GOODDEGG</t>
+          <t>SURDAL Round Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>The SURDAL Round Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SURDAL Round Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -16632,12 +16632,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>TADCASTER Coffee Table in Dark Cherry | GOODDEGG</t>
+          <t>TADCASTER Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>The TADCASTER Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TADCASTER Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -16773,12 +16773,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>TANIKA Coffee Table in Chrome | GOODDEGG</t>
+          <t>TANIKA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>The TANIKA Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TANIKA Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>THISTED Rect Marble Coffee Table w/ Casters creates a welcoming place for meals and. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>THISTED Rect Marble Coffee Table w/ Casters supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>THISTED Triangle Marble Coffee Table in White Black | GOODDEGG</t>
+          <t>THISTED Triangle Marble Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>THISTED Triangle Marble Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>THISTED Triangle Marble Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -17196,12 +17196,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>TITUS Coffee Table in White Chrome | GOODDEGG</t>
+          <t>TITUS Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>The TITUS Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TITUS Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -17337,12 +17337,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>TORKEL Coffee Table in White Chrome | GOODDEGG</t>
+          <t>TORKEL Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>The TORKEL Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TORKEL Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -17478,12 +17478,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>VALO Coffee Table in Satin Plated Black | GOODDEGG</t>
+          <t>VALO Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>The VALO Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VALO Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -17617,12 +17617,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>VILLARSGLANE Coffee Table in Chrome | GOODDEGG</t>
+          <t>VILLARSGLANE Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>The VILLARSGLANE Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VILLARSGLANE Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -17754,12 +17754,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>VIRDEN Oval Cocktail Table in Black White Gold | GOODDEGG</t>
+          <t>VIRDEN Oval Cocktail Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>The VIRDEN Oval Cocktail Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VIRDEN Oval Cocktail Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -17895,12 +17895,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>VIRDEN Rectangle Cocktail Table in Black White Gold | GOODDE</t>
+          <t>VIRDEN Rectangle Cocktail Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>The VIRDEN Rectangle Cocktail Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VIRDEN Rectangle Cocktail Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -18036,12 +18036,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>VIRDEN Round Cocktail Table in Black White Gold | GOODDEGG</t>
+          <t>VIRDEN Round Cocktail Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>The VIRDEN Round Cocktail Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VIRDEN Round Cocktail Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -18177,12 +18177,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>VIRDEN Square Cocktail Table in Black White Gold | GOODDEGG</t>
+          <t>VIRDEN Square Cocktail Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>The VIRDEN Square Cocktail Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VIRDEN Square Cocktail Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -18321,12 +18321,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>WALWORTH Coffee Table in Dark Oak | GOODDEGG</t>
+          <t>WALWORTH Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>The WALWORTH Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WALWORTH Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -18461,12 +18461,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>WESTERHAM Oval Cocktail Table in Dark Cherry | GOODDEGG</t>
+          <t>WESTERHAM Oval Cocktail Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>The WESTERHAM Oval Cocktail Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WESTERHAM Oval Cocktail Table Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -18601,12 +18601,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>WETTINGEN Coffee Table in Chrome | GOODDEGG</t>
+          <t>WETTINGEN Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>The WETTINGEN Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WETTINGEN Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -18741,12 +18741,12 @@
       </c>
       <c r="H128" s="37" t="inlineStr">
         <is>
-          <t>WETZIKON Coffee Table in Black Silver | GOODDEGG</t>
+          <t>WETZIKON Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I128" s="37" t="inlineStr">
         <is>
-          <t>The WETZIKON Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WETZIKON Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J128" s="37" t="inlineStr">
@@ -18889,12 +18889,12 @@
       </c>
       <c r="H129" s="37" t="inlineStr">
         <is>
-          <t>WETZIKON Coffee Table in White Silver | GOODDEGG</t>
+          <t>WETZIKON Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I129" s="37" t="inlineStr">
         <is>
-          <t>The WETZIKON Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WETZIKON Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J129" s="37" t="inlineStr">
@@ -19034,12 +19034,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>XANTHUS Coffee Table in Black | GOODDEGG</t>
+          <t>XANTHUS Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>The XANTHUS Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>XANTHUS Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -19171,12 +19171,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>ZOLA Coffee Table in Chrome | GOODDEGG</t>
+          <t>ZOLA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>The ZOLA Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZOLA Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -19312,12 +19312,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ALVISE End Table in Champagne | GOODDEGG</t>
+          <t>ALVISE End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>The ALVISE End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALVISE End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -19451,12 +19451,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>ARLINGTON End Table in Antique White | GOODDEGG</t>
+          <t>ARLINGTON End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>The ARLINGTON End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARLINGTON End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -19594,12 +19594,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>ATWOOD II End Table in Dark Walnut | GOODDEGG</t>
+          <t>ATWOOD II End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>The ATWOOD II End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ATWOOD II End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -19733,12 +19733,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>AUGSBURG End Table in Walnut Gold | GOODDEGG</t>
+          <t>AUGSBURG End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>The AUGSBURG End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AUGSBURG End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -19876,12 +19876,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>BACERRA End Table in Antique White Gold | GOODDEGG</t>
+          <t>BACERRA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>The BACERRA End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BACERRA End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -20017,12 +20017,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>BATAM II End Table in White Natural Tone | GOODDEGG</t>
+          <t>BATAM II End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>The BATAM II End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BATAM II End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -20154,12 +20154,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>BIMA II End Table in White Natural Tone | GOODDEGG</t>
+          <t>BIMA II End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>The BIMA II End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BIMA II End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -20295,12 +20295,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>BISHOP End Table in Black Gray | GOODDEGG</t>
+          <t>BISHOP End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>The BISHOP End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BISHOP End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -20434,12 +20434,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>CALANDRA End Table in Antique Black | GOODDEGG</t>
+          <t>CALANDRA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>The CALANDRA End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CALANDRA End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -20577,12 +20577,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>CARRIE End Table in Antique Black | GOODDEGG</t>
+          <t>CARRIE End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>The CARRIE End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CARRIE End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -20718,12 +20718,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>CONISBROUGH Round End Table in Modern | GOODDEGG</t>
+          <t>CONISBROUGH Round End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>The CONISBROUGH Round End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CONISBROUGH Round End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -20867,12 +20867,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>COOKSHIRE End Table in Rich Tobacco | GOODDEGG</t>
+          <t>COOKSHIRE End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>The COOKSHIRE End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>COOKSHIRE End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -21010,12 +21010,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>CORINNE End Table in White Distressed Dark Oak | GOODDEGG</t>
+          <t>CORINNE End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>The CORINNE End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CORINNE End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -21153,12 +21153,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>CRYSTAL FALLS End Table in Dark Cherry | GOODDEGG</t>
+          <t>CRYSTAL FALLS End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>The CRYSTAL FALLS End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRYSTAL FALLS End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -21295,12 +21295,12 @@
       </c>
       <c r="H146" s="24" t="inlineStr">
         <is>
-          <t>DUBENDORF End Table in Black | GOODDEGG</t>
+          <t>DUBENDORF End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I146" s="24" t="inlineStr">
         <is>
-          <t>The DUBENDORF End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DUBENDORF End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J146" s="24" t="inlineStr">
@@ -21439,12 +21439,12 @@
       </c>
       <c r="H147" s="24" t="inlineStr">
         <is>
-          <t>DUBENDORF End Table in White | GOODDEGG</t>
+          <t>DUBENDORF End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I147" s="24" t="inlineStr">
         <is>
-          <t>The DUBENDORF End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DUBENDORF End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J147" s="24" t="inlineStr">
@@ -21582,12 +21582,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>EIMEAR End Table in White Black | GOODDEGG</t>
+          <t>EIMEAR End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>The EIMEAR End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EIMEAR End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -21725,12 +21725,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>FINLEY End Table in Espresso | GOODDEGG</t>
+          <t>FINLEY End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>The FINLEY End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FINLEY End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -21868,12 +21868,12 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>GIORDANI End Table in Weathered Oak | GOODDEGG</t>
+          <t>GIORDANI End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>The GIORDANI End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GIORDANI End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -22016,12 +22016,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>GRANVIA End Table in Dark Cherry | GOODDEGG</t>
+          <t>GRANVIA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>The GRANVIA End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRANVIA End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -22157,12 +22157,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>GRASTEN Square End Table in Ash Gray | GOODDEGG</t>
+          <t>GRASTEN Square End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>The GRASTEN Square End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRASTEN Square End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -22306,12 +22306,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>HALCASTER End Table in Java | GOODDEGG</t>
+          <t>HALCASTER End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>The HALCASTER End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALCASTER End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -22448,12 +22448,12 @@
       </c>
       <c r="H154" s="48" t="inlineStr">
         <is>
-          <t>HALEWOOD End Table in Black | GOODDEGG</t>
+          <t>HALEWOOD End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I154" s="48" t="inlineStr">
         <is>
-          <t>The HALEWOOD End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALEWOOD End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J154" s="48" t="inlineStr">
@@ -22594,12 +22594,12 @@
       </c>
       <c r="H155" s="48" t="inlineStr">
         <is>
-          <t>HALEWOOD End Table in Oak | GOODDEGG</t>
+          <t>HALEWOOD End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I155" s="48" t="inlineStr">
         <is>
-          <t>The HALEWOOD End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALEWOOD End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J155" s="48" t="inlineStr">
@@ -22735,12 +22735,12 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>IZAR End Table in White Gun Metal | GOODDEGG</t>
+          <t>IZAR End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>The IZAR End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>IZAR End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -22874,12 +22874,12 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>JOLIET End Table in Antique White | GOODDEGG</t>
+          <t>JOLIET End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>The JOLIET End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JOLIET End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -23018,12 +23018,12 @@
       </c>
       <c r="H158" s="50" t="inlineStr">
         <is>
-          <t>KOBLENZ End Table in Light Teal | GOODDEGG</t>
+          <t>KOBLENZ End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I158" s="50" t="inlineStr">
         <is>
-          <t>The KOBLENZ End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KOBLENZ End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J158" s="50" t="inlineStr">
@@ -23164,12 +23164,12 @@
       </c>
       <c r="H159" s="50" t="inlineStr">
         <is>
-          <t>KOBLENZ End Table in Dark Walnut | GOODDEGG</t>
+          <t>KOBLENZ End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I159" s="50" t="inlineStr">
         <is>
-          <t>The KOBLENZ End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KOBLENZ End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J159" s="50" t="inlineStr">
@@ -23307,12 +23307,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>LAILA End Table in Chrome | GOODDEGG</t>
+          <t>LAILA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>The LAILA End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LAILA End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -23444,12 +23444,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>LOBB End Table in Natural Tone Black | GOODDEGG</t>
+          <t>LOBB End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>The LOBB End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LOBB End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -23590,12 +23590,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>LODIA End Table in Gray | GOODDEGG</t>
+          <t>LODIA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>The LODIA End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LODIA End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -23728,12 +23728,12 @@
       </c>
       <c r="H163" s="52" t="inlineStr">
         <is>
-          <t>LODIA III End Table in Black | GOODDEGG</t>
+          <t>LODIA III End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I163" s="52" t="inlineStr">
         <is>
-          <t>The LODIA III End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LODIA III End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J163" s="52" t="inlineStr">
@@ -23870,12 +23870,12 @@
       </c>
       <c r="H164" s="52" t="inlineStr">
         <is>
-          <t>LODIA III End Table in White | GOODDEGG</t>
+          <t>LODIA III End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I164" s="52" t="inlineStr">
         <is>
-          <t>The LODIA III End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LODIA III End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J164" s="52" t="inlineStr">
@@ -24011,12 +24011,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>LUDVIG End Table in Chrome Clear | GOODDEGG</t>
+          <t>LUDVIG End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>The LUDVIG End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LUDVIG End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -24154,12 +24154,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>MAJKEN End Table in White Natural Tone | GOODDEGG</t>
+          <t>MAJKEN End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>The MAJKEN End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MAJKEN End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -24296,12 +24296,12 @@
       </c>
       <c r="H167" s="24" t="inlineStr">
         <is>
-          <t>MANNEDORF End Table in Black Dark Walnut | GOODDEGG</t>
+          <t>MANNEDORF End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I167" s="24" t="inlineStr">
         <is>
-          <t>The MANNEDORF End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MANNEDORF End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J167" s="24" t="inlineStr">
@@ -24440,12 +24440,12 @@
       </c>
       <c r="H168" s="24" t="inlineStr">
         <is>
-          <t>MANNEDORF End Table in Black White | GOODDEGG</t>
+          <t>MANNEDORF End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I168" s="24" t="inlineStr">
         <is>
-          <t>The MANNEDORF End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MANNEDORF End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J168" s="24" t="inlineStr">
@@ -24587,12 +24587,12 @@
       </c>
       <c r="H169" s="54" t="inlineStr">
         <is>
-          <t>MARSTON End Table in Dark Walnut | GOODDEGG</t>
+          <t>MARSTON End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I169" s="54" t="inlineStr">
         <is>
-          <t>The MARSTON End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARSTON End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J169" s="54" t="inlineStr">
@@ -24734,12 +24734,12 @@
       </c>
       <c r="H170" s="54" t="inlineStr">
         <is>
-          <t>MARSTON End Table in Champagne | GOODDEGG</t>
+          <t>MARSTON End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I170" s="54" t="inlineStr">
         <is>
-          <t>The MARSTON End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARSTON End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J170" s="54" t="inlineStr">
@@ -24877,12 +24877,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>MAY End Table in Brown Cherry | GOODDEGG</t>
+          <t>MAY End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>The MAY End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MAY End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -25018,12 +25018,12 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>MEDA End Table in White Chrome | GOODDEGG</t>
+          <t>MEDA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>The MEDA End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MEDA End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -25162,12 +25162,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>MOA End Table in White Natural Tone | GOODDEGG</t>
+          <t>MOA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>The MOA End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MOA End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -25304,12 +25304,12 @@
       </c>
       <c r="H174" s="48" t="inlineStr">
         <is>
-          <t>NAHARA End Table in Black | GOODDEGG</t>
+          <t>NAHARA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I174" s="48" t="inlineStr">
         <is>
-          <t>The NAHARA End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NAHARA End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J174" s="48" t="inlineStr">
@@ -25446,12 +25446,12 @@
       </c>
       <c r="H175" s="48" t="inlineStr">
         <is>
-          <t>NAHARA End Table in Gray | GOODDEGG</t>
+          <t>NAHARA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I175" s="48" t="inlineStr">
         <is>
-          <t>The NAHARA End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NAHARA End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J175" s="48" t="inlineStr">
@@ -25588,12 +25588,12 @@
       </c>
       <c r="H176" s="48" t="inlineStr">
         <is>
-          <t>NAHARA End Table in White | GOODDEGG</t>
+          <t>NAHARA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I176" s="48" t="inlineStr">
         <is>
-          <t>The NAHARA End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NAHARA End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J176" s="48" t="inlineStr">
@@ -25730,12 +25730,12 @@
       </c>
       <c r="H177" s="50" t="inlineStr">
         <is>
-          <t>NINOVE End Table in Black Chrome | GOODDEGG</t>
+          <t>NINOVE End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I177" s="50" t="inlineStr">
         <is>
-          <t>The NINOVE End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NINOVE End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J177" s="50" t="inlineStr">
@@ -25874,12 +25874,12 @@
       </c>
       <c r="H178" s="50" t="inlineStr">
         <is>
-          <t>NINOVE End Table in White Chrome | GOODDEGG</t>
+          <t>NINOVE End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I178" s="50" t="inlineStr">
         <is>
-          <t>The NINOVE End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NINOVE End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J178" s="50" t="inlineStr">
@@ -26017,12 +26017,12 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>NORTHWICH End Table in Black Gray Matte Gold | GOODDEGG</t>
+          <t>NORTHWICH End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>The NORTHWICH End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NORTHWICH End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -26154,12 +26154,12 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>NOVA End Table in Satin Plated Black | GOODDEGG</t>
+          <t>NOVA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>The NOVA End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NOVA End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -26293,12 +26293,12 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>OAKWAY End Table in Weathered Oak | GOODDEGG</t>
+          <t>OAKWAY End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>The OAKWAY End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OAKWAY End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -26434,12 +26434,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>ORLA II End Table in Satin Plated Black | GOODDEGG</t>
+          <t>ORLA II End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>The ORLA II End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ORLA II End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -26571,12 +26571,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>ORRIN End Table in Gray Walnut | GOODDEGG</t>
+          <t>ORRIN End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>The ORRIN End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ORRIN End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -26717,12 +26717,12 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>POLTIMORE Round End Table in Oak | GOODDEGG</t>
+          <t>POLTIMORE Round End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>The POLTIMORE Round End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>POLTIMORE Round End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -26858,12 +26858,12 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>RAYA End Table in White | GOODDEGG</t>
+          <t>RAYA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>The RAYA End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RAYA End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -27003,12 +27003,12 @@
       </c>
       <c r="H186" s="35" t="inlineStr">
         <is>
-          <t>ROCHESTER End Table in Champagne | GOODDEGG</t>
+          <t>ROCHESTER End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I186" s="35" t="inlineStr">
         <is>
-          <t>The ROCHESTER End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ROCHESTER End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J186" s="35" t="inlineStr">
@@ -27154,12 +27154,12 @@
       </c>
       <c r="H187" s="35" t="inlineStr">
         <is>
-          <t>ROCHESTER End Table in Champagne | GOODDEGG</t>
+          <t>ROCHESTER End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I187" s="35" t="inlineStr">
         <is>
-          <t>The ROCHESTER End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ROCHESTER End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J187" s="35" t="inlineStr">
@@ -27299,12 +27299,12 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>ROSETTA End Table in Dark Walnut | GOODDEGG</t>
+          <t>ROSETTA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>The ROSETTA End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ROSETTA End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -27440,12 +27440,12 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>ROXO End Table in Satin Plated Black | GOODDEGG</t>
+          <t>ROXO End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>The ROXO End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ROXO End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -27577,12 +27577,12 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>RYLEE End Table in Chrome | GOODDEGG</t>
+          <t>RYLEE End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>The RYLEE End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RYLEE End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -27718,12 +27718,12 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>SINDAL End Table in Black | GOODDEGG</t>
+          <t>SINDAL End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>The SINDAL End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINDAL End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -27855,12 +27855,12 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>SINDAL Round End Table in Black | GOODDEGG</t>
+          <t>SINDAL Round End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>The SINDAL Round End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINDAL Round End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -27992,12 +27992,12 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>SLOANE End Table in White Dark Gray Chrome | GOODDEGG</t>
+          <t>SLOANE End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>The SLOANE End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SLOANE End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -28130,12 +28130,12 @@
       </c>
       <c r="H194" s="33" t="inlineStr">
         <is>
-          <t>STATEN End Table in Glossy Black Chrome | GOODDEGG</t>
+          <t>STATEN End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I194" s="33" t="inlineStr">
         <is>
-          <t>The STATEN End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STATEN End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J194" s="33" t="inlineStr">
@@ -28276,12 +28276,12 @@
       </c>
       <c r="H195" s="33" t="inlineStr">
         <is>
-          <t>STATEN End Table in Glossy White Chrome | GOODDEGG</t>
+          <t>STATEN End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I195" s="33" t="inlineStr">
         <is>
-          <t>The STATEN End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STATEN End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J195" s="33" t="inlineStr">
@@ -28421,12 +28421,12 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>SUNDANCE End Table in Chrome | GOODDEGG</t>
+          <t>SUNDANCE End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>The SUNDANCE End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SUNDANCE End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -28562,12 +28562,12 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>SURDAL End Table in Black | GOODDEGG</t>
+          <t>SURDAL End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>The SURDAL End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SURDAL End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -28702,12 +28702,12 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>TADCASTER End Table in Dark Cherry | GOODDEGG</t>
+          <t>TADCASTER End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>The TADCASTER End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TADCASTER End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -28843,12 +28843,12 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>TANIKA End Table in Chrome | GOODDEGG</t>
+          <t>TANIKA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>The TANIKA End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TANIKA End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -28982,12 +28982,12 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>THISTED Square Marble End Table in White Black | GOODDEGG</t>
+          <t>THISTED Square Marble End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>The THISTED Square Marble End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>THISTED Square Marble End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -29123,12 +29123,12 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>TITUS End Table in White Chrome | GOODDEGG</t>
+          <t>TITUS End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>The TITUS End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TITUS End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -29264,12 +29264,12 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>TORKEL End Table in White Chrome | GOODDEGG</t>
+          <t>TORKEL End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>The TORKEL End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TORKEL End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -29405,12 +29405,12 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>VALO End Table in Satin Plated Black | GOODDEGG</t>
+          <t>VALO End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>The VALO End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VALO End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -29544,12 +29544,12 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>VILLARSGLANE End Table in Chrome | GOODDEGG</t>
+          <t>VILLARSGLANE End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>The VILLARSGLANE End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VILLARSGLANE End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -29681,12 +29681,12 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>VIRDEN Round End Table in Black White Gold | GOODDEGG</t>
+          <t>VIRDEN Round End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>The VIRDEN Round End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VIRDEN Round End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -29822,12 +29822,12 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>VIRDEN Square End Table in Black White Gold | GOODDEGG</t>
+          <t>VIRDEN Square End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>The VIRDEN Square End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VIRDEN Square End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -29966,12 +29966,12 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>WALWORTH End Table in Dark Oak | GOODDEGG</t>
+          <t>WALWORTH End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>The WALWORTH End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WALWORTH End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>WESTERHAM End Table w/ LED in Dark Cherry | GOODDEGG</t>
+          <t>WESTERHAM End Table w/ LED | GOODDEGG</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>The WESTERHAM End Table w/ LED creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WESTERHAM End Table w/ LED supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -30246,12 +30246,12 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>WETTINGEN End Table in Chrome | GOODDEGG</t>
+          <t>WETTINGEN End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>The WETTINGEN End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WETTINGEN End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -30386,12 +30386,12 @@
       </c>
       <c r="H210" s="39" t="inlineStr">
         <is>
-          <t>WETZIKON End Table in Black Silver | GOODDEGG</t>
+          <t>WETZIKON End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I210" s="39" t="inlineStr">
         <is>
-          <t>The WETZIKON End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WETZIKON End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J210" s="39" t="inlineStr">
@@ -30534,12 +30534,12 @@
       </c>
       <c r="H211" s="39" t="inlineStr">
         <is>
-          <t>WETZIKON End Table in White Silver | GOODDEGG</t>
+          <t>WETZIKON End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I211" s="39" t="inlineStr">
         <is>
-          <t>The WETZIKON End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WETZIKON End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J211" s="39" t="inlineStr">
@@ -30679,12 +30679,12 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>XANTHUS End Table in Black | GOODDEGG</t>
+          <t>XANTHUS End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>The XANTHUS End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>XANTHUS End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -30816,12 +30816,12 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>ZOLA End Table in Chrome | GOODDEGG</t>
+          <t>ZOLA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>The ZOLA End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZOLA End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -30959,12 +30959,12 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>ARLINGTON Sofa Table in Antique White | GOODDEGG</t>
+          <t>ARLINGTON Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>The ARLINGTON Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARLINGTON Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -31102,12 +31102,12 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>ATWOOD II Sofa Table in Dark Walnut | GOODDEGG</t>
+          <t>ATWOOD II Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>The ATWOOD II Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ATWOOD II Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -31241,12 +31241,12 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>AUGSBURG Side Table in Walnut Gold | GOODDEGG</t>
+          <t>AUGSBURG Side Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>The AUGSBURG Side Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AUGSBURG Side Table Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -31384,12 +31384,12 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>AUGSBURG Sofa Table in Walnut Gold | GOODDEGG</t>
+          <t>AUGSBURG Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>The AUGSBURG Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AUGSBURG Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -31528,12 +31528,12 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>BACERRA Sofa Table in Antique White Gold | GOODDEGG</t>
+          <t>BACERRA Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>The BACERRA Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BACERRA Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -31669,12 +31669,12 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>BATAM II Sofa Table in White Natural Tone | GOODDEGG</t>
+          <t>BATAM II Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>The BATAM II Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BATAM II Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -31806,12 +31806,12 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>BIMA II Sofa Table in White Natural Tone | GOODDEGG</t>
+          <t>BIMA II Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>The BIMA II Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BIMA II Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -31945,12 +31945,12 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>BRAMPTON Sofa Table in Espresso Black | GOODDEGG</t>
+          <t>BRAMPTON Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>The BRAMPTON Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BRAMPTON Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -32088,12 +32088,12 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>BRYANNA Sofa Table in Antique Light Oak | GOODDEGG</t>
+          <t>BRYANNA Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>The BRYANNA Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BRYANNA Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -32231,12 +32231,12 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>BUNBURY Sofa Table in Cherry | GOODDEGG</t>
+          <t>BUNBURY Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>The BUNBURY Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BUNBURY Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -32374,12 +32374,12 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>CALANDRA Sofa Table in Antique Black | GOODDEGG</t>
+          <t>CALANDRA Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>The CALANDRA Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CALANDRA Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -32518,12 +32518,12 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>CHESHIRE Sofa Table in Dark Cherry | GOODDEGG</t>
+          <t>CHESHIRE Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>The CHESHIRE Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CHESHIRE Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -32661,12 +32661,12 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>CRYSTAL FALLS Sofa Table in Dark Cherry | GOODDEGG</t>
+          <t>CRYSTAL FALLS Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>The CRYSTAL FALLS Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRYSTAL FALLS Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -32803,12 +32803,12 @@
       </c>
       <c r="H227" s="46" t="inlineStr">
         <is>
-          <t>DUBENDORF Sofa Table in Black | GOODDEGG</t>
+          <t>DUBENDORF Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I227" s="46" t="inlineStr">
         <is>
-          <t>The DUBENDORF Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DUBENDORF Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J227" s="46" t="inlineStr">
@@ -32947,12 +32947,12 @@
       </c>
       <c r="H228" s="46" t="inlineStr">
         <is>
-          <t>DUBENDORF Sofa Table in White | GOODDEGG</t>
+          <t>DUBENDORF Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I228" s="46" t="inlineStr">
         <is>
-          <t>The DUBENDORF Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DUBENDORF Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J228" s="46" t="inlineStr">
@@ -33090,12 +33090,12 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>EIMEAR Sofa Table in White Black | GOODDEGG</t>
+          <t>EIMEAR Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>The EIMEAR Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EIMEAR Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -33233,12 +33233,12 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>GIORDANI Sofa Table in Weathered Oak | GOODDEGG</t>
+          <t>GIORDANI Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>The GIORDANI Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GIORDANI Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -33381,12 +33381,12 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>GRANVIA Sofa Table in Dark Cherry | GOODDEGG</t>
+          <t>GRANVIA Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>The GRANVIA Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRANVIA Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -33522,12 +33522,12 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>IZAR Sofa Table in White Gun Metal | GOODDEGG</t>
+          <t>IZAR Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>The IZAR Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>IZAR Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="H233" s="44" t="inlineStr">
         <is>
-          <t>KOBLENZ Sofa Table in Light Teal | GOODDEGG</t>
+          <t>KOBLENZ Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I233" s="44" t="inlineStr">
         <is>
-          <t>The KOBLENZ Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KOBLENZ Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J233" s="44" t="inlineStr">
@@ -33808,12 +33808,12 @@
       </c>
       <c r="H234" s="44" t="inlineStr">
         <is>
-          <t>KOBLENZ Sofa Table in Dark Walnut | GOODDEGG</t>
+          <t>KOBLENZ Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I234" s="44" t="inlineStr">
         <is>
-          <t>The KOBLENZ Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KOBLENZ Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J234" s="44" t="inlineStr">
@@ -33951,12 +33951,12 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>LAILA Sofa Table in Chrome | GOODDEGG</t>
+          <t>LAILA Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>The LAILA Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LAILA Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -34088,12 +34088,12 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>LOBB Sofa Table in Natural Tone Black | GOODDEGG</t>
+          <t>LOBB Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>The LOBB Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LOBB Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -34235,12 +34235,12 @@
       </c>
       <c r="H237" s="30" t="inlineStr">
         <is>
-          <t>LODIA III Sofa Table in Black | GOODDEGG</t>
+          <t>LODIA III Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I237" s="30" t="inlineStr">
         <is>
-          <t>The LODIA III Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LODIA III Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J237" s="30" t="inlineStr">
@@ -34377,12 +34377,12 @@
       </c>
       <c r="H238" s="30" t="inlineStr">
         <is>
-          <t>LODIA III Sofa Table in White | GOODDEGG</t>
+          <t>LODIA III Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I238" s="30" t="inlineStr">
         <is>
-          <t>The LODIA III Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LODIA III Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J238" s="30" t="inlineStr">
@@ -34518,12 +34518,12 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>LODIA Sofa Table in Gray | GOODDEGG</t>
+          <t>LODIA Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>The LODIA Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LODIA Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -34655,12 +34655,12 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>LUDVIG Sofa Table in Chrome Clear | GOODDEGG</t>
+          <t>LUDVIG Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>The LUDVIG Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LUDVIG Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -34798,12 +34798,12 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>MAJKEN Sofa Table in White Natural Tone | GOODDEGG</t>
+          <t>MAJKEN Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>The MAJKEN Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MAJKEN Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -34940,12 +34940,12 @@
       </c>
       <c r="H242" s="46" t="inlineStr">
         <is>
-          <t>MANNEDORF Sofa Table in Black Dark Walnut | GOODDEGG</t>
+          <t>MANNEDORF Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I242" s="46" t="inlineStr">
         <is>
-          <t>The MANNEDORF Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MANNEDORF Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J242" s="46" t="inlineStr">
@@ -35088,12 +35088,12 @@
       </c>
       <c r="H243" s="46" t="inlineStr">
         <is>
-          <t>MANNEDORF Sofa Table in Black White | GOODDEGG</t>
+          <t>MANNEDORF Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I243" s="46" t="inlineStr">
         <is>
-          <t>The MANNEDORF Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MANNEDORF Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J243" s="46" t="inlineStr">
@@ -35231,12 +35231,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>MAY Sofa Table in Brown Cherry | GOODDEGG</t>
+          <t>MAY Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>The MAY Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MAY Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -35374,12 +35374,12 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>MEADOW Sofa Table in Antique Black | GOODDEGG</t>
+          <t>MEADOW Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>The MEADOW Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MEADOW Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -35517,12 +35517,12 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>MOA Sofa Table in White Natural Tone | GOODDEGG</t>
+          <t>MOA Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>The MOA Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MOA Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -35659,12 +35659,12 @@
       </c>
       <c r="H247" s="56" t="inlineStr">
         <is>
-          <t>NAHARA Sofa Table in Black | GOODDEGG</t>
+          <t>NAHARA Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I247" s="56" t="inlineStr">
         <is>
-          <t>The NAHARA Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NAHARA Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J247" s="56" t="inlineStr">
@@ -35801,12 +35801,12 @@
       </c>
       <c r="H248" s="56" t="inlineStr">
         <is>
-          <t>NAHARA Sofa Table in Gray | GOODDEGG</t>
+          <t>NAHARA Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I248" s="56" t="inlineStr">
         <is>
-          <t>The NAHARA Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NAHARA Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J248" s="56" t="inlineStr">
@@ -35943,12 +35943,12 @@
       </c>
       <c r="H249" s="56" t="inlineStr">
         <is>
-          <t>NAHARA Sofa Table in White | GOODDEGG</t>
+          <t>NAHARA Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I249" s="56" t="inlineStr">
         <is>
-          <t>The NAHARA Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NAHARA Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J249" s="56" t="inlineStr">
@@ -36084,12 +36084,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>NOVA Sofa Table in Satin Plated Black | GOODDEGG</t>
+          <t>NOVA Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>The NOVA Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NOVA Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>OAKWAY Sofa Table in Weathered Oak | GOODDEGG</t>
+          <t>OAKWAY Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>The OAKWAY Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OAKWAY Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -36364,12 +36364,12 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>OLBIA Sofa Table in Rustic Oak Sand Black | GOODDEGG</t>
+          <t>OLBIA Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>The OLBIA Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OLBIA Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>ORLA II Sofa Table in Satin Plated Black | GOODDEGG</t>
+          <t>ORLA II Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>The ORLA II Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ORLA II Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -36642,12 +36642,12 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>RAYA Sofa Table in White | GOODDEGG</t>
+          <t>RAYA Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>The RAYA Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RAYA Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -36785,12 +36785,12 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>ROSETTA Sofa Table in Dark Walnut | GOODDEGG</t>
+          <t>ROSETTA Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>The ROSETTA Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ROSETTA Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -36926,12 +36926,12 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>ROXO Sofa Table in Satin Plated Black | GOODDEGG</t>
+          <t>ROXO Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>The ROXO Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ROXO Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -37063,12 +37063,12 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>RYLEE Sofa Table in Chrome | GOODDEGG</t>
+          <t>RYLEE Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>The RYLEE Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RYLEE Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -37204,12 +37204,12 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>SLOANE Sofa Table in White Dark Gray Chrome | GOODDEGG</t>
+          <t>SLOANE Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>The SLOANE Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SLOANE Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -37342,12 +37342,12 @@
       </c>
       <c r="H259" s="54" t="inlineStr">
         <is>
-          <t>STATEN Sofa Table in Glossy Black Chrome | GOODDEGG</t>
+          <t>STATEN Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I259" s="54" t="inlineStr">
         <is>
-          <t>The STATEN Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STATEN Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J259" s="54" t="inlineStr">
@@ -37488,12 +37488,12 @@
       </c>
       <c r="H260" s="54" t="inlineStr">
         <is>
-          <t>STATEN Sofa Table in Glossy White Chrome | GOODDEGG</t>
+          <t>STATEN Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I260" s="54" t="inlineStr">
         <is>
-          <t>The STATEN Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STATEN Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J260" s="54" t="inlineStr">
@@ -37633,12 +37633,12 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>SUNDANCE Sofa Table in Chrome | GOODDEGG</t>
+          <t>SUNDANCE Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>The SUNDANCE Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SUNDANCE Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -37774,12 +37774,12 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>TITUS Sofa Table in White Chrome | GOODDEGG</t>
+          <t>TITUS Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>The TITUS Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TITUS Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -37915,12 +37915,12 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>VALO Sofa Table in Satin Plated Black | GOODDEGG</t>
+          <t>VALO Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>The VALO Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VALO Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -38054,12 +38054,12 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>VILLARSGLANE Sofa Table in Chrome | GOODDEGG</t>
+          <t>VILLARSGLANE Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>The VILLARSGLANE Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VILLARSGLANE Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -38194,12 +38194,12 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>WALWORTH Sofa Table in Dark Oak | GOODDEGG</t>
+          <t>WALWORTH Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>The WALWORTH Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WALWORTH Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -38337,12 +38337,12 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>WETTINGEN Sofa Table in Chrome | GOODDEGG</t>
+          <t>WETTINGEN Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>The WETTINGEN Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WETTINGEN Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -38477,12 +38477,12 @@
       </c>
       <c r="H267" s="48" t="inlineStr">
         <is>
-          <t>WETZIKON Sofa Table in Black Silver | GOODDEGG</t>
+          <t>WETZIKON Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I267" s="48" t="inlineStr">
         <is>
-          <t>The WETZIKON Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WETZIKON Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J267" s="48" t="inlineStr">
@@ -38625,12 +38625,12 @@
       </c>
       <c r="H268" s="48" t="inlineStr">
         <is>
-          <t>WETZIKON Sofa Table in White Silver | GOODDEGG</t>
+          <t>WETZIKON Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I268" s="48" t="inlineStr">
         <is>
-          <t>The WETZIKON Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WETZIKON Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J268" s="48" t="inlineStr">
@@ -38770,12 +38770,12 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>XANTHUS Sofa Table in Black | GOODDEGG</t>
+          <t>XANTHUS Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>The XANTHUS Sofa Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>XANTHUS Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -38909,12 +38909,12 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>ARTH Side Table in Walnut | GOODDEGG</t>
+          <t>ARTH Side Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>The ARTH Side Table adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARTH Side Table Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -39052,12 +39052,12 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>SPIEZ Accent Chair in Walnut Beige | GOODDEGG</t>
+          <t>SPIEZ Accent Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>The SPIEZ Accent Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SPIEZ Accent Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -39200,12 +39200,12 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>BELP Accent Chair in Walnut Beige | GOODDEGG</t>
+          <t>BELP Accent Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>The BELP Accent Chair creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELP Accent Chair Side Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -39346,12 +39346,12 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>CHILOQUIN Side Table in Natural | GOODDEGG</t>
+          <t>CHILOQUIN Side Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>The CHILOQUIN Side Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CHILOQUIN Side Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -39487,12 +39487,12 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>GARIBALDI Side Table in Brown Gray | GOODDEGG</t>
+          <t>GARIBALDI Side Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>The GARIBALDI Side Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GARIBALDI Side Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -39628,12 +39628,12 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>NORTHWICH Side Table in White Matte Gold | GOODDEGG</t>
+          <t>NORTHWICH Side Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>The NORTHWICH Side Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NORTHWICH Side Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -39767,12 +39767,12 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>VARDO Side Table in Walnut | GOODDEGG</t>
+          <t>VARDO Side Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>The VARDO Side Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VARDO Side Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -39908,12 +39908,12 @@
       </c>
       <c r="H277" s="52" t="inlineStr">
         <is>
-          <t>BORUP 3 Pc. Table Set in Dark Brown Black | GOODDEGG</t>
+          <t>BORUP 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I277" s="52" t="inlineStr">
         <is>
-          <t>The BORUP Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BORUP 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J277" s="52" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="H278" s="52" t="inlineStr">
         <is>
-          <t>BORUP 3 Pc. Table Set in Natural Black | GOODDEGG</t>
+          <t>BORUP 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I278" s="52" t="inlineStr">
         <is>
-          <t>The BORUP Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BORUP 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J278" s="52" t="inlineStr">
@@ -40193,12 +40193,12 @@
       </c>
       <c r="H279" s="54" t="inlineStr">
         <is>
-          <t>FINDLAY 3 Pc. Table Set in Black | GOODDEGG</t>
+          <t>FINDLAY 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I279" s="54" t="inlineStr">
         <is>
-          <t>The FINDLAY Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FINDLAY 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J279" s="54" t="inlineStr">
@@ -40339,12 +40339,12 @@
       </c>
       <c r="H280" s="54" t="inlineStr">
         <is>
-          <t>FINDLAY 3 Pc. Table Set in Brown | GOODDEGG</t>
+          <t>FINDLAY 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I280" s="54" t="inlineStr">
         <is>
-          <t>The FINDLAY Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FINDLAY 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J280" s="54" t="inlineStr">
@@ -40485,12 +40485,12 @@
       </c>
       <c r="H281" s="54" t="inlineStr">
         <is>
-          <t>FINDLAY 3 Pc. Table Set in Black &amp; White | GOODDEGG</t>
+          <t>FINDLAY 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I281" s="54" t="inlineStr">
         <is>
-          <t>The FINDLAY Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FINDLAY 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J281" s="54" t="inlineStr">
@@ -40631,12 +40631,12 @@
       </c>
       <c r="H282" s="54" t="inlineStr">
         <is>
-          <t>FINDLAY 3 Pc. Table Set in Gray | GOODDEGG</t>
+          <t>FINDLAY 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I282" s="54" t="inlineStr">
         <is>
-          <t>The FINDLAY Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FINDLAY 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J282" s="54" t="inlineStr">
@@ -40777,12 +40777,12 @@
       </c>
       <c r="H283" s="54" t="inlineStr">
         <is>
-          <t>FINDLAY 3 Pc. Table Set in Light Gray | GOODDEGG</t>
+          <t>FINDLAY 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I283" s="54" t="inlineStr">
         <is>
-          <t>The FINDLAY Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FINDLAY 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J283" s="54" t="inlineStr">
@@ -40923,12 +40923,12 @@
       </c>
       <c r="H284" s="54" t="inlineStr">
         <is>
-          <t>FINDLAY 3 Pc. Table Set in White | GOODDEGG</t>
+          <t>FINDLAY 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I284" s="54" t="inlineStr">
         <is>
-          <t>The FINDLAY Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FINDLAY 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J284" s="54" t="inlineStr">
@@ -41067,12 +41067,12 @@
       </c>
       <c r="H285" s="56" t="inlineStr">
         <is>
-          <t>HOLEN 3 Pc. Table Set in Gray | GOODDEGG</t>
+          <t>HOLEN 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I285" s="56" t="inlineStr">
         <is>
-          <t>The HOLEN Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLEN 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J285" s="56" t="inlineStr">
@@ -41211,12 +41211,12 @@
       </c>
       <c r="H286" s="56" t="inlineStr">
         <is>
-          <t>HOLEN 3 Pc. Table Set in Natural | GOODDEGG</t>
+          <t>HOLEN 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I286" s="56" t="inlineStr">
         <is>
-          <t>The HOLEN Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLEN 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J286" s="56" t="inlineStr">
@@ -41354,12 +41354,12 @@
       </c>
       <c r="H287" s="28" t="inlineStr">
         <is>
-          <t>OPHIRA 3 Pc. Table Set in Dark Brown | GOODDEGG</t>
+          <t>OPHIRA 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I287" s="28" t="inlineStr">
         <is>
-          <t>The OPHIRA Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OPHIRA 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J287" s="28" t="inlineStr">
@@ -41495,12 +41495,12 @@
       </c>
       <c r="H288" s="28" t="inlineStr">
         <is>
-          <t>OPHIRA 3 Pc. Table Set in Natural | GOODDEGG</t>
+          <t>OPHIRA 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I288" s="28" t="inlineStr">
         <is>
-          <t>The OPHIRA Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OPHIRA 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J288" s="28" t="inlineStr">
@@ -41636,12 +41636,12 @@
       </c>
       <c r="H289" s="52" t="inlineStr">
         <is>
-          <t>PALLAS 3 Pc. Table Set in Black | GOODDEGG</t>
+          <t>PALLAS 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I289" s="52" t="inlineStr">
         <is>
-          <t>The PALLAS Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALLAS 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J289" s="52" t="inlineStr">
@@ -41777,12 +41777,12 @@
       </c>
       <c r="H290" s="52" t="inlineStr">
         <is>
-          <t>PALLAS 3 Pc. Table Set in Natural | GOODDEGG</t>
+          <t>PALLAS 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I290" s="52" t="inlineStr">
         <is>
-          <t>The PALLAS Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALLAS 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J290" s="52" t="inlineStr">
@@ -41918,12 +41918,12 @@
       </c>
       <c r="H291" s="52" t="inlineStr">
         <is>
-          <t>PALLAS 3 Pc. Table Set in White | GOODDEGG</t>
+          <t>PALLAS 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I291" s="52" t="inlineStr">
         <is>
-          <t>The PALLAS Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALLAS 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J291" s="52" t="inlineStr">
@@ -42059,12 +42059,12 @@
       </c>
       <c r="H292" s="24" t="inlineStr">
         <is>
-          <t>RONDE 3 Pc. Table Set in Natural | GOODDEGG</t>
+          <t>RONDE 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I292" s="24" t="inlineStr">
         <is>
-          <t>The RONDE Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RONDE 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J292" s="24" t="inlineStr">
@@ -42200,12 +42200,12 @@
       </c>
       <c r="H293" s="24" t="inlineStr">
         <is>
-          <t>RONDE 3 Pc. Table Set in White | GOODDEGG</t>
+          <t>RONDE 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I293" s="24" t="inlineStr">
         <is>
-          <t>The RONDE Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RONDE 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J293" s="24" t="inlineStr">
@@ -42342,12 +42342,12 @@
       </c>
       <c r="H294" s="56" t="inlineStr">
         <is>
-          <t>WHETSTONE 3 Pc. Table Set in Black | GOODDEGG</t>
+          <t>WHETSTONE 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I294" s="56" t="inlineStr">
         <is>
-          <t>The WHETSTONE Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WHETSTONE 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J294" s="56" t="inlineStr">
@@ -42486,12 +42486,12 @@
       </c>
       <c r="H295" s="56" t="inlineStr">
         <is>
-          <t>WHETSTONE 3 Pc. Table Set in White | GOODDEGG</t>
+          <t>WHETSTONE 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I295" s="56" t="inlineStr">
         <is>
-          <t>The WHETSTONE Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WHETSTONE 3 Pc. Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J295" s="56" t="inlineStr">
@@ -42631,12 +42631,12 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>BRAMPTON 3 Pc. Table Set in Espresso Black | GOODDEGG</t>
+          <t>BRAMPTON 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>The BRAMPTON Table brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BRAMPTON 3 Pc. Table Set Occasional Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -42779,12 +42779,12 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Bryanna 3 Pc. Set in Antique Light Oak | GOODDEGG</t>
+          <t>BRYANNA 3 Pc. Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>The BRYANNA brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BRYANNA 3 Pc. Set Occasional Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -42927,12 +42927,12 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>BUNBURY 3 Pc. Coffee Table Set in Cherry | GOODDEGG</t>
+          <t>BUNBURY 3 Pc. Coffee Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>The BUNBURY Coffee Table brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BUNBURY 3 Pc. Coffee Table Set Occasional Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -43071,12 +43071,12 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>CHESHIRE 3 Pc. Table Set in Dark Cherry | GOODDEGG</t>
+          <t>CHESHIRE 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>The CHESHIRE Table brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CHESHIRE 3 Pc. Table Set Occasional Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -43224,7 +43224,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>LECHESTER Coffee Table w/ Faux Marble brings everyday comfort and function to your. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Occasional Set LECHESTER 3 Pc. Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -43367,12 +43367,12 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>LODIVEA 3 Pc. Coffee Table Set w/ Faux Marble in Black | GOODDEGG</t>
+          <t>LODIVEA 3 Pc. Coffee Table Set w/ Faux Marble | GOODDEGG</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>LODIVEA Coffee Table w/ Faux Marble brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Occasional Set LODIVEA 3 Pc. Coffee Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
@@ -43510,12 +43510,12 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>MONANGO 3 Pc. Table Set in Weathered Gray | GOODDEGG</t>
+          <t>MONANGO 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>The MONANGO Table brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MONANGO 3 Pc. Table Set Occasional Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
@@ -43651,12 +43651,12 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>OLBIA 3 Pc. Coffee Table Set in Rustic Oak Sand Black | GOODDEGG</t>
+          <t>OLBIA 3 Pc. Coffee Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>The OLBIA Coffee Table brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OLBIA 3 Pc. Coffee Table Set Occasional Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
@@ -43799,12 +43799,12 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>ORBE 3 Pc. Table Set in Espresso | GOODDEGG</t>
+          <t>ORBE 3 Pc. Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>The ORBE Table brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ORBE 3 Pc. Table Set Occasional Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
@@ -43941,12 +43941,12 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Garibaldi TV Stand in Brown Gray | GOODDEGG</t>
+          <t>GARIBALDI TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>The GARIBALDI TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GARIBALDI TV Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
@@ -44081,12 +44081,12 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Hepburne 70" TV Stand in Adjustable Shelves | GOODDEGG</t>
+          <t>HEPBURNE 70" TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>The HEPBURNE TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HEPBURNE 70" TV Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
@@ -44219,12 +44219,12 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>IDANHA TV Stand in Natural | GOODDEGG</t>
+          <t>IDANHA TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>The IDANHA TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>IDANHA TV Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
@@ -44359,12 +44359,12 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Westerham 70" TV Stand in Dark Cherry | GOODDEGG</t>
+          <t>WESTERHAM 70" TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>The WESTERHAM TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WESTERHAM 70" TV Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
@@ -44499,12 +44499,12 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>ORKDAL Coffee Table in Walnut | GOODDEGG</t>
+          <t>ORKDAL Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>The ORKDAL Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ORKDAL Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
@@ -44642,12 +44642,12 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>ORKDAL End Table in Walnut | GOODDEGG</t>
+          <t>ORKDAL End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>The ORKDAL End Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ORKDAL End Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
@@ -44785,12 +44785,12 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>ORKDAL Sofa Table in Walnut | GOODDEGG</t>
+          <t>ORKDAL Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>The ORKDAL Sofa Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ORKDAL Sofa Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">

--- a/FOA Singles/Living-Single.xlsx
+++ b/FOA Singles/Living-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/FOA Singles/Living-Single.xlsx
+++ b/FOA Singles/Living-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
